--- a/hourly datasets/PlantID_year21final.xlsx
+++ b/hourly datasets/PlantID_year21final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1163"/>
+  <dimension ref="A1:C1183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1407,10 +1407,10 @@
         <v>56808</v>
       </c>
       <c r="B89" t="n">
-        <v>0.6560628661035663</v>
+        <v>0.3478856442693265</v>
       </c>
       <c r="C89" t="n">
-        <v>0.3451010713324684</v>
+        <v>0.2714913077185301</v>
       </c>
     </row>
     <row r="90">
@@ -2628,10 +2628,10 @@
         <v>55736</v>
       </c>
       <c r="B200" t="n">
-        <v>0.5024937978274088</v>
+        <v>0.5025053243843344</v>
       </c>
       <c r="C200" t="n">
-        <v>0.250091054208617</v>
+        <v>0.249616401221764</v>
       </c>
     </row>
     <row r="201">
@@ -3684,10 +3684,10 @@
         <v>55375</v>
       </c>
       <c r="B296" t="n">
-        <v>0.4991038301116364</v>
+        <v>0.4990565637886372</v>
       </c>
       <c r="C296" t="n">
-        <v>0.1825762648393743</v>
+        <v>0.1825707546251471</v>
       </c>
     </row>
     <row r="297">
@@ -5246,10 +5246,10 @@
         <v>55088</v>
       </c>
       <c r="B438" t="n">
-        <v>0.2983767718434241</v>
+        <v>0.5569152198503536</v>
       </c>
       <c r="C438" t="n">
-        <v>0.0831649225884578</v>
+        <v>0.511785397159541</v>
       </c>
     </row>
     <row r="439">
@@ -5312,10 +5312,10 @@
         <v>55076</v>
       </c>
       <c r="B444" t="n">
-        <v>0.6184826993728053</v>
+        <v>0.3576282880875815</v>
       </c>
       <c r="C444" t="n">
-        <v>0.1782577627300797</v>
+        <v>0.1468891029233338</v>
       </c>
     </row>
     <row r="445">
@@ -5631,10 +5631,10 @@
         <v>54802</v>
       </c>
       <c r="B473" t="n">
-        <v>0.5332754748417758</v>
+        <v>0.5336645761853478</v>
       </c>
       <c r="C473" t="n">
-        <v>0.1416295273471442</v>
+        <v>0.1416161960653781</v>
       </c>
     </row>
     <row r="474">
@@ -5727,266 +5727,266 @@
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>54638</v>
+        <v>54634</v>
       </c>
       <c r="B482" t="n">
-        <v>0.1610285940099401</v>
+        <v>0.224631897800049</v>
       </c>
       <c r="C482" t="n">
-        <v>0.1463367509708348</v>
+        <v>0.1092926301399697</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>54634</v>
+        <v>54605</v>
       </c>
       <c r="B483" t="n">
-        <v>0.224631897800049</v>
+        <v>0.3063754922102614</v>
       </c>
       <c r="C483" t="n">
-        <v>0.1092926301399697</v>
+        <v>0.2891919376631645</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>54605</v>
+        <v>54593</v>
       </c>
       <c r="B484" t="n">
-        <v>0.3063754922102614</v>
+        <v>0.3284086644228006</v>
       </c>
       <c r="C484" t="n">
-        <v>0.2891919376631645</v>
+        <v>0.1595329340011535</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>54593</v>
+        <v>54592</v>
       </c>
       <c r="B485" t="n">
-        <v>0.3284086644228006</v>
+        <v>0.3639186404823023</v>
       </c>
       <c r="C485" t="n">
-        <v>0.1595329340011535</v>
+        <v>0.1654075528017875</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>54592</v>
+        <v>54586</v>
       </c>
       <c r="B486" t="n">
-        <v>0.3639186404823023</v>
+        <v>0.400788398139746</v>
       </c>
       <c r="C486" t="n">
-        <v>0.1654075528017875</v>
+        <v>0.1581699489361221</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>54586</v>
+        <v>54574</v>
       </c>
       <c r="B487" t="n">
-        <v>0.400788398139746</v>
+        <v>0.4060944849538036</v>
       </c>
       <c r="C487" t="n">
-        <v>0.1581699489361221</v>
+        <v>0.1630613774039515</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>54574</v>
+        <v>54556</v>
       </c>
       <c r="B488" t="n">
-        <v>0.4060944849538036</v>
+        <v>0.05144623658320026</v>
       </c>
       <c r="C488" t="n">
-        <v>0.1630613774039515</v>
+        <v>0.03839014620205811</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>54556</v>
+        <v>54547</v>
       </c>
       <c r="B489" t="n">
-        <v>0.5375731595324875</v>
+        <v>0.4988209105644663</v>
       </c>
       <c r="C489" t="n">
-        <v>0.5504879849364057</v>
+        <v>0.2949807278642568</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>54547</v>
+        <v>54537</v>
       </c>
       <c r="B490" t="n">
-        <v>0.4988209105644663</v>
+        <v>0.3288649969752688</v>
       </c>
       <c r="C490" t="n">
-        <v>0.2949807278642568</v>
+        <v>0.2347665317848232</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>54537</v>
+        <v>54476</v>
       </c>
       <c r="B491" t="n">
-        <v>0.3288649969752688</v>
+        <v>0.2794412034482892</v>
       </c>
       <c r="C491" t="n">
-        <v>0.2347665317848232</v>
+        <v>0.1111362300272125</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>54476</v>
+        <v>54466</v>
       </c>
       <c r="B492" t="n">
-        <v>0.2794412034482892</v>
+        <v>0.4893873083030407</v>
       </c>
       <c r="C492" t="n">
-        <v>0.1111362300272125</v>
+        <v>0.4349286841484414</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>54466</v>
+        <v>54426</v>
       </c>
       <c r="B493" t="n">
-        <v>0.4893873083030407</v>
+        <v>0.4359577836311091</v>
       </c>
       <c r="C493" t="n">
-        <v>0.4349286841484414</v>
+        <v>0.4397060526148447</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>54426</v>
+        <v>54415</v>
       </c>
       <c r="B494" t="n">
-        <v>0.4359577836311091</v>
+        <v>0.2146940262075893</v>
       </c>
       <c r="C494" t="n">
-        <v>0.4397060526148447</v>
+        <v>0.1410578881686743</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>54415</v>
+        <v>54365</v>
       </c>
       <c r="B495" t="n">
-        <v>0.2146940262075893</v>
+        <v>0.4493372096919986</v>
       </c>
       <c r="C495" t="n">
-        <v>0.1410578881686743</v>
+        <v>0.2873065778271885</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>54365</v>
+        <v>54324</v>
       </c>
       <c r="B496" t="n">
-        <v>0.4493372096919986</v>
+        <v>0.2923822164492309</v>
       </c>
       <c r="C496" t="n">
-        <v>0.2873065778271885</v>
+        <v>0.1852842470525195</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>54324</v>
+        <v>54304</v>
       </c>
       <c r="B497" t="n">
-        <v>0.2923822164492309</v>
+        <v>0.3623695729252085</v>
       </c>
       <c r="C497" t="n">
-        <v>0.1852842470525195</v>
+        <v>0.1617722182517574</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>54304</v>
+        <v>54276</v>
       </c>
       <c r="B498" t="n">
-        <v>0.3623695729252085</v>
+        <v>0.09271303005027264</v>
       </c>
       <c r="C498" t="n">
-        <v>0.1617722182517574</v>
+        <v>0.09055857683687731</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>54276</v>
+        <v>54238</v>
       </c>
       <c r="B499" t="n">
-        <v>0.2891540654975843</v>
+        <v>0.2510686750674331</v>
       </c>
       <c r="C499" t="n">
-        <v>0.2669522966123516</v>
+        <v>0.1162527508097197</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>54238</v>
+        <v>54149</v>
       </c>
       <c r="B500" t="n">
-        <v>0.2510686750674331</v>
+        <v>0.5132916247742721</v>
       </c>
       <c r="C500" t="n">
-        <v>0.1162527508097197</v>
+        <v>0.5180870754856077</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>54149</v>
+        <v>54131</v>
       </c>
       <c r="B501" t="n">
-        <v>0.5132916247742721</v>
+        <v>0.2889652986472018</v>
       </c>
       <c r="C501" t="n">
-        <v>0.5180870754856077</v>
+        <v>0.0977610661696833</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>54131</v>
+        <v>54114</v>
       </c>
       <c r="B502" t="n">
-        <v>0.2889652986472018</v>
+        <v>0.4249256844106838</v>
       </c>
       <c r="C502" t="n">
-        <v>0.0977610661696833</v>
+        <v>0.1842022498053335</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>54114</v>
+        <v>54099</v>
       </c>
       <c r="B503" t="n">
-        <v>0.4249256844106838</v>
+        <v>0.1813711832428597</v>
       </c>
       <c r="C503" t="n">
-        <v>0.1842022498053335</v>
+        <v>0.08324420409254858</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>54099</v>
+        <v>54096</v>
       </c>
       <c r="B504" t="n">
-        <v>0.1813711832428597</v>
+        <v>0.3917201416119265</v>
       </c>
       <c r="C504" t="n">
-        <v>0.08324420409254858</v>
+        <v>0.1720061789473381</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>54096</v>
+        <v>54081</v>
       </c>
       <c r="B505" t="n">
-        <v>0.3917801316366308</v>
+        <v>0.2074718844271447</v>
       </c>
       <c r="C505" t="n">
-        <v>0.1720163740800255</v>
+        <v>0.1664786149734753</v>
       </c>
     </row>
     <row r="506">
@@ -6035,607 +6035,607 @@
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>52176</v>
+        <v>52193</v>
       </c>
       <c r="B510" t="n">
-        <v>0.3760395306362695</v>
+        <v>0.2759392619982804</v>
       </c>
       <c r="C510" t="n">
-        <v>0.1505576716551372</v>
+        <v>0.2846721642795024</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>52168</v>
+        <v>52176</v>
       </c>
       <c r="B511" t="n">
-        <v>0.6049910102642932</v>
+        <v>0.3760395306362695</v>
       </c>
       <c r="C511" t="n">
-        <v>0.05781173190270094</v>
+        <v>0.1505576716551372</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>52149</v>
+        <v>52168</v>
       </c>
       <c r="B512" t="n">
-        <v>0.2757565578470069</v>
+        <v>0.6050330506345066</v>
       </c>
       <c r="C512" t="n">
-        <v>0.2348794646741324</v>
+        <v>0.05878222915609287</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>52088</v>
+        <v>52149</v>
       </c>
       <c r="B513" t="n">
-        <v>0.4682489533924946</v>
+        <v>0.2757565578470069</v>
       </c>
       <c r="C513" t="n">
-        <v>0.4693598721569915</v>
+        <v>0.2348794646741324</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>52087</v>
+        <v>52088</v>
       </c>
       <c r="B514" t="n">
-        <v>0.2809251099854099</v>
+        <v>0.4682489533924946</v>
       </c>
       <c r="C514" t="n">
-        <v>0.2636292512618233</v>
+        <v>0.4693598721569915</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>52056</v>
+        <v>52087</v>
       </c>
       <c r="B515" t="n">
-        <v>0.291924187765657</v>
+        <v>0.2809251099854099</v>
       </c>
       <c r="C515" t="n">
-        <v>0.1398811423811004</v>
+        <v>0.2636292512618233</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>52026</v>
+        <v>52056</v>
       </c>
       <c r="B516" t="n">
-        <v>0.4378969828910325</v>
+        <v>0.291924187765657</v>
       </c>
       <c r="C516" t="n">
-        <v>0.1396828469630562</v>
+        <v>0.1398811423811004</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>52019</v>
+        <v>52026</v>
       </c>
       <c r="B517" t="n">
-        <v>0.3920419865911501</v>
+        <v>0.4378969828910325</v>
       </c>
       <c r="C517" t="n">
-        <v>0.3432349854382034</v>
+        <v>0.1396828469630562</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>51030</v>
+        <v>52019</v>
       </c>
       <c r="B518" t="n">
-        <v>0.2988507603050974</v>
+        <v>0.3920419865911501</v>
       </c>
       <c r="C518" t="n">
-        <v>0.1829664156882185</v>
+        <v>0.3432349854382034</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>50978</v>
+        <v>51030</v>
       </c>
       <c r="B519" t="n">
-        <v>0.2944359588931713</v>
+        <v>0.2988507603050974</v>
       </c>
       <c r="C519" t="n">
-        <v>0.1629688988575661</v>
+        <v>0.1829664156882185</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>50974</v>
+        <v>50978</v>
       </c>
       <c r="B520" t="n">
-        <v>0.5556422391456203</v>
+        <v>0.2944359588931713</v>
       </c>
       <c r="C520" t="n">
-        <v>0.2552642678008697</v>
+        <v>0.1629688988575661</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>50956</v>
+        <v>50974</v>
       </c>
       <c r="B521" t="n">
-        <v>0.3215880919584869</v>
+        <v>0.2706221782173364</v>
       </c>
       <c r="C521" t="n">
-        <v>0.1786418269238361</v>
+        <v>0.1829911273914785</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>50949</v>
+        <v>50956</v>
       </c>
       <c r="B522" t="n">
-        <v>0.4304710016078944</v>
+        <v>0.1602265856195124</v>
       </c>
       <c r="C522" t="n">
-        <v>0.2576457083385465</v>
+        <v>0.1189153943464306</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>50900</v>
+        <v>50949</v>
       </c>
       <c r="B523" t="n">
         <v>0.4304710016078944</v>
       </c>
       <c r="C523" t="n">
-        <v>0.6037504894176957</v>
+        <v>0.2576457083385465</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>50888</v>
+        <v>50900</v>
       </c>
       <c r="B524" t="n">
-        <v>0.4349765649084052</v>
+        <v>0.3975377187560111</v>
       </c>
       <c r="C524" t="n">
-        <v>0.2722037614779731</v>
+        <v>0.3037442529610638</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>50865</v>
+        <v>50888</v>
       </c>
       <c r="B525" t="n">
-        <v>0.2583966430423923</v>
+        <v>0.4349765649084052</v>
       </c>
       <c r="C525" t="n">
-        <v>0.2621277440820914</v>
+        <v>0.2722037614779731</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>50835</v>
+        <v>50865</v>
       </c>
       <c r="B526" t="n">
-        <v>0.5664789324249264</v>
+        <v>0.2583966430423923</v>
       </c>
       <c r="C526" t="n">
-        <v>0.1563697322328185</v>
+        <v>0.2621277440820914</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>50815</v>
+        <v>50835</v>
       </c>
       <c r="B527" t="n">
-        <v>0.3539194898910987</v>
+        <v>0.3256899481170822</v>
       </c>
       <c r="C527" t="n">
-        <v>0.3513827286284792</v>
+        <v>0.1304980258741255</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>50799</v>
+        <v>50815</v>
       </c>
       <c r="B528" t="n">
-        <v>0.3687838443026349</v>
+        <v>0.3539194898910987</v>
       </c>
       <c r="C528" t="n">
-        <v>0.2125797733595964</v>
+        <v>0.3513827286284792</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>50776</v>
+        <v>50799</v>
       </c>
       <c r="B529" t="n">
-        <v>0.7364146092395814</v>
+        <v>0.3687838443026349</v>
       </c>
       <c r="C529" t="n">
-        <v>0.2198559091191267</v>
+        <v>0.2125797733595964</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>50744</v>
+        <v>50776</v>
       </c>
       <c r="B530" t="n">
-        <v>0.3394646625991539</v>
+        <v>0.5042250982629406</v>
       </c>
       <c r="C530" t="n">
-        <v>0.2139449293826964</v>
+        <v>0.2141531953847354</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>50732</v>
+        <v>50744</v>
       </c>
       <c r="B531" t="n">
-        <v>0.4125014035535375</v>
+        <v>0.3394646625991539</v>
       </c>
       <c r="C531" t="n">
-        <v>0.3792135390031374</v>
+        <v>0.2139449293826964</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>50729</v>
+        <v>50733</v>
       </c>
       <c r="B532" t="n">
-        <v>0.2017033029073844</v>
+        <v>0.1840443724642797</v>
       </c>
       <c r="C532" t="n">
-        <v>0.1906944236855855</v>
+        <v>0.1654240033943302</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>50707</v>
+        <v>50732</v>
       </c>
       <c r="B533" t="n">
-        <v>0.378530132477527</v>
+        <v>0.1391506972720696</v>
       </c>
       <c r="C533" t="n">
-        <v>0.3144873677958836</v>
+        <v>0.1163727642978764</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>50625</v>
+        <v>50729</v>
       </c>
       <c r="B534" t="n">
-        <v>0.5057787977472922</v>
+        <v>0.07159097071330502</v>
       </c>
       <c r="C534" t="n">
-        <v>0.5023209779099194</v>
+        <v>0.07014480242132962</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>50612</v>
+        <v>50707</v>
       </c>
       <c r="B535" t="n">
-        <v>0.3724619709352441</v>
+        <v>0.378530132477527</v>
       </c>
       <c r="C535" t="n">
-        <v>0.3760483182704746</v>
+        <v>0.3144873677958836</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>50611</v>
+        <v>50625</v>
       </c>
       <c r="B536" t="n">
-        <v>0.2055121923101276</v>
+        <v>0.5057787977472922</v>
       </c>
       <c r="C536" t="n">
-        <v>0.06501206617036688</v>
+        <v>0.5023209779099194</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>50561</v>
+        <v>50612</v>
       </c>
       <c r="B537" t="n">
-        <v>0.473850330222901</v>
+        <v>0.3724619709352441</v>
       </c>
       <c r="C537" t="n">
-        <v>0.4332832077642954</v>
+        <v>0.3760483182704746</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>50558</v>
+        <v>50611</v>
       </c>
       <c r="B538" t="n">
-        <v>0.4247457837541009</v>
+        <v>0.2055121923101276</v>
       </c>
       <c r="C538" t="n">
-        <v>0.1271322940466076</v>
+        <v>0.06501206617036688</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>50555</v>
+        <v>50561</v>
       </c>
       <c r="B539" t="n">
-        <v>0.2764197975977523</v>
+        <v>0.473850330222901</v>
       </c>
       <c r="C539" t="n">
-        <v>0.2275047305833693</v>
+        <v>0.4332832077642954</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>50491</v>
+        <v>50558</v>
       </c>
       <c r="B540" t="n">
-        <v>0.4494703814440995</v>
+        <v>0.4247457837541009</v>
       </c>
       <c r="C540" t="n">
-        <v>0.3723198397866629</v>
+        <v>0.1271322940466076</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>50472</v>
+        <v>50555</v>
       </c>
       <c r="B541" t="n">
-        <v>0.6315984681409896</v>
+        <v>0.2764197975977523</v>
       </c>
       <c r="C541" t="n">
-        <v>0.5267936972455606</v>
+        <v>0.2275047305833693</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>50463</v>
+        <v>50491</v>
       </c>
       <c r="B542" t="n">
-        <v>0.3786579835985342</v>
+        <v>0.2494877334397422</v>
       </c>
       <c r="C542" t="n">
-        <v>0.3453427837709925</v>
+        <v>0.1761629247894256</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>50458</v>
+        <v>50472</v>
       </c>
       <c r="B543" t="n">
-        <v>0.4303523047193825</v>
+        <v>0.6315984681409896</v>
       </c>
       <c r="C543" t="n">
-        <v>0.1677109919136181</v>
+        <v>0.5267936972455606</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>50451</v>
+        <v>50463</v>
       </c>
       <c r="B544" t="n">
-        <v>0.3751731571758846</v>
+        <v>0.3786579835985342</v>
       </c>
       <c r="C544" t="n">
-        <v>0.1068863673328224</v>
+        <v>0.3453427837709925</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>50450</v>
+        <v>50458</v>
       </c>
       <c r="B545" t="n">
-        <v>0.3989663324084597</v>
+        <v>0.4303523047193825</v>
       </c>
       <c r="C545" t="n">
-        <v>0.4033823203514878</v>
+        <v>0.1677109919136181</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>50449</v>
+        <v>50451</v>
       </c>
       <c r="B546" t="n">
-        <v>0.3772787882490992</v>
+        <v>0.3751731571758846</v>
       </c>
       <c r="C546" t="n">
-        <v>0.1225989472056124</v>
+        <v>0.1068863673328224</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>50397</v>
+        <v>50450</v>
       </c>
       <c r="B547" t="n">
-        <v>0.7638745124569666</v>
+        <v>0.3989663324084597</v>
       </c>
       <c r="C547" t="n">
-        <v>0.7758515425174501</v>
+        <v>0.4033823203514878</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>50385</v>
+        <v>50449</v>
       </c>
       <c r="B548" t="n">
-        <v>0.4128644139552782</v>
+        <v>0.3772787882490992</v>
       </c>
       <c r="C548" t="n">
-        <v>0.2641450222168226</v>
+        <v>0.1225989472056124</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>50368</v>
+        <v>50397</v>
       </c>
       <c r="B549" t="n">
-        <v>0.3507461865301054</v>
+        <v>0.4602449380269448</v>
       </c>
       <c r="C549" t="n">
-        <v>0.3549010066594801</v>
+        <v>0.6244710296620412</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>50296</v>
+        <v>50385</v>
       </c>
       <c r="B550" t="n">
-        <v>0.5706211734796507</v>
+        <v>0.4128644139552782</v>
       </c>
       <c r="C550" t="n">
-        <v>0.3476125124647472</v>
+        <v>0.2641450222168226</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>50292</v>
+        <v>50368</v>
       </c>
       <c r="B551" t="n">
-        <v>0.4120087906479347</v>
+        <v>0.2171654024632724</v>
       </c>
       <c r="C551" t="n">
-        <v>0.3365553173454073</v>
+        <v>0.1375320713163049</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>50279</v>
+        <v>50296</v>
       </c>
       <c r="B552" t="n">
-        <v>0.3486122079810578</v>
+        <v>0.5706211734796507</v>
       </c>
       <c r="C552" t="n">
-        <v>0.2779113381753101</v>
+        <v>0.3476125124647472</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>50240</v>
+        <v>50292</v>
       </c>
       <c r="B553" t="n">
-        <v>0.345290391773289</v>
+        <v>0.4120087906479347</v>
       </c>
       <c r="C553" t="n">
-        <v>0.3261093345263977</v>
+        <v>0.3365553173454073</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>50109</v>
+        <v>50279</v>
       </c>
       <c r="B554" t="n">
-        <v>0.4075283815803284</v>
+        <v>0.3486122079810578</v>
       </c>
       <c r="C554" t="n">
-        <v>0.1828273883893078</v>
+        <v>0.2779113381753101</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>50006</v>
+        <v>50240</v>
       </c>
       <c r="B555" t="n">
-        <v>0.5427200914535585</v>
+        <v>0.1023279212173438</v>
       </c>
       <c r="C555" t="n">
-        <v>0.4950759776207879</v>
+        <v>0.08529140012060682</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>50002</v>
+        <v>50109</v>
       </c>
       <c r="B556" t="n">
-        <v>0.2972649074512224</v>
+        <v>0.4075283815803284</v>
       </c>
       <c r="C556" t="n">
-        <v>0.1698227676068577</v>
+        <v>0.1828273883893078</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>10870</v>
+        <v>50006</v>
       </c>
       <c r="B557" t="n">
-        <v>0.2990023950190672</v>
+        <v>0.5427200914535585</v>
       </c>
       <c r="C557" t="n">
-        <v>0.2055379846927555</v>
+        <v>0.4950759776207879</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>10867</v>
+        <v>50002</v>
       </c>
       <c r="B558" t="n">
-        <v>0.5825292643183621</v>
+        <v>0.2972649074512224</v>
       </c>
       <c r="C558" t="n">
-        <v>0.6172313011074074</v>
+        <v>0.1698227676068577</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>10866</v>
+        <v>10870</v>
       </c>
       <c r="B559" t="n">
-        <v>0.6184896992909699</v>
+        <v>0.2990023950190672</v>
       </c>
       <c r="C559" t="n">
-        <v>0.5792063129061953</v>
+        <v>0.2055379846927555</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>10822</v>
+        <v>10867</v>
       </c>
       <c r="B560" t="n">
-        <v>0.1943001046092285</v>
+        <v>0.2137840774050754</v>
       </c>
       <c r="C560" t="n">
-        <v>0.06703268223150197</v>
+        <v>0.0394274135050201</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>10805</v>
+        <v>10866</v>
       </c>
       <c r="B561" t="n">
-        <v>0.3117295282427174</v>
+        <v>0.3091467412253826</v>
       </c>
       <c r="C561" t="n">
-        <v>0.2001613720346193</v>
+        <v>0.3092146473605172</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>10776</v>
+        <v>10822</v>
       </c>
       <c r="B562" t="n">
-        <v>0.2570013757900979</v>
+        <v>0.1943001046092285</v>
       </c>
       <c r="C562" t="n">
-        <v>0.05046557632641901</v>
+        <v>0.06703268223150197</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>10774</v>
+        <v>10805</v>
       </c>
       <c r="B563" t="n">
-        <v>0.8129330469166055</v>
+        <v>0.3117295282427174</v>
       </c>
       <c r="C563" t="n">
-        <v>0.2785523810563296</v>
+        <v>0.2001613720346193</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>10771</v>
+        <v>10776</v>
       </c>
       <c r="B564" t="n">
-        <v>0.6299211659037645</v>
+        <v>0.2570013757900979</v>
       </c>
       <c r="C564" t="n">
-        <v>0.3739532784695855</v>
+        <v>0.05046557632641901</v>
       </c>
     </row>
     <row r="565">
@@ -6665,6565 +6665,6785 @@
         <v>10745</v>
       </c>
       <c r="B567" t="n">
-        <v>0.3275516299758444</v>
+        <v>0.3275456154898435</v>
       </c>
       <c r="C567" t="n">
-        <v>0.2486866677257126</v>
+        <v>0.2486915012621301</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>10743</v>
+        <v>10726</v>
       </c>
       <c r="B568" t="n">
-        <v>0.7784285515341615</v>
+        <v>0.3123953246782417</v>
       </c>
       <c r="C568" t="n">
-        <v>0.05076899741415881</v>
+        <v>0.1941453923681501</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>10726</v>
+        <v>10725</v>
       </c>
       <c r="B569" t="n">
-        <v>0.3123953246782417</v>
+        <v>0.4391890847142154</v>
       </c>
       <c r="C569" t="n">
-        <v>0.1941453923681501</v>
+        <v>0.4244562645505815</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>10725</v>
+        <v>10682</v>
       </c>
       <c r="B570" t="n">
-        <v>0.4391890847142154</v>
+        <v>0.4555541360324639</v>
       </c>
       <c r="C570" t="n">
-        <v>0.4244562645505815</v>
+        <v>0.212187088834951</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>10682</v>
+        <v>10678</v>
       </c>
       <c r="B571" t="n">
-        <v>0.4555541360324639</v>
+        <v>0.2893417485373901</v>
       </c>
       <c r="C571" t="n">
-        <v>0.212187088834951</v>
+        <v>0.09778841155574958</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>10678</v>
+        <v>10650</v>
       </c>
       <c r="B572" t="n">
-        <v>0.2893417485373901</v>
+        <v>0.5557420852732056</v>
       </c>
       <c r="C572" t="n">
-        <v>0.09778841155574958</v>
+        <v>0.5665601136343985</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>10650</v>
+        <v>10649</v>
       </c>
       <c r="B573" t="n">
-        <v>0.5557420852732056</v>
+        <v>0.3767102340901913</v>
       </c>
       <c r="C573" t="n">
-        <v>0.5665601136343985</v>
+        <v>0.378640404653146</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>10649</v>
+        <v>10621</v>
       </c>
       <c r="B574" t="n">
-        <v>0.3767102340901913</v>
+        <v>0.454630794811666</v>
       </c>
       <c r="C574" t="n">
-        <v>0.378640404653146</v>
+        <v>0.451991435290739</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>10621</v>
+        <v>10620</v>
       </c>
       <c r="B575" t="n">
-        <v>0.454630794811666</v>
+        <v>0.401105323362954</v>
       </c>
       <c r="C575" t="n">
-        <v>0.451991435290739</v>
+        <v>0.4181999805330461</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>10620</v>
+        <v>10619</v>
       </c>
       <c r="B576" t="n">
-        <v>0.401105323362954</v>
+        <v>0.4591503005584441</v>
       </c>
       <c r="C576" t="n">
-        <v>0.4181999805330461</v>
+        <v>0.4589976387564254</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>10619</v>
+        <v>10617</v>
       </c>
       <c r="B577" t="n">
-        <v>0.4591503005584441</v>
+        <v>0.4531370626490013</v>
       </c>
       <c r="C577" t="n">
-        <v>0.4589976387564254</v>
+        <v>0.2192615983939237</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>10617</v>
+        <v>10603</v>
       </c>
       <c r="B578" t="n">
-        <v>0.4531370626490013</v>
+        <v>0.3311914635364891</v>
       </c>
       <c r="C578" t="n">
-        <v>0.2192615983939237</v>
+        <v>0.1482765310626272</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>10603</v>
+        <v>10567</v>
       </c>
       <c r="B579" t="n">
-        <v>0.3311914635364891</v>
+        <v>0.3069702437358044</v>
       </c>
       <c r="C579" t="n">
-        <v>0.1482765310626272</v>
+        <v>0.2028704263493739</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>10567</v>
+        <v>10566</v>
       </c>
       <c r="B580" t="n">
-        <v>0.3069702437358044</v>
+        <v>0.3172391937951577</v>
       </c>
       <c r="C580" t="n">
-        <v>0.2028704263493739</v>
+        <v>0.2401433838366319</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>10566</v>
+        <v>10525</v>
       </c>
       <c r="B581" t="n">
-        <v>0.5686356493218818</v>
+        <v>0.2560244971971203</v>
       </c>
       <c r="C581" t="n">
-        <v>0.4430549504416021</v>
+        <v>0.03451693897827137</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>10525</v>
+        <v>10405</v>
       </c>
       <c r="B582" t="n">
-        <v>0.2560244971971203</v>
+        <v>0.3013292187202166</v>
       </c>
       <c r="C582" t="n">
-        <v>0.03451693897827137</v>
+        <v>0.2360334867021623</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>10464</v>
+        <v>10349</v>
       </c>
       <c r="B583" t="n">
-        <v>0.4827123078507166</v>
+        <v>0.3630654154070135</v>
       </c>
       <c r="C583" t="n">
-        <v>0.2168592749508027</v>
+        <v>0.3660378864913306</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>10405</v>
+        <v>10343</v>
       </c>
       <c r="B584" t="n">
-        <v>0.3013292187202166</v>
+        <v>0.19471209942379</v>
       </c>
       <c r="C584" t="n">
-        <v>0.2360334867021623</v>
+        <v>0.05333866379241745</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>10379</v>
+        <v>10328</v>
       </c>
       <c r="B585" t="n">
-        <v>1.462377251494974</v>
+        <v>0.2154203342869591</v>
       </c>
       <c r="C585" t="n">
-        <v>0.143114986595665</v>
+        <v>0.2154890570285991</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>10349</v>
+        <v>10308</v>
       </c>
       <c r="B586" t="n">
-        <v>0.3630654154070135</v>
+        <v>0.4341584313931149</v>
       </c>
       <c r="C586" t="n">
-        <v>0.3660378864913306</v>
+        <v>0.2214717768777134</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>10343</v>
+        <v>10307</v>
       </c>
       <c r="B587" t="n">
-        <v>0.19471209942379</v>
+        <v>0.3566575968699111</v>
       </c>
       <c r="C587" t="n">
-        <v>0.05333866379241745</v>
+        <v>0.1897911074164836</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>10328</v>
+        <v>10298</v>
       </c>
       <c r="B588" t="n">
-        <v>0.7520014296398777</v>
+        <v>0.3348731291054095</v>
       </c>
       <c r="C588" t="n">
-        <v>0.7349441939477475</v>
+        <v>0.2110703209791583</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>10308</v>
+        <v>10294</v>
       </c>
       <c r="B589" t="n">
-        <v>0.4341584313931149</v>
+        <v>0.4294248121135393</v>
       </c>
       <c r="C589" t="n">
-        <v>0.2214717768777134</v>
+        <v>0.1221582784694287</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>10307</v>
+        <v>10244</v>
       </c>
       <c r="B590" t="n">
-        <v>0.3566575968699111</v>
+        <v>0.300539459165282</v>
       </c>
       <c r="C590" t="n">
-        <v>0.1897911074164836</v>
+        <v>0.2931290692915857</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>10298</v>
+        <v>10190</v>
       </c>
       <c r="B591" t="n">
-        <v>0.3348731291054095</v>
+        <v>0.3827011561733407</v>
       </c>
       <c r="C591" t="n">
-        <v>0.2110703209791583</v>
+        <v>0.3710198964150494</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>10294</v>
+        <v>10169</v>
       </c>
       <c r="B592" t="n">
-        <v>0.4288697255577224</v>
+        <v>0.4206119629873609</v>
       </c>
       <c r="C592" t="n">
-        <v>0.122089184343032</v>
+        <v>0.2040344762386311</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>10190</v>
+        <v>10156</v>
       </c>
       <c r="B593" t="n">
-        <v>0.3827011561733407</v>
+        <v>0.3811666445467506</v>
       </c>
       <c r="C593" t="n">
-        <v>0.3710198964150494</v>
+        <v>0.1776819517267768</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>10169</v>
+        <v>10143</v>
       </c>
       <c r="B594" t="n">
-        <v>0.4206119629873609</v>
+        <v>0.3030647748623956</v>
       </c>
       <c r="C594" t="n">
-        <v>0.2040344762386311</v>
+        <v>0.05912791041528032</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>10156</v>
+        <v>10113</v>
       </c>
       <c r="B595" t="n">
-        <v>0.3811666445467506</v>
+        <v>0.1922764149267586</v>
       </c>
       <c r="C595" t="n">
-        <v>0.1776819517267768</v>
+        <v>0.1571118346757607</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>10143</v>
+        <v>10099</v>
       </c>
       <c r="B596" t="n">
-        <v>0.3030647748623956</v>
+        <v>0.4241189563393574</v>
       </c>
       <c r="C596" t="n">
-        <v>0.05912791041528032</v>
+        <v>0.4159636743122511</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>10113</v>
+        <v>10043</v>
       </c>
       <c r="B597" t="n">
-        <v>0.6172821804313822</v>
+        <v>0.3157936778230006</v>
       </c>
       <c r="C597" t="n">
-        <v>0.2865195253058209</v>
+        <v>0.1464149310591135</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>10099</v>
+        <v>10034</v>
       </c>
       <c r="B598" t="n">
-        <v>0.4241189563393574</v>
+        <v>0.4256553509785937</v>
       </c>
       <c r="C598" t="n">
-        <v>0.4159636743122511</v>
+        <v>0.2415294714510685</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>10043</v>
+        <v>10030</v>
       </c>
       <c r="B599" t="n">
-        <v>0.3157936778230006</v>
+        <v>0.395208067604207</v>
       </c>
       <c r="C599" t="n">
-        <v>0.1464149310591135</v>
+        <v>0.280567973609415</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>10034</v>
+        <v>10017</v>
       </c>
       <c r="B600" t="n">
-        <v>0.4256553509785937</v>
+        <v>0.5274512988216579</v>
       </c>
       <c r="C600" t="n">
-        <v>0.2415294714510685</v>
+        <v>0.5315192496782379</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>10030</v>
+        <v>8906</v>
       </c>
       <c r="B601" t="n">
-        <v>0.395208067604207</v>
+        <v>0.6953125741637103</v>
       </c>
       <c r="C601" t="n">
-        <v>0.280567973609415</v>
+        <v>0.4220880597728315</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>10017</v>
+        <v>8226</v>
       </c>
       <c r="B602" t="n">
-        <v>0.5274512988216579</v>
+        <v>0.3653118021838609</v>
       </c>
       <c r="C602" t="n">
-        <v>0.5315192496782379</v>
+        <v>0.1524920242924817</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>8906</v>
+        <v>8224</v>
       </c>
       <c r="B603" t="n">
-        <v>0.6953125741637103</v>
+        <v>0.3747894962628129</v>
       </c>
       <c r="C603" t="n">
-        <v>0.4220880597728315</v>
+        <v>0.2605442064114544</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>8226</v>
+        <v>8222</v>
       </c>
       <c r="B604" t="n">
-        <v>0.3653118021838609</v>
+        <v>0.3331609963310331</v>
       </c>
       <c r="C604" t="n">
-        <v>0.1524920242924817</v>
+        <v>0.119860545391513</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>8224</v>
+        <v>8219</v>
       </c>
       <c r="B605" t="n">
-        <v>0.3747894962628129</v>
+        <v>0.3727710616767546</v>
       </c>
       <c r="C605" t="n">
-        <v>0.2605442064114544</v>
+        <v>0.2712614751820708</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>8222</v>
+        <v>8102</v>
       </c>
       <c r="B606" t="n">
-        <v>0.3331609963310331</v>
+        <v>0.3757268206827413</v>
       </c>
       <c r="C606" t="n">
-        <v>0.119860545391513</v>
+        <v>0.2107950407283304</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
-        <v>8219</v>
+        <v>8069</v>
       </c>
       <c r="B607" t="n">
-        <v>0.3727710616767546</v>
+        <v>0.3515489745398354</v>
       </c>
       <c r="C607" t="n">
-        <v>0.2712614751820708</v>
+        <v>0.303294864373161</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>8102</v>
+        <v>8068</v>
       </c>
       <c r="B608" t="n">
-        <v>0.3757268206827413</v>
+        <v>0.4852632241553132</v>
       </c>
       <c r="C608" t="n">
-        <v>0.2107950407283304</v>
+        <v>0.3246612708715699</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
-        <v>8069</v>
+        <v>8066</v>
       </c>
       <c r="B609" t="n">
-        <v>0.3515489745398354</v>
+        <v>0.3455144250036168</v>
       </c>
       <c r="C609" t="n">
-        <v>0.303294864373161</v>
+        <v>0.2570037132542499</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>8068</v>
+        <v>8063</v>
       </c>
       <c r="B610" t="n">
-        <v>0.4852632241553132</v>
+        <v>0.3065318338976682</v>
       </c>
       <c r="C610" t="n">
-        <v>0.3246612708715699</v>
+        <v>0.2352108701763784</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>8066</v>
+        <v>8059</v>
       </c>
       <c r="B611" t="n">
-        <v>0.3455144250036168</v>
+        <v>0.3312794343920738</v>
       </c>
       <c r="C611" t="n">
-        <v>0.2570037132542499</v>
+        <v>0.1672669901324101</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>8063</v>
+        <v>8056</v>
       </c>
       <c r="B612" t="n">
-        <v>0.3065318338976682</v>
+        <v>0.3351531347903499</v>
       </c>
       <c r="C612" t="n">
-        <v>0.2352108701763784</v>
+        <v>0.2531505811945315</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
-        <v>8059</v>
+        <v>8054</v>
       </c>
       <c r="B613" t="n">
-        <v>0.3312794343920738</v>
+        <v>0.3403544146083436</v>
       </c>
       <c r="C613" t="n">
-        <v>0.1672669901324101</v>
+        <v>0.1155358082824752</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>8056</v>
+        <v>8053</v>
       </c>
       <c r="B614" t="n">
-        <v>0.3351531347903499</v>
+        <v>0.336496738745494</v>
       </c>
       <c r="C614" t="n">
-        <v>0.2531505811945315</v>
+        <v>0.3396520725221175</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>8054</v>
+        <v>8049</v>
       </c>
       <c r="B615" t="n">
-        <v>0.3403544146083436</v>
+        <v>0.2810005631973558</v>
       </c>
       <c r="C615" t="n">
-        <v>0.1155358082824752</v>
+        <v>0.2546502689888163</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>8053</v>
+        <v>8048</v>
       </c>
       <c r="B616" t="n">
-        <v>0.336496738745494</v>
+        <v>0.3451469005182279</v>
       </c>
       <c r="C616" t="n">
-        <v>0.3396520725221175</v>
+        <v>0.2690802888387572</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>8049</v>
+        <v>8042</v>
       </c>
       <c r="B617" t="n">
-        <v>0.2810005631973558</v>
+        <v>0.398074518918294</v>
       </c>
       <c r="C617" t="n">
-        <v>0.2546502689888163</v>
+        <v>0.2443321857452343</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>8048</v>
+        <v>8037</v>
       </c>
       <c r="B618" t="n">
-        <v>0.3451469005182279</v>
+        <v>0.2606563371998817</v>
       </c>
       <c r="C618" t="n">
-        <v>0.2690802888387572</v>
+        <v>0.07890602695439165</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>8042</v>
+        <v>8031</v>
       </c>
       <c r="B619" t="n">
-        <v>0.398074518918294</v>
+        <v>0.4745235285539328</v>
       </c>
       <c r="C619" t="n">
-        <v>0.2443321857452343</v>
+        <v>0.1944417437627035</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>8037</v>
+        <v>8029</v>
       </c>
       <c r="B620" t="n">
-        <v>0.2606563371998817</v>
+        <v>0.2414857096691129</v>
       </c>
       <c r="C620" t="n">
-        <v>0.07890602695439165</v>
+        <v>0.09607783449066051</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>8031</v>
+        <v>8027</v>
       </c>
       <c r="B621" t="n">
-        <v>0.4745235285539328</v>
+        <v>0.2981598555454822</v>
       </c>
       <c r="C621" t="n">
-        <v>0.1944417437627035</v>
+        <v>0.1906227882569803</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>8029</v>
+        <v>8023</v>
       </c>
       <c r="B622" t="n">
-        <v>0.2414857096691129</v>
+        <v>0.3330095584966227</v>
       </c>
       <c r="C622" t="n">
-        <v>0.09607783449066051</v>
+        <v>0.2692885661641626</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>8027</v>
+        <v>8008</v>
       </c>
       <c r="B623" t="n">
-        <v>0.2981598555454822</v>
+        <v>0.1499587276431306</v>
       </c>
       <c r="C623" t="n">
-        <v>0.1906227882569803</v>
+        <v>0.01738955801380378</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>8023</v>
+        <v>8007</v>
       </c>
       <c r="B624" t="n">
-        <v>0.3330095584966227</v>
+        <v>0.2611105558121956</v>
       </c>
       <c r="C624" t="n">
-        <v>0.2692885661641626</v>
+        <v>0.2589823790122756</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>8008</v>
+        <v>8006</v>
       </c>
       <c r="B625" t="n">
-        <v>0.1499587276431306</v>
+        <v>0.3696870700716044</v>
       </c>
       <c r="C625" t="n">
-        <v>0.01738955801380378</v>
+        <v>0.2550575377590834</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>8007</v>
+        <v>8002</v>
       </c>
       <c r="B626" t="n">
-        <v>0.2611105558121956</v>
+        <v>0.3215434972737941</v>
       </c>
       <c r="C626" t="n">
-        <v>0.2589823790122756</v>
+        <v>0.1550898353172853</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>8006</v>
+        <v>8000</v>
       </c>
       <c r="B627" t="n">
-        <v>0.3696870700716044</v>
+        <v>0.4118396141193378</v>
       </c>
       <c r="C627" t="n">
-        <v>0.2550575377590834</v>
+        <v>0.1441762205686311</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>8002</v>
+        <v>7999</v>
       </c>
       <c r="B628" t="n">
-        <v>0.3215434972737941</v>
+        <v>0.504262763935304</v>
       </c>
       <c r="C628" t="n">
-        <v>0.1550898353172853</v>
+        <v>0.200837494327848</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>8000</v>
+        <v>7991</v>
       </c>
       <c r="B629" t="n">
-        <v>0.4118396141193378</v>
+        <v>0.4341391833927904</v>
       </c>
       <c r="C629" t="n">
-        <v>0.1441762205686311</v>
+        <v>0.1531557143593084</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
-        <v>7999</v>
+        <v>7989</v>
       </c>
       <c r="B630" t="n">
-        <v>0.504262763935304</v>
+        <v>0.3544441957060059</v>
       </c>
       <c r="C630" t="n">
-        <v>0.200837494327848</v>
+        <v>0.3496694026630111</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
-        <v>7991</v>
+        <v>7988</v>
       </c>
       <c r="B631" t="n">
-        <v>0.4341391833927904</v>
+        <v>0.3421726854164923</v>
       </c>
       <c r="C631" t="n">
-        <v>0.1531557143593084</v>
+        <v>0.09660703248394664</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
-        <v>7989</v>
+        <v>7987</v>
       </c>
       <c r="B632" t="n">
-        <v>0.3544441957060059</v>
+        <v>0.3603853066963003</v>
       </c>
       <c r="C632" t="n">
-        <v>0.3496694026630111</v>
+        <v>0.2086753279793638</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="n">
-        <v>7988</v>
+        <v>7985</v>
       </c>
       <c r="B633" t="n">
-        <v>0.3421726854164923</v>
+        <v>0.3304770085832602</v>
       </c>
       <c r="C633" t="n">
-        <v>0.09660703248394664</v>
+        <v>0.1844730152284585</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
-        <v>7987</v>
+        <v>7984</v>
       </c>
       <c r="B634" t="n">
-        <v>0.3603853066963003</v>
+        <v>0.3666780572721746</v>
       </c>
       <c r="C634" t="n">
-        <v>0.2086753279793638</v>
+        <v>0.3357901228868675</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="n">
-        <v>7985</v>
+        <v>7981</v>
       </c>
       <c r="B635" t="n">
-        <v>0.3304770085832602</v>
+        <v>0.2989422513727468</v>
       </c>
       <c r="C635" t="n">
-        <v>0.1844730152284585</v>
+        <v>0.2761324102446012</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>7984</v>
+        <v>7975</v>
       </c>
       <c r="B636" t="n">
-        <v>0.3666780572721746</v>
+        <v>0.3867458392164843</v>
       </c>
       <c r="C636" t="n">
-        <v>0.3357901228868675</v>
+        <v>0.2705977848692995</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
-        <v>7981</v>
+        <v>7972</v>
       </c>
       <c r="B637" t="n">
-        <v>0.2989422513727468</v>
+        <v>0.2797116096677786</v>
       </c>
       <c r="C637" t="n">
-        <v>0.2761324102446012</v>
+        <v>0.2831923560801178</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="B638" t="n">
-        <v>0.3867458392164843</v>
+        <v>0.3495100091599342</v>
       </c>
       <c r="C638" t="n">
-        <v>0.2705977848692995</v>
+        <v>0.2133895957990492</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>7972</v>
+        <v>7964</v>
       </c>
       <c r="B639" t="n">
-        <v>0.2797116096677786</v>
+        <v>0.3243481755641284</v>
       </c>
       <c r="C639" t="n">
-        <v>0.2831923560801178</v>
+        <v>0.2960360218914083</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>7967</v>
+        <v>7962</v>
       </c>
       <c r="B640" t="n">
-        <v>0.3495100091599342</v>
+        <v>0.3524070977414397</v>
       </c>
       <c r="C640" t="n">
-        <v>0.2133895957990492</v>
+        <v>0.109122915427052</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
-        <v>7964</v>
+        <v>7960</v>
       </c>
       <c r="B641" t="n">
-        <v>0.3243481755641284</v>
+        <v>0.2896603303236049</v>
       </c>
       <c r="C641" t="n">
-        <v>0.2960360218914083</v>
+        <v>0.2776166862810381</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="n">
-        <v>7962</v>
+        <v>7953</v>
       </c>
       <c r="B642" t="n">
-        <v>0.3524070977414397</v>
+        <v>0.3311073757355821</v>
       </c>
       <c r="C642" t="n">
-        <v>0.109122915427052</v>
+        <v>0.242618124008679</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="n">
-        <v>7960</v>
+        <v>7948</v>
       </c>
       <c r="B643" t="n">
-        <v>0.2896603303236049</v>
+        <v>0.3710461624297358</v>
       </c>
       <c r="C643" t="n">
-        <v>0.2776166862810381</v>
+        <v>0.2994390502973839</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
-        <v>7953</v>
+        <v>7947</v>
       </c>
       <c r="B644" t="n">
-        <v>0.3311073757355821</v>
+        <v>0.3568528147388095</v>
       </c>
       <c r="C644" t="n">
-        <v>0.242618124008679</v>
+        <v>0.09817465446324902</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="n">
-        <v>7948</v>
+        <v>7946</v>
       </c>
       <c r="B645" t="n">
-        <v>0.3710461624297358</v>
+        <v>0.3537017725350743</v>
       </c>
       <c r="C645" t="n">
-        <v>0.2994390502973839</v>
+        <v>0.1851548526115495</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>7947</v>
+        <v>7929</v>
       </c>
       <c r="B646" t="n">
-        <v>0.3568528147388095</v>
+        <v>0.3169162163072962</v>
       </c>
       <c r="C646" t="n">
-        <v>0.09817465446324902</v>
+        <v>0.272098981150233</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="n">
-        <v>7946</v>
+        <v>7928</v>
       </c>
       <c r="B647" t="n">
-        <v>0.3537017725350743</v>
+        <v>0.3464785708227324</v>
       </c>
       <c r="C647" t="n">
-        <v>0.1851548526115495</v>
+        <v>0.2851551462790525</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
-        <v>7929</v>
+        <v>7925</v>
       </c>
       <c r="B648" t="n">
-        <v>0.3169162163072962</v>
+        <v>0.256621447473779</v>
       </c>
       <c r="C648" t="n">
-        <v>0.272098981150233</v>
+        <v>0.2291950739119887</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>7928</v>
+        <v>7917</v>
       </c>
       <c r="B649" t="n">
-        <v>0.3464785708227324</v>
+        <v>0.5085102925702194</v>
       </c>
       <c r="C649" t="n">
-        <v>0.2851551462790525</v>
+        <v>0.1949179639035675</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="n">
-        <v>7925</v>
+        <v>7916</v>
       </c>
       <c r="B650" t="n">
-        <v>0.256621447473779</v>
+        <v>0.3008577460463622</v>
       </c>
       <c r="C650" t="n">
-        <v>0.2291950739119887</v>
+        <v>0.2620417338183303</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>7917</v>
+        <v>7915</v>
       </c>
       <c r="B651" t="n">
-        <v>0.5085102925702194</v>
+        <v>0.3366773402474857</v>
       </c>
       <c r="C651" t="n">
-        <v>0.1949179639035675</v>
+        <v>0.3399565151070055</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>7916</v>
+        <v>7914</v>
       </c>
       <c r="B652" t="n">
-        <v>0.3008577460463622</v>
+        <v>0.3527727737009676</v>
       </c>
       <c r="C652" t="n">
-        <v>0.2620417338183303</v>
+        <v>0.2351689698688355</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>7915</v>
+        <v>7913</v>
       </c>
       <c r="B653" t="n">
-        <v>0.3366773402474857</v>
+        <v>0.3328837653559623</v>
       </c>
       <c r="C653" t="n">
-        <v>0.3399565151070055</v>
+        <v>0.3325836325131394</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>7914</v>
+        <v>7912</v>
       </c>
       <c r="B654" t="n">
-        <v>0.3527727737009676</v>
+        <v>0.3383422917156491</v>
       </c>
       <c r="C654" t="n">
-        <v>0.2351689698688355</v>
+        <v>0.346412438115029</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>7913</v>
+        <v>7910</v>
       </c>
       <c r="B655" t="n">
-        <v>0.3328837653559623</v>
+        <v>0.34455661243719</v>
       </c>
       <c r="C655" t="n">
-        <v>0.3325836325131394</v>
+        <v>0.3220575874498205</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>7912</v>
+        <v>7909</v>
       </c>
       <c r="B656" t="n">
-        <v>0.3383422917156491</v>
+        <v>0.3447271653975056</v>
       </c>
       <c r="C656" t="n">
-        <v>0.346412438115029</v>
+        <v>0.1253691112416465</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>7910</v>
+        <v>7903</v>
       </c>
       <c r="B657" t="n">
-        <v>0.34455661243719</v>
+        <v>0.3187617516478571</v>
       </c>
       <c r="C657" t="n">
-        <v>0.3220575874498205</v>
+        <v>0.2542972456346962</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>7909</v>
+        <v>7902</v>
       </c>
       <c r="B658" t="n">
-        <v>0.3447271653975056</v>
+        <v>0.3307812858151916</v>
       </c>
       <c r="C658" t="n">
-        <v>0.1253691112416465</v>
+        <v>0.230165940043154</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>7903</v>
+        <v>7900</v>
       </c>
       <c r="B659" t="n">
-        <v>0.3187617516478571</v>
+        <v>0.4493016108833764</v>
       </c>
       <c r="C659" t="n">
-        <v>0.2542972456346962</v>
+        <v>0.3035616566491178</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>7902</v>
+        <v>7897</v>
       </c>
       <c r="B660" t="n">
-        <v>0.3307812858151916</v>
+        <v>0.5156678209502478</v>
       </c>
       <c r="C660" t="n">
-        <v>0.230165940043154</v>
+        <v>0.3362718033033771</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="n">
-        <v>7900</v>
+        <v>7887</v>
       </c>
       <c r="B661" t="n">
-        <v>0.4493016108833764</v>
+        <v>0.4283765895250299</v>
       </c>
       <c r="C661" t="n">
-        <v>0.3035616566491178</v>
+        <v>0.3003830930722938</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>7897</v>
+        <v>7873</v>
       </c>
       <c r="B662" t="n">
-        <v>0.5156678209502478</v>
+        <v>0.3523623488436657</v>
       </c>
       <c r="C662" t="n">
-        <v>0.3362718033033771</v>
+        <v>0.2870802778077</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="n">
-        <v>7887</v>
+        <v>7872</v>
       </c>
       <c r="B663" t="n">
-        <v>0.4283765895250299</v>
+        <v>0.3285671593260567</v>
       </c>
       <c r="C663" t="n">
-        <v>0.3003830930722938</v>
+        <v>0.3148325906594294</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="n">
-        <v>7873</v>
+        <v>7870</v>
       </c>
       <c r="B664" t="n">
-        <v>0.3523623488436657</v>
+        <v>0.2778593480695454</v>
       </c>
       <c r="C664" t="n">
-        <v>0.2870802778077</v>
+        <v>0.2407460356822911</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="n">
-        <v>7872</v>
+        <v>7869</v>
       </c>
       <c r="B665" t="n">
-        <v>0.3285671593260567</v>
+        <v>0.3607185556237688</v>
       </c>
       <c r="C665" t="n">
-        <v>0.3148325906594294</v>
+        <v>0.3313945564110323</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>7870</v>
+        <v>7863</v>
       </c>
       <c r="B666" t="n">
-        <v>0.2778593480695454</v>
+        <v>0.2812645803862296</v>
       </c>
       <c r="C666" t="n">
-        <v>0.2407460356822911</v>
+        <v>0.2700082622660603</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="n">
-        <v>7869</v>
+        <v>7858</v>
       </c>
       <c r="B667" t="n">
-        <v>0.3607185556237688</v>
+        <v>0.2642958238817926</v>
       </c>
       <c r="C667" t="n">
-        <v>0.3313945564110323</v>
+        <v>0.1830088732867627</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>7863</v>
+        <v>7848</v>
       </c>
       <c r="B668" t="n">
-        <v>0.2812645803862296</v>
+        <v>0.2794806016031766</v>
       </c>
       <c r="C668" t="n">
-        <v>0.2700082622660603</v>
+        <v>0.259432385053333</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="n">
-        <v>7858</v>
+        <v>7846</v>
       </c>
       <c r="B669" t="n">
-        <v>0.2642958238817926</v>
+        <v>0.3718154070417191</v>
       </c>
       <c r="C669" t="n">
-        <v>0.1830088732867627</v>
+        <v>0.2973862384450962</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>7848</v>
+        <v>7845</v>
       </c>
       <c r="B670" t="n">
-        <v>0.2794806016031766</v>
+        <v>0.5512774594273224</v>
       </c>
       <c r="C670" t="n">
-        <v>0.259432385053333</v>
+        <v>0.314574601087393</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>7846</v>
+        <v>7844</v>
       </c>
       <c r="B671" t="n">
-        <v>0.3718154070417191</v>
+        <v>0.58111007752505</v>
       </c>
       <c r="C671" t="n">
-        <v>0.2973862384450962</v>
+        <v>0.4012145015919644</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>7845</v>
+        <v>7843</v>
       </c>
       <c r="B672" t="n">
-        <v>0.5512774594273224</v>
+        <v>0.3146168577324596</v>
       </c>
       <c r="C672" t="n">
-        <v>0.314574601087393</v>
+        <v>0.3526011283795457</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>7844</v>
+        <v>7842</v>
       </c>
       <c r="B673" t="n">
-        <v>0.58111007752505</v>
+        <v>0.3962576189382387</v>
       </c>
       <c r="C673" t="n">
-        <v>0.4012145015919644</v>
+        <v>0.3159001428726632</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="n">
-        <v>7843</v>
+        <v>7839</v>
       </c>
       <c r="B674" t="n">
-        <v>0.3146168577324596</v>
+        <v>0.3466080472850435</v>
       </c>
       <c r="C674" t="n">
-        <v>0.3526011283795457</v>
+        <v>0.342210001424284</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="n">
-        <v>7842</v>
+        <v>7838</v>
       </c>
       <c r="B675" t="n">
-        <v>0.3962576189382387</v>
+        <v>0.3479370363831973</v>
       </c>
       <c r="C675" t="n">
-        <v>0.3159001428726632</v>
+        <v>0.3502858040972028</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>7839</v>
+        <v>7837</v>
       </c>
       <c r="B676" t="n">
-        <v>0.3466080472850435</v>
+        <v>0.3326106817732888</v>
       </c>
       <c r="C676" t="n">
-        <v>0.342210001424284</v>
+        <v>0.18710368748296</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>7838</v>
+        <v>7836</v>
       </c>
       <c r="B677" t="n">
-        <v>0.3479370363831973</v>
+        <v>0.4143185601603109</v>
       </c>
       <c r="C677" t="n">
-        <v>0.3502858040972028</v>
+        <v>0.3307088774545511</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>7837</v>
+        <v>7835</v>
       </c>
       <c r="B678" t="n">
-        <v>0.3326106817732888</v>
+        <v>0.3350164154714367</v>
       </c>
       <c r="C678" t="n">
-        <v>0.18710368748296</v>
+        <v>0.3212352929715385</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="n">
-        <v>7836</v>
+        <v>7834</v>
       </c>
       <c r="B679" t="n">
-        <v>0.4143185601603109</v>
+        <v>0.3258756145989539</v>
       </c>
       <c r="C679" t="n">
-        <v>0.3307088774545511</v>
+        <v>0.2552959434884654</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="n">
-        <v>7835</v>
+        <v>7829</v>
       </c>
       <c r="B680" t="n">
-        <v>0.3350164154714367</v>
+        <v>0.2720160534524564</v>
       </c>
       <c r="C680" t="n">
-        <v>0.3212352929715385</v>
+        <v>0.238528862708441</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="n">
-        <v>7834</v>
+        <v>7826</v>
       </c>
       <c r="B681" t="n">
-        <v>0.3258756145989539</v>
+        <v>0.3338363946849056</v>
       </c>
       <c r="C681" t="n">
-        <v>0.2552959434884654</v>
+        <v>0.2807192325934568</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="n">
-        <v>7829</v>
+        <v>7825</v>
       </c>
       <c r="B682" t="n">
-        <v>0.2720160534524564</v>
+        <v>0.3255509338482149</v>
       </c>
       <c r="C682" t="n">
-        <v>0.238528862708441</v>
+        <v>0.3318946588373498</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="n">
-        <v>7826</v>
+        <v>7818</v>
       </c>
       <c r="B683" t="n">
-        <v>0.3338363946849056</v>
+        <v>0.3723745570841512</v>
       </c>
       <c r="C683" t="n">
-        <v>0.2807192325934568</v>
+        <v>0.257217036951943</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>7825</v>
+        <v>7813</v>
       </c>
       <c r="B684" t="n">
-        <v>0.3255509338482149</v>
+        <v>0.3136699912295433</v>
       </c>
       <c r="C684" t="n">
-        <v>0.3318946588373498</v>
+        <v>0.2743180448346374</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="n">
-        <v>7818</v>
+        <v>7805</v>
       </c>
       <c r="B685" t="n">
-        <v>0.3723745570841512</v>
+        <v>0.456189736713444</v>
       </c>
       <c r="C685" t="n">
-        <v>0.257217036951943</v>
+        <v>0.3181576517914407</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="n">
-        <v>7813</v>
+        <v>7790</v>
       </c>
       <c r="B686" t="n">
-        <v>0.3136699912295433</v>
+        <v>0.3906825000463383</v>
       </c>
       <c r="C686" t="n">
-        <v>0.2743180448346374</v>
+        <v>0.3373925596097309</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="n">
-        <v>7805</v>
+        <v>7783</v>
       </c>
       <c r="B687" t="n">
-        <v>0.456189736713444</v>
+        <v>0.2703517666325279</v>
       </c>
       <c r="C687" t="n">
-        <v>0.3181576517914407</v>
+        <v>0.2893791411610428</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="n">
-        <v>7790</v>
+        <v>7782</v>
       </c>
       <c r="B688" t="n">
-        <v>0.3906825000463383</v>
+        <v>0.2682729074377508</v>
       </c>
       <c r="C688" t="n">
-        <v>0.3373925596097309</v>
+        <v>0.2432040704851841</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="n">
-        <v>7783</v>
+        <v>7768</v>
       </c>
       <c r="B689" t="n">
-        <v>0.2703517666325279</v>
+        <v>0.3672528051993141</v>
       </c>
       <c r="C689" t="n">
-        <v>0.2893791411610428</v>
+        <v>0.3551306688575585</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="n">
-        <v>7782</v>
+        <v>7765</v>
       </c>
       <c r="B690" t="n">
-        <v>0.2682729074377508</v>
+        <v>0.2811942157591334</v>
       </c>
       <c r="C690" t="n">
-        <v>0.2432040704851841</v>
+        <v>0.28014647245295</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="n">
-        <v>7768</v>
+        <v>7764</v>
       </c>
       <c r="B691" t="n">
-        <v>0.3672528051993141</v>
+        <v>0.3047865807652489</v>
       </c>
       <c r="C691" t="n">
-        <v>0.3551306688575585</v>
+        <v>0.275047350926157</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="n">
-        <v>7765</v>
+        <v>7763</v>
       </c>
       <c r="B692" t="n">
-        <v>0.2811942157591334</v>
+        <v>0.341485789301657</v>
       </c>
       <c r="C692" t="n">
-        <v>0.28014647245295</v>
+        <v>0.2381828963251348</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="n">
-        <v>7764</v>
+        <v>7762</v>
       </c>
       <c r="B693" t="n">
-        <v>0.3047865807652489</v>
+        <v>0.4953954098790317</v>
       </c>
       <c r="C693" t="n">
-        <v>0.275047350926157</v>
+        <v>0.1900133928894069</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="n">
-        <v>7763</v>
+        <v>7760</v>
       </c>
       <c r="B694" t="n">
-        <v>0.341485789301657</v>
+        <v>0.3583524724568777</v>
       </c>
       <c r="C694" t="n">
-        <v>0.2381828963251348</v>
+        <v>0.2812270714527229</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="n">
-        <v>7762</v>
+        <v>7759</v>
       </c>
       <c r="B695" t="n">
-        <v>0.4953954098790317</v>
+        <v>0.2931620224066062</v>
       </c>
       <c r="C695" t="n">
-        <v>0.1900133928894069</v>
+        <v>0.177717270263286</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="n">
-        <v>7760</v>
+        <v>7757</v>
       </c>
       <c r="B696" t="n">
-        <v>0.3583524724568777</v>
+        <v>0.5058573207426578</v>
       </c>
       <c r="C696" t="n">
-        <v>0.2812270714527229</v>
+        <v>0.2896186320289391</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="n">
-        <v>7759</v>
+        <v>7754</v>
       </c>
       <c r="B697" t="n">
-        <v>0.2931620224066062</v>
+        <v>0.3064669092977178</v>
       </c>
       <c r="C697" t="n">
-        <v>0.177717270263286</v>
+        <v>0.2440709323468915</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="n">
-        <v>7757</v>
+        <v>7749</v>
       </c>
       <c r="B698" t="n">
-        <v>0.5058573207426578</v>
+        <v>0.3046867958751081</v>
       </c>
       <c r="C698" t="n">
-        <v>0.2896186320289391</v>
+        <v>0.3050698737379933</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="n">
-        <v>7754</v>
+        <v>7721</v>
       </c>
       <c r="B699" t="n">
-        <v>0.3064669092977178</v>
+        <v>0.5710475468167608</v>
       </c>
       <c r="C699" t="n">
-        <v>0.2440709323468915</v>
+        <v>0.2059359489646288</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="n">
-        <v>7749</v>
+        <v>7710</v>
       </c>
       <c r="B700" t="n">
-        <v>0.3046867958751081</v>
+        <v>0.5187495450509138</v>
       </c>
       <c r="C700" t="n">
-        <v>0.3050698737379933</v>
+        <v>0.4813483645168811</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="n">
-        <v>7721</v>
+        <v>7699</v>
       </c>
       <c r="B701" t="n">
-        <v>0.5710475468167608</v>
+        <v>0.3916487675452484</v>
       </c>
       <c r="C701" t="n">
-        <v>0.2059359489646288</v>
+        <v>0.1332360868417644</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="n">
-        <v>7710</v>
+        <v>7698</v>
       </c>
       <c r="B702" t="n">
-        <v>0.5187495450509138</v>
+        <v>0.4989143305264717</v>
       </c>
       <c r="C702" t="n">
-        <v>0.4813483645168811</v>
+        <v>0.4973873173969376</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="n">
-        <v>7699</v>
+        <v>7697</v>
       </c>
       <c r="B703" t="n">
-        <v>0.3916487675452484</v>
+        <v>0.4649357924286003</v>
       </c>
       <c r="C703" t="n">
-        <v>0.1332360868417644</v>
+        <v>0.4694351871078346</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="n">
-        <v>7698</v>
+        <v>7605</v>
       </c>
       <c r="B704" t="n">
-        <v>0.4989143305264717</v>
+        <v>0.4974749173142178</v>
       </c>
       <c r="C704" t="n">
-        <v>0.4973873173969376</v>
+        <v>0.1291164949212592</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="n">
-        <v>7697</v>
+        <v>7604</v>
       </c>
       <c r="B705" t="n">
-        <v>0.4649357924286003</v>
+        <v>0.4822259496705243</v>
       </c>
       <c r="C705" t="n">
-        <v>0.4694351871078346</v>
+        <v>0.1802156732648054</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="n">
-        <v>7605</v>
+        <v>7552</v>
       </c>
       <c r="B706" t="n">
-        <v>0.4974749173142178</v>
+        <v>0.4853656026431568</v>
       </c>
       <c r="C706" t="n">
-        <v>0.1291164949212592</v>
+        <v>0.4876491800809379</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="n">
-        <v>7604</v>
+        <v>7551</v>
       </c>
       <c r="B707" t="n">
-        <v>0.4822259496705243</v>
+        <v>0.4017585731826976</v>
       </c>
       <c r="C707" t="n">
-        <v>0.1802156732648054</v>
+        <v>0.3217669579557944</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="n">
-        <v>7552</v>
+        <v>7527</v>
       </c>
       <c r="B708" t="n">
-        <v>0.4853656026431568</v>
+        <v>0.4021152485747536</v>
       </c>
       <c r="C708" t="n">
-        <v>0.4876491800809379</v>
+        <v>0.1869318320193167</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="n">
-        <v>7551</v>
+        <v>7515</v>
       </c>
       <c r="B709" t="n">
-        <v>0.4017585731826976</v>
+        <v>0.3005183837695835</v>
       </c>
       <c r="C709" t="n">
-        <v>0.3217669579557944</v>
+        <v>0.2076716519721876</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="n">
-        <v>7527</v>
+        <v>7504</v>
       </c>
       <c r="B710" t="n">
-        <v>0.4021152485747536</v>
+        <v>0.3496374112556851</v>
       </c>
       <c r="C710" t="n">
-        <v>0.1869318320193167</v>
+        <v>0.1503022944516275</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="n">
-        <v>7515</v>
+        <v>7456</v>
       </c>
       <c r="B711" t="n">
-        <v>0.3005183837695835</v>
+        <v>0.3328308943451335</v>
       </c>
       <c r="C711" t="n">
-        <v>0.2076716519721876</v>
+        <v>0.3417668763916912</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="n">
-        <v>7504</v>
+        <v>7449</v>
       </c>
       <c r="B712" t="n">
-        <v>0.3496374112556851</v>
+        <v>0.4326884652167706</v>
       </c>
       <c r="C712" t="n">
-        <v>0.1503022944516275</v>
+        <v>0.4380915436047124</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="n">
-        <v>7456</v>
+        <v>7380</v>
       </c>
       <c r="B713" t="n">
-        <v>0.3328308943451335</v>
+        <v>0.3250477940211425</v>
       </c>
       <c r="C713" t="n">
-        <v>0.3417668763916912</v>
+        <v>0.2642164302235582</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="n">
-        <v>7449</v>
+        <v>7350</v>
       </c>
       <c r="B714" t="n">
-        <v>0.4326884652167706</v>
+        <v>0.4997245340038924</v>
       </c>
       <c r="C714" t="n">
-        <v>0.4380915436047124</v>
+        <v>0.1214823505718279</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="n">
-        <v>7380</v>
+        <v>7348</v>
       </c>
       <c r="B715" t="n">
-        <v>0.3250477940211425</v>
+        <v>0.3188992287387976</v>
       </c>
       <c r="C715" t="n">
-        <v>0.2642164302235582</v>
+        <v>0.3089912765256613</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="n">
-        <v>7350</v>
+        <v>7345</v>
       </c>
       <c r="B716" t="n">
-        <v>0.4998093502748546</v>
+        <v>0.2986005000878827</v>
       </c>
       <c r="C716" t="n">
-        <v>0.1214887614046764</v>
+        <v>0.07709820605853399</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="n">
-        <v>7348</v>
+        <v>7343</v>
       </c>
       <c r="B717" t="n">
-        <v>0.3188992287387976</v>
+        <v>0.3941599961760166</v>
       </c>
       <c r="C717" t="n">
-        <v>0.3089912765256613</v>
+        <v>0.1792939205878877</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="n">
-        <v>7345</v>
+        <v>7336</v>
       </c>
       <c r="B718" t="n">
-        <v>0.2986005000878827</v>
+        <v>0.2932779887693165</v>
       </c>
       <c r="C718" t="n">
-        <v>0.07709820605853399</v>
+        <v>0.2865447683257172</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="n">
-        <v>7343</v>
+        <v>7335</v>
       </c>
       <c r="B719" t="n">
-        <v>0.3941599961760166</v>
+        <v>0.2832746014931929</v>
       </c>
       <c r="C719" t="n">
-        <v>0.1792939205878877</v>
+        <v>0.2844799457342692</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="n">
-        <v>7336</v>
+        <v>7325</v>
       </c>
       <c r="B720" t="n">
-        <v>0.2932779887693165</v>
+        <v>0.2791098610264018</v>
       </c>
       <c r="C720" t="n">
-        <v>0.2865447683257172</v>
+        <v>0.1076646918293653</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="n">
-        <v>7335</v>
+        <v>7318</v>
       </c>
       <c r="B721" t="n">
-        <v>0.2832746014931929</v>
+        <v>0.2521526523247613</v>
       </c>
       <c r="C721" t="n">
-        <v>0.2844799457342692</v>
+        <v>0.2597872241916175</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="n">
-        <v>7325</v>
+        <v>7315</v>
       </c>
       <c r="B722" t="n">
-        <v>0.2791098610264018</v>
+        <v>0.3698279939313583</v>
       </c>
       <c r="C722" t="n">
-        <v>0.1076646918293653</v>
+        <v>0.2736126796538697</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="n">
-        <v>7318</v>
+        <v>7314</v>
       </c>
       <c r="B723" t="n">
-        <v>0.2521526523247613</v>
+        <v>0.305828652890638</v>
       </c>
       <c r="C723" t="n">
-        <v>0.2597872241916175</v>
+        <v>0.08415420361230849</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="n">
-        <v>7315</v>
+        <v>7307</v>
       </c>
       <c r="B724" t="n">
-        <v>0.3698279939313583</v>
+        <v>0.4560875752734623</v>
       </c>
       <c r="C724" t="n">
-        <v>0.2736126796538697</v>
+        <v>0.196090829052396</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="n">
-        <v>7314</v>
+        <v>7302</v>
       </c>
       <c r="B725" t="n">
-        <v>0.305828652890638</v>
+        <v>0.3416439328117672</v>
       </c>
       <c r="C725" t="n">
-        <v>0.08415420361230849</v>
+        <v>0.295329999436111</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="n">
-        <v>7307</v>
+        <v>7296</v>
       </c>
       <c r="B726" t="n">
-        <v>0.4560875752734623</v>
+        <v>0.5367699885308257</v>
       </c>
       <c r="C726" t="n">
-        <v>0.196090829052396</v>
+        <v>0.4236728337861173</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="n">
-        <v>7302</v>
+        <v>7288</v>
       </c>
       <c r="B727" t="n">
-        <v>0.3416439328117672</v>
+        <v>0.2672873829880692</v>
       </c>
       <c r="C727" t="n">
-        <v>0.295329999436111</v>
+        <v>0.2465653277253968</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="n">
-        <v>7296</v>
+        <v>7277</v>
       </c>
       <c r="B728" t="n">
-        <v>0.5367699885308257</v>
+        <v>0.3675500157295302</v>
       </c>
       <c r="C728" t="n">
-        <v>0.4236728337861173</v>
+        <v>0.2607391529555412</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>7288</v>
+        <v>7270</v>
       </c>
       <c r="B729" t="n">
-        <v>0.2672873829880692</v>
+        <v>0.270543032849736</v>
       </c>
       <c r="C729" t="n">
-        <v>0.2465653277253968</v>
+        <v>0.2770299039328928</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>7277</v>
+        <v>7266</v>
       </c>
       <c r="B730" t="n">
-        <v>0.3675500157295302</v>
+        <v>0.4178164054566383</v>
       </c>
       <c r="C730" t="n">
-        <v>0.2607391529555412</v>
+        <v>0.282376813927163</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="n">
-        <v>7270</v>
+        <v>7258</v>
       </c>
       <c r="B731" t="n">
-        <v>0.270543032849736</v>
+        <v>0.3085094401409363</v>
       </c>
       <c r="C731" t="n">
-        <v>0.2770299039328928</v>
+        <v>0.2370500067180846</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="n">
-        <v>7266</v>
+        <v>7242</v>
       </c>
       <c r="B732" t="n">
-        <v>0.4178164054566383</v>
+        <v>0.5214184041421026</v>
       </c>
       <c r="C732" t="n">
-        <v>0.282376813927163</v>
+        <v>0.2796843111595249</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="n">
-        <v>7258</v>
+        <v>7237</v>
       </c>
       <c r="B733" t="n">
-        <v>0.3085094401409363</v>
+        <v>0.3028271198889579</v>
       </c>
       <c r="C733" t="n">
-        <v>0.2370500067180846</v>
+        <v>0.1973358325781017</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="n">
-        <v>7242</v>
+        <v>7213</v>
       </c>
       <c r="B734" t="n">
-        <v>0.5214184041421026</v>
+        <v>0.3473592290527097</v>
       </c>
       <c r="C734" t="n">
-        <v>0.2796843111595249</v>
+        <v>0.2249145688909041</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>7237</v>
+        <v>7212</v>
       </c>
       <c r="B735" t="n">
-        <v>0.3028271198889579</v>
+        <v>0.2569035896194281</v>
       </c>
       <c r="C735" t="n">
-        <v>0.1973358325781017</v>
+        <v>0.2517774843163089</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="n">
-        <v>7213</v>
+        <v>7210</v>
       </c>
       <c r="B736" t="n">
-        <v>0.3473592290527097</v>
+        <v>0.3347058714958683</v>
       </c>
       <c r="C736" t="n">
-        <v>0.2249145688909041</v>
+        <v>0.1678536055915924</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="n">
-        <v>7212</v>
+        <v>7203</v>
       </c>
       <c r="B737" t="n">
-        <v>0.2569035896194281</v>
+        <v>0.247802127161507</v>
       </c>
       <c r="C737" t="n">
-        <v>0.2517774843163089</v>
+        <v>0.1708076108265049</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="n">
-        <v>7210</v>
+        <v>7159</v>
       </c>
       <c r="B738" t="n">
-        <v>0.3347058714958683</v>
+        <v>0.2986526186190754</v>
       </c>
       <c r="C738" t="n">
-        <v>0.1678536055915924</v>
+        <v>0.214297344623135</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="n">
-        <v>7203</v>
+        <v>7158</v>
       </c>
       <c r="B739" t="n">
-        <v>0.247802127161507</v>
+        <v>0.2777438927748049</v>
       </c>
       <c r="C739" t="n">
-        <v>0.1708076108265049</v>
+        <v>0.1206463790738219</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="n">
-        <v>7159</v>
+        <v>7155</v>
       </c>
       <c r="B740" t="n">
-        <v>0.2986526186190754</v>
+        <v>0.3042094432449874</v>
       </c>
       <c r="C740" t="n">
-        <v>0.214297344623135</v>
+        <v>0.2059475833762333</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="n">
-        <v>7158</v>
+        <v>7153</v>
       </c>
       <c r="B741" t="n">
-        <v>0.2777438927748049</v>
+        <v>0.4188666294899271</v>
       </c>
       <c r="C741" t="n">
-        <v>0.1206463790738219</v>
+        <v>0.2836735982625915</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="n">
-        <v>7155</v>
+        <v>7146</v>
       </c>
       <c r="B742" t="n">
-        <v>0.3042094432449874</v>
+        <v>0.2835797800812763</v>
       </c>
       <c r="C742" t="n">
-        <v>0.2059475833762333</v>
+        <v>0.2378602585284893</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="n">
-        <v>7153</v>
+        <v>7145</v>
       </c>
       <c r="B743" t="n">
-        <v>0.4188666294899271</v>
+        <v>0.2620794303053172</v>
       </c>
       <c r="C743" t="n">
-        <v>0.2836735982625915</v>
+        <v>0.1813728943869889</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="n">
-        <v>7146</v>
+        <v>7138</v>
       </c>
       <c r="B744" t="n">
-        <v>0.2843530660773662</v>
+        <v>0.2659183525655396</v>
       </c>
       <c r="C744" t="n">
-        <v>0.2377803326332092</v>
+        <v>0.2609559866832266</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="n">
-        <v>7145</v>
+        <v>7097</v>
       </c>
       <c r="B745" t="n">
-        <v>0.2620794303053172</v>
+        <v>0.3190143683247253</v>
       </c>
       <c r="C745" t="n">
-        <v>0.1813728943869889</v>
+        <v>0.2497397251130826</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="n">
-        <v>7138</v>
+        <v>7082</v>
       </c>
       <c r="B746" t="n">
-        <v>0.2659183525655396</v>
+        <v>0.4884841381471512</v>
       </c>
       <c r="C746" t="n">
-        <v>0.2609559866832266</v>
+        <v>0.253676835092758</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="n">
-        <v>7097</v>
+        <v>7063</v>
       </c>
       <c r="B747" t="n">
-        <v>0.3190143683247253</v>
+        <v>0.6772527614081236</v>
       </c>
       <c r="C747" t="n">
-        <v>0.2497397251130826</v>
+        <v>0.4484279887464624</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="n">
-        <v>7082</v>
+        <v>7032</v>
       </c>
       <c r="B748" t="n">
-        <v>0.4884841381471512</v>
+        <v>0.2500716955936144</v>
       </c>
       <c r="C748" t="n">
-        <v>0.253676835092758</v>
+        <v>0.2498651422411876</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="n">
-        <v>7063</v>
+        <v>7030</v>
       </c>
       <c r="B749" t="n">
-        <v>0.6772527614081236</v>
+        <v>0.3436396021416417</v>
       </c>
       <c r="C749" t="n">
-        <v>0.4484279887464624</v>
+        <v>0.3295963285578136</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="n">
-        <v>7032</v>
+        <v>7013</v>
       </c>
       <c r="B750" t="n">
-        <v>0.2500716955936144</v>
+        <v>0.3767286721542808</v>
       </c>
       <c r="C750" t="n">
-        <v>0.2498651422411876</v>
+        <v>0.3766326853230121</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="n">
-        <v>7030</v>
+        <v>6824</v>
       </c>
       <c r="B751" t="n">
-        <v>0.3436396021416417</v>
+        <v>0.1900481822057505</v>
       </c>
       <c r="C751" t="n">
-        <v>0.3295963285578136</v>
+        <v>0.05014858117210822</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="n">
-        <v>7013</v>
+        <v>6823</v>
       </c>
       <c r="B752" t="n">
-        <v>0.3767286721542808</v>
+        <v>0.3465529109555359</v>
       </c>
       <c r="C752" t="n">
-        <v>0.3766326853230121</v>
+        <v>0.1937342358780432</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="n">
-        <v>6824</v>
+        <v>6772</v>
       </c>
       <c r="B753" t="n">
-        <v>0.1900481822057505</v>
+        <v>0.2909556887630436</v>
       </c>
       <c r="C753" t="n">
-        <v>0.05014858117210822</v>
+        <v>0.194995769040841</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="n">
-        <v>6823</v>
+        <v>6768</v>
       </c>
       <c r="B754" t="n">
-        <v>0.3465529109555359</v>
+        <v>0.3375532548607986</v>
       </c>
       <c r="C754" t="n">
-        <v>0.1937342358780432</v>
+        <v>0.2074101517576074</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="n">
-        <v>6772</v>
+        <v>6761</v>
       </c>
       <c r="B755" t="n">
-        <v>0.2909556887630436</v>
+        <v>0.3799073512829557</v>
       </c>
       <c r="C755" t="n">
-        <v>0.194995769040841</v>
+        <v>0.2633589718550108</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="n">
-        <v>6768</v>
+        <v>6741</v>
       </c>
       <c r="B756" t="n">
-        <v>0.3375532548607986</v>
+        <v>0.2042570769476116</v>
       </c>
       <c r="C756" t="n">
-        <v>0.2074101517576074</v>
+        <v>0.2171478114806526</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="n">
-        <v>6761</v>
+        <v>6705</v>
       </c>
       <c r="B757" t="n">
-        <v>0.3799073512829557</v>
+        <v>0.3329422847243379</v>
       </c>
       <c r="C757" t="n">
-        <v>0.2633589718550108</v>
+        <v>0.3280985353458105</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="n">
-        <v>6741</v>
+        <v>6664</v>
       </c>
       <c r="B758" t="n">
-        <v>0.2042570769476116</v>
+        <v>0.3758971771623588</v>
       </c>
       <c r="C758" t="n">
-        <v>0.2171478114806526</v>
+        <v>0.2090615883960997</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="n">
-        <v>6705</v>
+        <v>6652</v>
       </c>
       <c r="B759" t="n">
-        <v>0.3329422847243379</v>
+        <v>0.2147107360681471</v>
       </c>
       <c r="C759" t="n">
-        <v>0.3280985353458105</v>
+        <v>0.2527563782767405</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="n">
-        <v>6664</v>
+        <v>6651</v>
       </c>
       <c r="B760" t="n">
-        <v>0.3758971771623588</v>
+        <v>0.2038232981408532</v>
       </c>
       <c r="C760" t="n">
-        <v>0.2090615883960997</v>
+        <v>0.2479512647133689</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="n">
-        <v>6652</v>
+        <v>6650</v>
       </c>
       <c r="B761" t="n">
-        <v>0.2147107360681471</v>
+        <v>0.2000746438417244</v>
       </c>
       <c r="C761" t="n">
-        <v>0.2527563782767405</v>
+        <v>0.2519635305908348</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="n">
-        <v>6651</v>
+        <v>6641</v>
       </c>
       <c r="B762" t="n">
-        <v>0.2038232981408532</v>
+        <v>0.3256907579190448</v>
       </c>
       <c r="C762" t="n">
-        <v>0.2479512647133689</v>
+        <v>0.2311996690270806</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="n">
-        <v>6650</v>
+        <v>6639</v>
       </c>
       <c r="B763" t="n">
-        <v>0.2000746438417244</v>
+        <v>0.3344787752484715</v>
       </c>
       <c r="C763" t="n">
-        <v>0.2519635305908348</v>
+        <v>0.2028376515474279</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="n">
-        <v>6641</v>
+        <v>6635</v>
       </c>
       <c r="B764" t="n">
-        <v>0.3256907579190448</v>
+        <v>0.3190462020513519</v>
       </c>
       <c r="C764" t="n">
-        <v>0.2311996690270806</v>
+        <v>0.2291563534866973</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="n">
-        <v>6639</v>
+        <v>6584</v>
       </c>
       <c r="B765" t="n">
-        <v>0.3344787752484715</v>
+        <v>0.5854564940328495</v>
       </c>
       <c r="C765" t="n">
-        <v>0.2028376515474279</v>
+        <v>0.2853829778629149</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="n">
-        <v>6635</v>
+        <v>6481</v>
       </c>
       <c r="B766" t="n">
-        <v>0.3190462020513519</v>
+        <v>0.387377717320031</v>
       </c>
       <c r="C766" t="n">
-        <v>0.2291563534866973</v>
+        <v>0.2856176627078313</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="n">
-        <v>6584</v>
+        <v>6469</v>
       </c>
       <c r="B767" t="n">
-        <v>0.5854564940328495</v>
+        <v>0.3288410725515156</v>
       </c>
       <c r="C767" t="n">
-        <v>0.2853829778629149</v>
+        <v>0.229637966120823</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="n">
-        <v>6481</v>
+        <v>6373</v>
       </c>
       <c r="B768" t="n">
-        <v>0.387377717320031</v>
+        <v>0.3082674763806587</v>
       </c>
       <c r="C768" t="n">
-        <v>0.2856176627078313</v>
+        <v>0.2927700634360188</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="n">
-        <v>6469</v>
+        <v>6358</v>
       </c>
       <c r="B769" t="n">
-        <v>0.3288410725515156</v>
+        <v>0.3004938720842907</v>
       </c>
       <c r="C769" t="n">
-        <v>0.229637966120823</v>
+        <v>0.6828977334507822</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="n">
-        <v>6373</v>
+        <v>6264</v>
       </c>
       <c r="B770" t="n">
-        <v>0.3082674763806587</v>
+        <v>0.3702414897851868</v>
       </c>
       <c r="C770" t="n">
-        <v>0.2927700634360188</v>
+        <v>0.1270964198707062</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="n">
-        <v>6358</v>
+        <v>6258</v>
       </c>
       <c r="B771" t="n">
-        <v>0.3004938720842907</v>
+        <v>0.2237572748868596</v>
       </c>
       <c r="C771" t="n">
-        <v>0.6828977334507822</v>
+        <v>0.1925824146684291</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="n">
-        <v>6264</v>
+        <v>6257</v>
       </c>
       <c r="B772" t="n">
-        <v>0.3702414897851868</v>
+        <v>0.3323856977983995</v>
       </c>
       <c r="C772" t="n">
-        <v>0.1270964198707062</v>
+        <v>0.3119785975244607</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="n">
-        <v>6258</v>
+        <v>6254</v>
       </c>
       <c r="B773" t="n">
-        <v>0.2237572748868596</v>
+        <v>0.334367609114777</v>
       </c>
       <c r="C773" t="n">
-        <v>0.1925824146684291</v>
+        <v>0.1782227397960532</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="n">
-        <v>6257</v>
+        <v>6253</v>
       </c>
       <c r="B774" t="n">
-        <v>0.3323856977983995</v>
+        <v>0.6593947151944815</v>
       </c>
       <c r="C774" t="n">
-        <v>0.3119785975244607</v>
+        <v>0.2355734378875445</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="n">
-        <v>6254</v>
+        <v>6249</v>
       </c>
       <c r="B775" t="n">
-        <v>0.334367609114777</v>
+        <v>0.3512086127077975</v>
       </c>
       <c r="C775" t="n">
-        <v>0.1782227397960532</v>
+        <v>0.3123115966565057</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="n">
-        <v>6253</v>
+        <v>6248</v>
       </c>
       <c r="B776" t="n">
-        <v>0.6593947151944815</v>
+        <v>0.3253183842923532</v>
       </c>
       <c r="C776" t="n">
-        <v>0.2355734378875445</v>
+        <v>0.232155533238513</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="n">
-        <v>6250</v>
+        <v>6243</v>
       </c>
       <c r="B777" t="n">
-        <v>4.723492443392432</v>
+        <v>0.3579729083929972</v>
       </c>
       <c r="C777" t="n">
-        <v>0.2698742518273209</v>
+        <v>0.2765895414974064</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="n">
-        <v>6249</v>
+        <v>6223</v>
       </c>
       <c r="B778" t="n">
-        <v>0.3512086127077975</v>
+        <v>0.3144312865918614</v>
       </c>
       <c r="C778" t="n">
-        <v>0.3123115966565057</v>
+        <v>0.2664305243435861</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="n">
-        <v>6248</v>
+        <v>6213</v>
       </c>
       <c r="B779" t="n">
-        <v>0.3253183842923532</v>
+        <v>0.340245589618927</v>
       </c>
       <c r="C779" t="n">
-        <v>0.232155533238513</v>
+        <v>0.2048981216562148</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="n">
-        <v>6243</v>
+        <v>6204</v>
       </c>
       <c r="B780" t="n">
-        <v>0.3579729083929972</v>
+        <v>0.3057773022854034</v>
       </c>
       <c r="C780" t="n">
-        <v>0.2765895414974064</v>
+        <v>0.2233928083224712</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="n">
-        <v>6223</v>
+        <v>6195</v>
       </c>
       <c r="B781" t="n">
-        <v>0.3144312865918614</v>
+        <v>0.3844810245605971</v>
       </c>
       <c r="C781" t="n">
-        <v>0.2664305243435861</v>
+        <v>0.2257110905081751</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="n">
-        <v>6213</v>
+        <v>6194</v>
       </c>
       <c r="B782" t="n">
-        <v>0.340245589618927</v>
+        <v>0.3443599320466313</v>
       </c>
       <c r="C782" t="n">
-        <v>0.2048981216562148</v>
+        <v>0.2972914440856358</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="n">
-        <v>6204</v>
+        <v>6193</v>
       </c>
       <c r="B783" t="n">
-        <v>0.3057773022854034</v>
+        <v>0.3517238857055602</v>
       </c>
       <c r="C783" t="n">
-        <v>0.2233928083224712</v>
+        <v>0.2427509950658079</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="n">
-        <v>6195</v>
+        <v>6190</v>
       </c>
       <c r="B784" t="n">
-        <v>0.3844810245605971</v>
+        <v>0.3565566835743011</v>
       </c>
       <c r="C784" t="n">
-        <v>0.2257110905081751</v>
+        <v>0.3233374903318241</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="n">
-        <v>6194</v>
+        <v>6183</v>
       </c>
       <c r="B785" t="n">
-        <v>0.3443599320466313</v>
+        <v>0.3196636985354049</v>
       </c>
       <c r="C785" t="n">
-        <v>0.2972914440856358</v>
+        <v>0.1371473222240445</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="n">
-        <v>6193</v>
+        <v>6180</v>
       </c>
       <c r="B786" t="n">
-        <v>0.3517238857055602</v>
+        <v>0.3857632304768306</v>
       </c>
       <c r="C786" t="n">
-        <v>0.2427509950658079</v>
+        <v>0.2819818323916228</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="n">
-        <v>6190</v>
+        <v>6179</v>
       </c>
       <c r="B787" t="n">
-        <v>0.3565566835743011</v>
+        <v>0.3360632616178229</v>
       </c>
       <c r="C787" t="n">
-        <v>0.3233374903318241</v>
+        <v>0.3232621830842675</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="n">
-        <v>6183</v>
+        <v>6178</v>
       </c>
       <c r="B788" t="n">
-        <v>0.3196636985354049</v>
+        <v>0.3399597780607581</v>
       </c>
       <c r="C788" t="n">
-        <v>0.1371473222240445</v>
+        <v>0.1719658197038145</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="n">
-        <v>6180</v>
+        <v>6177</v>
       </c>
       <c r="B789" t="n">
-        <v>0.3857632304768306</v>
+        <v>0.3308206486370184</v>
       </c>
       <c r="C789" t="n">
-        <v>0.2819818323916228</v>
+        <v>0.2727522879579006</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="n">
-        <v>6179</v>
+        <v>6166</v>
       </c>
       <c r="B790" t="n">
-        <v>0.3360632616178229</v>
+        <v>0.3564930860246971</v>
       </c>
       <c r="C790" t="n">
-        <v>0.3232621830842675</v>
+        <v>0.1885566094076183</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="n">
-        <v>6178</v>
+        <v>6165</v>
       </c>
       <c r="B791" t="n">
-        <v>0.3399597780607581</v>
+        <v>0.3512321573125077</v>
       </c>
       <c r="C791" t="n">
-        <v>0.1719658197038145</v>
+        <v>0.2864841934563955</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="n">
-        <v>6177</v>
+        <v>6156</v>
       </c>
       <c r="B792" t="n">
-        <v>0.3308206486370184</v>
+        <v>0.4147416743025473</v>
       </c>
       <c r="C792" t="n">
-        <v>0.2727522879579006</v>
+        <v>0.2984635102466814</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="n">
-        <v>6166</v>
+        <v>6155</v>
       </c>
       <c r="B793" t="n">
-        <v>0.3564930860246971</v>
+        <v>0.386778368284526</v>
       </c>
       <c r="C793" t="n">
-        <v>0.1885566094076183</v>
+        <v>0.3190621333006167</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="n">
-        <v>6165</v>
+        <v>6146</v>
       </c>
       <c r="B794" t="n">
-        <v>0.3512321573125077</v>
+        <v>0.3663562587800235</v>
       </c>
       <c r="C794" t="n">
-        <v>0.2864841934563955</v>
+        <v>0.3684576160400438</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="n">
-        <v>6156</v>
+        <v>6139</v>
       </c>
       <c r="B795" t="n">
-        <v>0.4147416743025473</v>
+        <v>0.3226777471583943</v>
       </c>
       <c r="C795" t="n">
-        <v>0.2984635102466814</v>
+        <v>0.2668081146669355</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="n">
-        <v>6155</v>
+        <v>6138</v>
       </c>
       <c r="B796" t="n">
-        <v>0.386778368284526</v>
+        <v>0.3457424279977455</v>
       </c>
       <c r="C796" t="n">
-        <v>0.3190621333006167</v>
+        <v>0.1519936951283781</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="n">
-        <v>6146</v>
+        <v>6137</v>
       </c>
       <c r="B797" t="n">
-        <v>0.3663562587800235</v>
+        <v>0.3277872688283087</v>
       </c>
       <c r="C797" t="n">
-        <v>0.3684576160400438</v>
+        <v>0.2541606650370643</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="n">
-        <v>6139</v>
+        <v>6124</v>
       </c>
       <c r="B798" t="n">
-        <v>0.3226777471583943</v>
+        <v>0.3403086331795703</v>
       </c>
       <c r="C798" t="n">
-        <v>0.2668081146669355</v>
+        <v>0.2644809877840532</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="n">
-        <v>6138</v>
+        <v>6113</v>
       </c>
       <c r="B799" t="n">
-        <v>0.3457424279977455</v>
+        <v>0.3746039480269128</v>
       </c>
       <c r="C799" t="n">
-        <v>0.1519936951283781</v>
+        <v>0.3388376773907746</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="n">
-        <v>6137</v>
+        <v>6112</v>
       </c>
       <c r="B800" t="n">
-        <v>0.3277872688283087</v>
+        <v>0.4501588872997916</v>
       </c>
       <c r="C800" t="n">
-        <v>0.2541606650370643</v>
+        <v>0.3680231201320094</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="n">
-        <v>6124</v>
+        <v>6101</v>
       </c>
       <c r="B801" t="n">
-        <v>0.3403086331795703</v>
+        <v>0.3116103947406642</v>
       </c>
       <c r="C801" t="n">
-        <v>0.2644809877840532</v>
+        <v>0.1645344209239661</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="n">
-        <v>6113</v>
+        <v>6098</v>
       </c>
       <c r="B802" t="n">
-        <v>0.3746039480269128</v>
+        <v>0.3196972539457049</v>
       </c>
       <c r="C802" t="n">
-        <v>0.3388376773907746</v>
+        <v>0.09905186391081633</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="n">
-        <v>6112</v>
+        <v>6096</v>
       </c>
       <c r="B803" t="n">
-        <v>0.4501588872997916</v>
+        <v>0.368211714988518</v>
       </c>
       <c r="C803" t="n">
-        <v>0.3680231201320094</v>
+        <v>0.3210576701709636</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="n">
-        <v>6101</v>
+        <v>6095</v>
       </c>
       <c r="B804" t="n">
-        <v>0.3116103947406642</v>
+        <v>0.3602815904883994</v>
       </c>
       <c r="C804" t="n">
-        <v>0.1645344209239661</v>
+        <v>0.2146750224962126</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="n">
-        <v>6098</v>
+        <v>6090</v>
       </c>
       <c r="B805" t="n">
-        <v>0.3196972539457049</v>
+        <v>0.3422283564691548</v>
       </c>
       <c r="C805" t="n">
-        <v>0.09905186391081633</v>
+        <v>0.2833877145638216</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="n">
-        <v>6096</v>
+        <v>6089</v>
       </c>
       <c r="B806" t="n">
-        <v>0.368211714988518</v>
+        <v>0.2838830303636497</v>
       </c>
       <c r="C806" t="n">
-        <v>0.3210576701709636</v>
+        <v>0.1826927528147745</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="n">
-        <v>6095</v>
+        <v>6085</v>
       </c>
       <c r="B807" t="n">
-        <v>0.3602815904883994</v>
+        <v>0.304503650648991</v>
       </c>
       <c r="C807" t="n">
-        <v>0.2146750224962126</v>
+        <v>0.2900312965296057</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="n">
-        <v>6090</v>
+        <v>6077</v>
       </c>
       <c r="B808" t="n">
-        <v>0.3422283564691548</v>
+        <v>0.376486548911573</v>
       </c>
       <c r="C808" t="n">
-        <v>0.2833877145638216</v>
+        <v>0.3438433177846412</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="n">
-        <v>6089</v>
+        <v>6076</v>
       </c>
       <c r="B809" t="n">
-        <v>0.2838830303636497</v>
+        <v>0.3598510693859376</v>
       </c>
       <c r="C809" t="n">
-        <v>0.1826927528147745</v>
+        <v>0.2724871659783424</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="n">
-        <v>6085</v>
+        <v>6073</v>
       </c>
       <c r="B810" t="n">
-        <v>0.304503650648991</v>
+        <v>0.4906701292322861</v>
       </c>
       <c r="C810" t="n">
-        <v>0.2900312965296057</v>
+        <v>0.4117174898392327</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="n">
-        <v>6077</v>
+        <v>6071</v>
       </c>
       <c r="B811" t="n">
-        <v>0.376486548911573</v>
+        <v>0.41452715545352</v>
       </c>
       <c r="C811" t="n">
-        <v>0.3438433177846412</v>
+        <v>0.3857632518273271</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="n">
-        <v>6076</v>
+        <v>6068</v>
       </c>
       <c r="B812" t="n">
-        <v>0.3598510693859376</v>
+        <v>0.3560972395214522</v>
       </c>
       <c r="C812" t="n">
-        <v>0.2724871659783424</v>
+        <v>0.2683495954554355</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="n">
-        <v>6073</v>
+        <v>6065</v>
       </c>
       <c r="B813" t="n">
-        <v>0.4906701292322861</v>
+        <v>0.4049881065112617</v>
       </c>
       <c r="C813" t="n">
-        <v>0.4117174898392327</v>
+        <v>0.2977317919485741</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="n">
-        <v>6071</v>
+        <v>6064</v>
       </c>
       <c r="B814" t="n">
-        <v>0.41452715545352</v>
+        <v>0.3082196021516816</v>
       </c>
       <c r="C814" t="n">
-        <v>0.3857632518273271</v>
+        <v>0.1960930620534689</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="n">
-        <v>6068</v>
+        <v>6063</v>
       </c>
       <c r="B815" t="n">
-        <v>0.3560972395214522</v>
+        <v>0.2452485938571339</v>
       </c>
       <c r="C815" t="n">
-        <v>0.2683495954554355</v>
+        <v>0.2079030485451978</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="n">
-        <v>6065</v>
+        <v>6058</v>
       </c>
       <c r="B816" t="n">
-        <v>0.4049881065112617</v>
+        <v>0.3939858391726788</v>
       </c>
       <c r="C816" t="n">
-        <v>0.2977317919485741</v>
+        <v>0.3137908480060619</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="n">
-        <v>6064</v>
+        <v>6055</v>
       </c>
       <c r="B817" t="n">
-        <v>0.3082196021516816</v>
+        <v>0.3310623688160831</v>
       </c>
       <c r="C817" t="n">
-        <v>0.1960930620534689</v>
+        <v>0.2431518766306732</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="n">
-        <v>6063</v>
+        <v>6052</v>
       </c>
       <c r="B818" t="n">
-        <v>0.2452485938571339</v>
+        <v>0.4078348154015854</v>
       </c>
       <c r="C818" t="n">
-        <v>0.2079030485451978</v>
+        <v>0.341189610515847</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="n">
-        <v>6058</v>
+        <v>6046</v>
       </c>
       <c r="B819" t="n">
-        <v>0.3939858391726788</v>
+        <v>0.3496263592765862</v>
       </c>
       <c r="C819" t="n">
-        <v>0.3137908480060619</v>
+        <v>0.2516834475001223</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="n">
-        <v>6055</v>
+        <v>6042</v>
       </c>
       <c r="B820" t="n">
-        <v>0.3310623688160831</v>
+        <v>0.4588358261609038</v>
       </c>
       <c r="C820" t="n">
-        <v>0.2431518766306732</v>
+        <v>0.3083613727012616</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="n">
-        <v>6052</v>
+        <v>6041</v>
       </c>
       <c r="B821" t="n">
-        <v>0.4078348154015854</v>
+        <v>0.3783740059467767</v>
       </c>
       <c r="C821" t="n">
-        <v>0.341189610515847</v>
+        <v>0.344288115555093</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="n">
-        <v>6046</v>
+        <v>6035</v>
       </c>
       <c r="B822" t="n">
-        <v>0.3496263592765862</v>
+        <v>0.3649976191214529</v>
       </c>
       <c r="C822" t="n">
-        <v>0.2516834475001223</v>
+        <v>0.2139327357570942</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="n">
-        <v>6042</v>
+        <v>6034</v>
       </c>
       <c r="B823" t="n">
-        <v>0.4586137850081406</v>
+        <v>0.3495838398130346</v>
       </c>
       <c r="C823" t="n">
-        <v>0.3086947526239819</v>
+        <v>0.2875450974785897</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="n">
-        <v>6041</v>
+        <v>6030</v>
       </c>
       <c r="B824" t="n">
-        <v>0.3783740059467767</v>
+        <v>0.350528115654455</v>
       </c>
       <c r="C824" t="n">
-        <v>0.344288115555093</v>
+        <v>0.2373249530019562</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="n">
-        <v>6035</v>
+        <v>6021</v>
       </c>
       <c r="B825" t="n">
-        <v>0.3649976191214529</v>
+        <v>0.3392583733252892</v>
       </c>
       <c r="C825" t="n">
-        <v>0.2139327357570942</v>
+        <v>0.3464224857204047</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="n">
-        <v>6034</v>
+        <v>6019</v>
       </c>
       <c r="B826" t="n">
-        <v>0.3495838398130346</v>
+        <v>0.3694768923725739</v>
       </c>
       <c r="C826" t="n">
-        <v>0.2875450974785897</v>
+        <v>0.1754420145775303</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="n">
-        <v>6030</v>
+        <v>6018</v>
       </c>
       <c r="B827" t="n">
-        <v>0.350528115654455</v>
+        <v>0.3381760690485598</v>
       </c>
       <c r="C827" t="n">
-        <v>0.2373249530019562</v>
+        <v>0.1610644227360275</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="n">
-        <v>6021</v>
+        <v>6017</v>
       </c>
       <c r="B828" t="n">
-        <v>0.3392583733252892</v>
+        <v>0.3829597237026776</v>
       </c>
       <c r="C828" t="n">
-        <v>0.3464224857204047</v>
+        <v>0.2877928626805862</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="n">
-        <v>6019</v>
+        <v>6009</v>
       </c>
       <c r="B829" t="n">
-        <v>0.3694768923725739</v>
+        <v>0.3337229256250236</v>
       </c>
       <c r="C829" t="n">
-        <v>0.1754420145775303</v>
+        <v>0.2083612862054472</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="n">
-        <v>6018</v>
+        <v>6004</v>
       </c>
       <c r="B830" t="n">
-        <v>0.3381760690485598</v>
+        <v>0.3728449311377134</v>
       </c>
       <c r="C830" t="n">
-        <v>0.1610644227360275</v>
+        <v>0.1102894242260651</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="n">
-        <v>6017</v>
+        <v>6002</v>
       </c>
       <c r="B831" t="n">
-        <v>0.3829597237026776</v>
+        <v>0.3416990508642617</v>
       </c>
       <c r="C831" t="n">
-        <v>0.2877928626805862</v>
+        <v>0.3427146040982282</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="n">
-        <v>6009</v>
+        <v>5083</v>
       </c>
       <c r="B832" t="n">
-        <v>0.3337229256250236</v>
+        <v>0.3907932848193262</v>
       </c>
       <c r="C832" t="n">
-        <v>0.2083612862054472</v>
+        <v>0.2622779661793516</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="n">
-        <v>6004</v>
+        <v>4940</v>
       </c>
       <c r="B833" t="n">
-        <v>0.3728449311377134</v>
+        <v>0.3617748706344759</v>
       </c>
       <c r="C833" t="n">
-        <v>0.1102894242260651</v>
+        <v>0.2389098889524764</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="n">
-        <v>6002</v>
+        <v>4939</v>
       </c>
       <c r="B834" t="n">
-        <v>0.3416990508642617</v>
+        <v>0.468506558601854</v>
       </c>
       <c r="C834" t="n">
-        <v>0.3427146040982282</v>
+        <v>0.263427620320363</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="n">
-        <v>5083</v>
+        <v>4937</v>
       </c>
       <c r="B835" t="n">
-        <v>0.3907932848193262</v>
+        <v>0.4581695614245079</v>
       </c>
       <c r="C835" t="n">
-        <v>0.2622779661793516</v>
+        <v>0.254162618554191</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="n">
-        <v>4940</v>
+        <v>4271</v>
       </c>
       <c r="B836" t="n">
-        <v>0.3617748706344759</v>
+        <v>0.3261818489534721</v>
       </c>
       <c r="C836" t="n">
-        <v>0.2389098889524764</v>
+        <v>0.1927276196934845</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="n">
-        <v>4939</v>
+        <v>4266</v>
       </c>
       <c r="B837" t="n">
-        <v>0.468506558601854</v>
+        <v>0.3175206391225679</v>
       </c>
       <c r="C837" t="n">
-        <v>0.263427620320363</v>
+        <v>0.266969185599585</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="n">
-        <v>4937</v>
+        <v>4195</v>
       </c>
       <c r="B838" t="n">
-        <v>0.4581695614245079</v>
+        <v>0.3119502220935439</v>
       </c>
       <c r="C838" t="n">
-        <v>0.254162618554191</v>
+        <v>0.2045028374918748</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="n">
-        <v>4271</v>
+        <v>4162</v>
       </c>
       <c r="B839" t="n">
-        <v>0.3261818489534721</v>
+        <v>0.3346530547061654</v>
       </c>
       <c r="C839" t="n">
-        <v>0.1927276196934845</v>
+        <v>0.3154996174035343</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="n">
-        <v>4266</v>
+        <v>4158</v>
       </c>
       <c r="B840" t="n">
-        <v>0.3175206391225679</v>
+        <v>0.317020082467951</v>
       </c>
       <c r="C840" t="n">
-        <v>0.266969185599585</v>
+        <v>0.3019524244174864</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="n">
-        <v>4195</v>
+        <v>4143</v>
       </c>
       <c r="B841" t="n">
-        <v>0.3119502220935439</v>
+        <v>0.3495613044415612</v>
       </c>
       <c r="C841" t="n">
-        <v>0.2045028374918748</v>
+        <v>0.3218030214292061</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="n">
-        <v>4162</v>
+        <v>4078</v>
       </c>
       <c r="B842" t="n">
-        <v>0.3346530547061654</v>
+        <v>0.4241314601005604</v>
       </c>
       <c r="C842" t="n">
-        <v>0.3154996174035343</v>
+        <v>0.3502868616576083</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="n">
-        <v>4158</v>
+        <v>4076</v>
       </c>
       <c r="B843" t="n">
-        <v>0.317020082467951</v>
+        <v>0.259509833970178</v>
       </c>
       <c r="C843" t="n">
-        <v>0.3019524244174864</v>
+        <v>0.1781513424961083</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="n">
-        <v>4143</v>
+        <v>4072</v>
       </c>
       <c r="B844" t="n">
-        <v>0.3495613044415612</v>
+        <v>0.5430347165377909</v>
       </c>
       <c r="C844" t="n">
-        <v>0.3218030214292061</v>
+        <v>0.2516648734032336</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="n">
-        <v>4078</v>
+        <v>4050</v>
       </c>
       <c r="B845" t="n">
-        <v>0.4241314601005604</v>
+        <v>0.3829587519214677</v>
       </c>
       <c r="C845" t="n">
-        <v>0.3502868616576083</v>
+        <v>0.2826039353381212</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="n">
-        <v>4076</v>
+        <v>4042</v>
       </c>
       <c r="B846" t="n">
-        <v>0.2595509886996638</v>
+        <v>0.2228176546641775</v>
       </c>
       <c r="C846" t="n">
-        <v>0.178172170630156</v>
+        <v>0.2221736223559147</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="n">
-        <v>4072</v>
+        <v>4041</v>
       </c>
       <c r="B847" t="n">
-        <v>0.5430347165377909</v>
+        <v>0.3532992933491051</v>
       </c>
       <c r="C847" t="n">
-        <v>0.2516648734032336</v>
+        <v>0.2911506723653647</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="n">
-        <v>4050</v>
+        <v>4040</v>
       </c>
       <c r="B848" t="n">
-        <v>0.3829587519214677</v>
+        <v>0.5106068784514872</v>
       </c>
       <c r="C848" t="n">
-        <v>0.2826039353381212</v>
+        <v>0.2185160819719184</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="n">
-        <v>4041</v>
+        <v>4014</v>
       </c>
       <c r="B849" t="n">
-        <v>0.3532992933491051</v>
+        <v>0.251000709140881</v>
       </c>
       <c r="C849" t="n">
-        <v>0.2911506723653647</v>
+        <v>0.2389034210552508</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="n">
-        <v>4040</v>
+        <v>4005</v>
       </c>
       <c r="B850" t="n">
-        <v>0.5106068784514872</v>
+        <v>0.2544570515614628</v>
       </c>
       <c r="C850" t="n">
-        <v>0.2185160819719184</v>
+        <v>0.2119991969988011</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="n">
-        <v>4014</v>
+        <v>3992</v>
       </c>
       <c r="B851" t="n">
-        <v>0.251000709140881</v>
+        <v>0.3265203003683853</v>
       </c>
       <c r="C851" t="n">
-        <v>0.2389034210552508</v>
+        <v>0.2232537844063706</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="n">
-        <v>4005</v>
+        <v>3991</v>
       </c>
       <c r="B852" t="n">
-        <v>0.2544570515614628</v>
+        <v>0.235746703616662</v>
       </c>
       <c r="C852" t="n">
-        <v>0.2119991969988011</v>
+        <v>0.1319893535624447</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="n">
-        <v>3992</v>
+        <v>3954</v>
       </c>
       <c r="B853" t="n">
-        <v>0.3265203003683853</v>
+        <v>0.3643137296727272</v>
       </c>
       <c r="C853" t="n">
-        <v>0.2232537844063706</v>
+        <v>0.2624952297493431</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="n">
-        <v>3991</v>
+        <v>3948</v>
       </c>
       <c r="B854" t="n">
-        <v>0.235746703616662</v>
+        <v>0.3643182046288538</v>
       </c>
       <c r="C854" t="n">
-        <v>0.1319893535624447</v>
+        <v>0.2082808118399702</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="n">
-        <v>3954</v>
+        <v>3944</v>
       </c>
       <c r="B855" t="n">
-        <v>0.3643137296727272</v>
+        <v>0.3730206994540156</v>
       </c>
       <c r="C855" t="n">
-        <v>0.2624952297493431</v>
+        <v>0.2808182402987766</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="n">
-        <v>3948</v>
+        <v>3943</v>
       </c>
       <c r="B856" t="n">
-        <v>0.3643182046288538</v>
+        <v>0.3912962009615087</v>
       </c>
       <c r="C856" t="n">
-        <v>0.2082808118399702</v>
+        <v>0.2235965649308287</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="n">
-        <v>3944</v>
+        <v>3935</v>
       </c>
       <c r="B857" t="n">
-        <v>0.3730206994540156</v>
+        <v>0.3726844390255155</v>
       </c>
       <c r="C857" t="n">
-        <v>0.2808182402987766</v>
+        <v>0.2889770005132405</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="n">
-        <v>3943</v>
+        <v>3845</v>
       </c>
       <c r="B858" t="n">
-        <v>0.3912962009615087</v>
+        <v>0.330493635584287</v>
       </c>
       <c r="C858" t="n">
-        <v>0.2235965649308287</v>
+        <v>0.2054646900316744</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="n">
-        <v>3935</v>
+        <v>3809</v>
       </c>
       <c r="B859" t="n">
-        <v>0.3726844390255155</v>
+        <v>0.3702782467465688</v>
       </c>
       <c r="C859" t="n">
-        <v>0.2889770005132405</v>
+        <v>0.2544593141479853</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="n">
-        <v>3845</v>
+        <v>3804</v>
       </c>
       <c r="B860" t="n">
-        <v>0.330493635584287</v>
+        <v>0.5001071407132929</v>
       </c>
       <c r="C860" t="n">
-        <v>0.2054646900316744</v>
+        <v>0.2850159630218472</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="n">
-        <v>3809</v>
+        <v>3797</v>
       </c>
       <c r="B861" t="n">
-        <v>0.3702782467465688</v>
+        <v>0.4566094681463606</v>
       </c>
       <c r="C861" t="n">
-        <v>0.2544593141479853</v>
+        <v>0.4319831824570863</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="n">
-        <v>3804</v>
+        <v>3775</v>
       </c>
       <c r="B862" t="n">
-        <v>0.5001071407132929</v>
+        <v>0.3366675014419637</v>
       </c>
       <c r="C862" t="n">
-        <v>0.2850159630218472</v>
+        <v>0.2256991538196762</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="n">
-        <v>3797</v>
+        <v>3648</v>
       </c>
       <c r="B863" t="n">
-        <v>0.4566094681463606</v>
+        <v>0.4641712904272959</v>
       </c>
       <c r="C863" t="n">
-        <v>0.4319831824570863</v>
+        <v>0.2494360054705885</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="n">
-        <v>3775</v>
+        <v>3631</v>
       </c>
       <c r="B864" t="n">
-        <v>0.3366675014419637</v>
+        <v>0.3718539689744278</v>
       </c>
       <c r="C864" t="n">
-        <v>0.2256991538196762</v>
+        <v>0.2001140792575433</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="n">
-        <v>3482</v>
+        <v>3628</v>
       </c>
       <c r="B865" t="n">
-        <v>0.3346776734876837</v>
+        <v>0.3516103251978627</v>
       </c>
       <c r="C865" t="n">
-        <v>0.3002281558195911</v>
+        <v>0.321769053903764</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="n">
-        <v>3478</v>
+        <v>3612</v>
       </c>
       <c r="B866" t="n">
-        <v>0.3595922813033542</v>
+        <v>0.4655982358361293</v>
       </c>
       <c r="C866" t="n">
-        <v>0.2815885213400539</v>
+        <v>0.2793640591999018</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="n">
-        <v>3476</v>
+        <v>3611</v>
       </c>
       <c r="B867" t="n">
-        <v>0.3626795291148036</v>
+        <v>0.3471852698604746</v>
       </c>
       <c r="C867" t="n">
-        <v>0.2449406260260514</v>
+        <v>0.2689806218001153</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="n">
-        <v>3470</v>
+        <v>3609</v>
       </c>
       <c r="B868" t="n">
-        <v>0.3696848579224009</v>
+        <v>0.3659585925009755</v>
       </c>
       <c r="C868" t="n">
-        <v>0.3309760124135641</v>
+        <v>0.3117441477172098</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="n">
-        <v>3469</v>
+        <v>3604</v>
       </c>
       <c r="B869" t="n">
-        <v>0.2574974407528595</v>
+        <v>0.8569408864836299</v>
       </c>
       <c r="C869" t="n">
-        <v>0.2557062522369198</v>
+        <v>0.1822083245182801</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="n">
-        <v>3464</v>
+        <v>3601</v>
       </c>
       <c r="B870" t="n">
-        <v>0.2343856510491692</v>
+        <v>0.3572696440728385</v>
       </c>
       <c r="C870" t="n">
-        <v>0.236841706893045</v>
+        <v>0.2634182868701511</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="n">
-        <v>3460</v>
+        <v>3576</v>
       </c>
       <c r="B871" t="n">
-        <v>0.3588596090499862</v>
+        <v>0.3460652981680238</v>
       </c>
       <c r="C871" t="n">
-        <v>0.2648736566245349</v>
+        <v>0.3077906669956519</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="n">
-        <v>3459</v>
+        <v>3559</v>
       </c>
       <c r="B872" t="n">
-        <v>0.3582653699941508</v>
+        <v>0.3161865950968915</v>
       </c>
       <c r="C872" t="n">
-        <v>0.3061134796039866</v>
+        <v>0.2418093981180267</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="n">
-        <v>3457</v>
+        <v>3507</v>
       </c>
       <c r="B873" t="n">
-        <v>0.3572874473445922</v>
+        <v>0.2936834987214121</v>
       </c>
       <c r="C873" t="n">
-        <v>0.2784572716865864</v>
+        <v>0.1040427487814128</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="n">
-        <v>3456</v>
+        <v>3504</v>
       </c>
       <c r="B874" t="n">
-        <v>0.3661492509932175</v>
+        <v>0.3490309134562271</v>
       </c>
       <c r="C874" t="n">
-        <v>0.2299723422060515</v>
+        <v>0.1990747154898419</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="n">
-        <v>3453</v>
+        <v>3494</v>
       </c>
       <c r="B875" t="n">
-        <v>0.3171892471809213</v>
+        <v>0.2905726946657685</v>
       </c>
       <c r="C875" t="n">
-        <v>0.2701543595183473</v>
+        <v>0.2485184166997629</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="n">
-        <v>3452</v>
+        <v>3492</v>
       </c>
       <c r="B876" t="n">
-        <v>0.3353088992633245</v>
+        <v>0.2515509323821938</v>
       </c>
       <c r="C876" t="n">
-        <v>0.2152320125413965</v>
+        <v>0.2337402655435755</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="n">
-        <v>3443</v>
+        <v>3491</v>
       </c>
       <c r="B877" t="n">
-        <v>0.4463861534575695</v>
+        <v>0.3258890687430614</v>
       </c>
       <c r="C877" t="n">
-        <v>0.1995360071865612</v>
+        <v>0.2676769448130533</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="n">
-        <v>3441</v>
+        <v>3490</v>
       </c>
       <c r="B878" t="n">
-        <v>0.4898555276944004</v>
+        <v>0.3416835039013362</v>
       </c>
       <c r="C878" t="n">
-        <v>0.212917368272778</v>
+        <v>0.2348601509512404</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="n">
-        <v>3439</v>
+        <v>3485</v>
       </c>
       <c r="B879" t="n">
-        <v>0.4204061660697876</v>
+        <v>0.5142296342159252</v>
       </c>
       <c r="C879" t="n">
-        <v>0.2965508259322254</v>
+        <v>0.2781541830830315</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="n">
-        <v>3407</v>
+        <v>3484</v>
       </c>
       <c r="B880" t="n">
-        <v>0.3335590462967367</v>
+        <v>0.3178687423276553</v>
       </c>
       <c r="C880" t="n">
-        <v>0.3113417687130932</v>
+        <v>0.2925105522005826</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="n">
-        <v>3406</v>
+        <v>3482</v>
       </c>
       <c r="B881" t="n">
-        <v>0.5188656183236218</v>
+        <v>0.3346776734876837</v>
       </c>
       <c r="C881" t="n">
-        <v>0.4161096537213248</v>
+        <v>0.3002281558195911</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="n">
-        <v>3405</v>
+        <v>3478</v>
       </c>
       <c r="B882" t="n">
-        <v>0.4971659366602095</v>
+        <v>0.3595922813033542</v>
       </c>
       <c r="C882" t="n">
-        <v>0.3407814878275642</v>
+        <v>0.2815885213400539</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="n">
-        <v>3403</v>
+        <v>3476</v>
       </c>
       <c r="B883" t="n">
-        <v>0.3533233213118706</v>
+        <v>0.3626795291148036</v>
       </c>
       <c r="C883" t="n">
-        <v>0.3261852212704302</v>
+        <v>0.2449406260260514</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="n">
-        <v>3399</v>
+        <v>3470</v>
       </c>
       <c r="B884" t="n">
-        <v>0.3582383192651079</v>
+        <v>0.3696848579224009</v>
       </c>
       <c r="C884" t="n">
-        <v>0.1650980011020831</v>
+        <v>0.3309760124135641</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="n">
-        <v>3396</v>
+        <v>3469</v>
       </c>
       <c r="B885" t="n">
-        <v>0.3671997889203436</v>
+        <v>0.2574974407528595</v>
       </c>
       <c r="C885" t="n">
-        <v>0.2102227820950355</v>
+        <v>0.2557062522369198</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="n">
-        <v>3393</v>
+        <v>3464</v>
       </c>
       <c r="B886" t="n">
-        <v>0.5546103064857135</v>
+        <v>0.2343856510491692</v>
       </c>
       <c r="C886" t="n">
-        <v>0.3150818287705229</v>
+        <v>0.236841706893045</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="n">
-        <v>3338</v>
+        <v>3460</v>
       </c>
       <c r="B887" t="n">
-        <v>0.5044668861947847</v>
+        <v>0.3588596090499862</v>
       </c>
       <c r="C887" t="n">
-        <v>0.2852061851986646</v>
+        <v>0.2648736566245349</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="n">
-        <v>3298</v>
+        <v>3459</v>
       </c>
       <c r="B888" t="n">
-        <v>0.3933325958064388</v>
+        <v>0.3582653699941508</v>
       </c>
       <c r="C888" t="n">
-        <v>0.3121541520038592</v>
+        <v>0.3061134796039866</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="n">
-        <v>3297</v>
+        <v>3457</v>
       </c>
       <c r="B889" t="n">
-        <v>0.3707489006468219</v>
+        <v>0.3572874473445922</v>
       </c>
       <c r="C889" t="n">
-        <v>0.3234904782796169</v>
+        <v>0.2784572716865864</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="n">
-        <v>3295</v>
+        <v>3456</v>
       </c>
       <c r="B890" t="n">
-        <v>0.3486317529462843</v>
+        <v>0.3664345582904796</v>
       </c>
       <c r="C890" t="n">
-        <v>0.26134688425263</v>
+        <v>0.23018740635761</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="n">
-        <v>3287</v>
+        <v>3453</v>
       </c>
       <c r="B891" t="n">
-        <v>0.4188981722927569</v>
+        <v>0.3171892471809213</v>
       </c>
       <c r="C891" t="n">
-        <v>0.2714591136659169</v>
+        <v>0.2701543595183473</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="n">
-        <v>3285</v>
+        <v>3452</v>
       </c>
       <c r="B892" t="n">
-        <v>0.3432801222032547</v>
+        <v>0.3353088992633245</v>
       </c>
       <c r="C892" t="n">
-        <v>0.1948878790563332</v>
+        <v>0.2152320125413965</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="n">
-        <v>3264</v>
+        <v>3443</v>
       </c>
       <c r="B893" t="n">
-        <v>0.504223602627506</v>
+        <v>0.4463861534575695</v>
       </c>
       <c r="C893" t="n">
-        <v>0.257925069582548</v>
+        <v>0.1995360071865612</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="n">
-        <v>3250</v>
+        <v>3441</v>
       </c>
       <c r="B894" t="n">
-        <v>0.3568996709850802</v>
+        <v>0.4898555276944004</v>
       </c>
       <c r="C894" t="n">
-        <v>0.2833071535547235</v>
+        <v>0.212917368272778</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="n">
-        <v>3236</v>
+        <v>3439</v>
       </c>
       <c r="B895" t="n">
-        <v>0.298509314957978</v>
+        <v>0.4204061660697876</v>
       </c>
       <c r="C895" t="n">
-        <v>0.2077341914812946</v>
+        <v>0.2965508259322254</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="n">
-        <v>3176</v>
+        <v>3407</v>
       </c>
       <c r="B896" t="n">
-        <v>0.4448856320284529</v>
+        <v>0.3335590462967367</v>
       </c>
       <c r="C896" t="n">
-        <v>0.2241661561151415</v>
+        <v>0.3113417687130932</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="n">
-        <v>3161</v>
+        <v>3406</v>
       </c>
       <c r="B897" t="n">
-        <v>0.3434221925203501</v>
+        <v>0.5190605004818216</v>
       </c>
       <c r="C897" t="n">
-        <v>0.3082837822955668</v>
+        <v>0.4161042049075341</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="n">
-        <v>3149</v>
+        <v>3405</v>
       </c>
       <c r="B898" t="n">
-        <v>0.422102417882072</v>
+        <v>0.4971659366602095</v>
       </c>
       <c r="C898" t="n">
-        <v>0.3137820861064045</v>
+        <v>0.3407814878275642</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="n">
-        <v>3140</v>
+        <v>3403</v>
       </c>
       <c r="B899" t="n">
-        <v>0.3853793538575007</v>
+        <v>0.3533233213118706</v>
       </c>
       <c r="C899" t="n">
-        <v>0.295646403735536</v>
+        <v>0.3261852212704302</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="n">
-        <v>3138</v>
+        <v>3399</v>
       </c>
       <c r="B900" t="n">
-        <v>0.3385851225685665</v>
+        <v>0.3582383192651079</v>
       </c>
       <c r="C900" t="n">
-        <v>0.2530915466641269</v>
+        <v>0.1650980011020831</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="n">
-        <v>3136</v>
+        <v>3396</v>
       </c>
       <c r="B901" t="n">
-        <v>0.3697213549187663</v>
+        <v>0.3671997889203436</v>
       </c>
       <c r="C901" t="n">
-        <v>0.2835810809123797</v>
+        <v>0.2102227820950355</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="n">
-        <v>3132</v>
+        <v>3393</v>
       </c>
       <c r="B902" t="n">
-        <v>0.2928212772753394</v>
+        <v>0.5546103064857135</v>
       </c>
       <c r="C902" t="n">
-        <v>0.194546586083982</v>
+        <v>0.3150818287705229</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="n">
-        <v>3131</v>
+        <v>3338</v>
       </c>
       <c r="B903" t="n">
-        <v>0.3418854531932319</v>
+        <v>0.5044668861947847</v>
       </c>
       <c r="C903" t="n">
-        <v>0.2616257090794168</v>
+        <v>0.2852061851986646</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="n">
-        <v>3122</v>
+        <v>3298</v>
       </c>
       <c r="B904" t="n">
-        <v>0.3785207373715576</v>
+        <v>0.3933325958064388</v>
       </c>
       <c r="C904" t="n">
-        <v>0.306470578921682</v>
+        <v>0.3121541520038592</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="n">
-        <v>3118</v>
+        <v>3297</v>
       </c>
       <c r="B905" t="n">
-        <v>0.3686663845194791</v>
+        <v>0.3707489006468219</v>
       </c>
       <c r="C905" t="n">
-        <v>0.2940740678321718</v>
+        <v>0.3234904782796169</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="n">
-        <v>3116</v>
+        <v>3295</v>
       </c>
       <c r="B906" t="n">
-        <v>0.2162001975201314</v>
+        <v>0.3486317529462843</v>
       </c>
       <c r="C906" t="n">
-        <v>0.2018979815942632</v>
+        <v>0.26134688425263</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="n">
-        <v>3111</v>
+        <v>3287</v>
       </c>
       <c r="B907" t="n">
-        <v>0.2124562765661249</v>
+        <v>0.4188981722927569</v>
       </c>
       <c r="C907" t="n">
-        <v>0.2045065025084272</v>
+        <v>0.2714591136659169</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="n">
-        <v>3096</v>
+        <v>3285</v>
       </c>
       <c r="B908" t="n">
-        <v>0.45718014348947</v>
+        <v>0.3432801222032547</v>
       </c>
       <c r="C908" t="n">
-        <v>0.2034777537723072</v>
+        <v>0.1948878790563332</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="n">
-        <v>3008</v>
+        <v>3264</v>
       </c>
       <c r="B909" t="n">
-        <v>0.3926630703111071</v>
+        <v>0.504223602627506</v>
       </c>
       <c r="C909" t="n">
-        <v>0.2969040388854062</v>
+        <v>0.257925069582548</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="n">
-        <v>3006</v>
+        <v>3250</v>
       </c>
       <c r="B910" t="n">
-        <v>0.3307685886274527</v>
+        <v>0.3568996709850802</v>
       </c>
       <c r="C910" t="n">
-        <v>0.296217895346381</v>
+        <v>0.2833071535547235</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="n">
-        <v>2965</v>
+        <v>3236</v>
       </c>
       <c r="B911" t="n">
-        <v>0.3209565644256328</v>
+        <v>0.298509314957978</v>
       </c>
       <c r="C911" t="n">
-        <v>0.2748666092451554</v>
+        <v>0.2077341914812946</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="n">
-        <v>2964</v>
+        <v>3176</v>
       </c>
       <c r="B912" t="n">
-        <v>0.3208240534728893</v>
+        <v>0.4448856320284529</v>
       </c>
       <c r="C912" t="n">
-        <v>0.2655806931886983</v>
+        <v>0.2241661561151415</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="n">
-        <v>2963</v>
+        <v>3161</v>
       </c>
       <c r="B913" t="n">
-        <v>0.3320134354932753</v>
+        <v>0.3434221925203501</v>
       </c>
       <c r="C913" t="n">
-        <v>0.256944022260216</v>
+        <v>0.3082837822955668</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="n">
-        <v>2956</v>
+        <v>3149</v>
       </c>
       <c r="B914" t="n">
-        <v>0.344440094584369</v>
+        <v>0.422102417882072</v>
       </c>
       <c r="C914" t="n">
-        <v>0.2820689173841204</v>
+        <v>0.3137820861064045</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="n">
-        <v>2952</v>
+        <v>3148</v>
       </c>
       <c r="B915" t="n">
-        <v>0.3255275495494014</v>
+        <v>0.3477516480076078</v>
       </c>
       <c r="C915" t="n">
-        <v>0.2507902994041949</v>
+        <v>0.2592286348993911</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="n">
-        <v>2951</v>
+        <v>3140</v>
       </c>
       <c r="B916" t="n">
-        <v>0.3353632104076897</v>
+        <v>0.3853793538575007</v>
       </c>
       <c r="C916" t="n">
-        <v>0.2897660478652996</v>
+        <v>0.295646403735536</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="n">
-        <v>2880</v>
+        <v>3138</v>
       </c>
       <c r="B917" t="n">
-        <v>0.2714211292979192</v>
+        <v>0.3385851225685665</v>
       </c>
       <c r="C917" t="n">
-        <v>0.2214169514369332</v>
+        <v>0.2530915466641269</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="n">
-        <v>2876</v>
+        <v>3136</v>
       </c>
       <c r="B918" t="n">
-        <v>0.3621596385605007</v>
+        <v>0.3697213549187663</v>
       </c>
       <c r="C918" t="n">
-        <v>0.3001264624162437</v>
+        <v>0.2835810809123797</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="n">
-        <v>2869</v>
+        <v>3132</v>
       </c>
       <c r="B919" t="n">
-        <v>0.3028466178228051</v>
+        <v>0.2928212772753394</v>
       </c>
       <c r="C919" t="n">
-        <v>0.2514092271349473</v>
+        <v>0.194546586083982</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="n">
-        <v>2866</v>
+        <v>3131</v>
       </c>
       <c r="B920" t="n">
-        <v>0.5621305388653212</v>
+        <v>0.3418854531932319</v>
       </c>
       <c r="C920" t="n">
-        <v>0.2842802165435908</v>
+        <v>0.2616257090794168</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="n">
-        <v>2847</v>
+        <v>3122</v>
       </c>
       <c r="B921" t="n">
-        <v>0.9716356061417373</v>
+        <v>0.3785207373715576</v>
       </c>
       <c r="C921" t="n">
-        <v>0.3338154086735513</v>
+        <v>0.306470578921682</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="n">
-        <v>2836</v>
+        <v>3118</v>
       </c>
       <c r="B922" t="n">
-        <v>0.3904267181121351</v>
+        <v>0.3686663845194791</v>
       </c>
       <c r="C922" t="n">
-        <v>0.2133157872669535</v>
+        <v>0.2940740678321718</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="n">
-        <v>2832</v>
+        <v>3116</v>
       </c>
       <c r="B923" t="n">
-        <v>0.3790382711651467</v>
+        <v>0.2162001975201314</v>
       </c>
       <c r="C923" t="n">
-        <v>0.2650944331044763</v>
+        <v>0.2018979815942632</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="n">
-        <v>2831</v>
+        <v>3111</v>
       </c>
       <c r="B924" t="n">
-        <v>0.2483639083878845</v>
+        <v>0.2124562765661249</v>
       </c>
       <c r="C924" t="n">
-        <v>0.01380290962039178</v>
+        <v>0.2045065025084272</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="n">
-        <v>2828</v>
+        <v>3096</v>
       </c>
       <c r="B925" t="n">
-        <v>0.3646026641021252</v>
+        <v>0.45718014348947</v>
       </c>
       <c r="C925" t="n">
-        <v>0.1929013573584469</v>
+        <v>0.2034777537723072</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="n">
-        <v>2823</v>
+        <v>3008</v>
       </c>
       <c r="B926" t="n">
-        <v>0.346862092163365</v>
+        <v>0.3926630703111071</v>
       </c>
       <c r="C926" t="n">
-        <v>0.3445169079850843</v>
+        <v>0.2969040388854062</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="n">
-        <v>2817</v>
+        <v>3006</v>
       </c>
       <c r="B927" t="n">
-        <v>0.3399157335318119</v>
+        <v>0.329864314254977</v>
       </c>
       <c r="C927" t="n">
-        <v>0.2276697801513621</v>
+        <v>0.296050902365721</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="n">
-        <v>2790</v>
+        <v>2965</v>
       </c>
       <c r="B928" t="n">
-        <v>0.2997899353602586</v>
+        <v>0.3209565644256328</v>
       </c>
       <c r="C928" t="n">
-        <v>0.1221145396483305</v>
+        <v>0.2748666092451554</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="n">
-        <v>2727</v>
+        <v>2964</v>
       </c>
       <c r="B929" t="n">
-        <v>0.3850476929669744</v>
+        <v>0.3208240534728893</v>
       </c>
       <c r="C929" t="n">
-        <v>0.349660379445293</v>
+        <v>0.2655806931886983</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="n">
-        <v>2723</v>
+        <v>2963</v>
       </c>
       <c r="B930" t="n">
-        <v>0.5018057054083022</v>
+        <v>0.3320134354932753</v>
       </c>
       <c r="C930" t="n">
-        <v>0.1609011691355129</v>
+        <v>0.256944022260216</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="n">
-        <v>2721</v>
+        <v>2956</v>
       </c>
       <c r="B931" t="n">
-        <v>0.4022156496393816</v>
+        <v>0.344440094584369</v>
       </c>
       <c r="C931" t="n">
-        <v>0.299490970225146</v>
+        <v>0.2820689173841204</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="n">
-        <v>2720</v>
+        <v>2952</v>
       </c>
       <c r="B932" t="n">
-        <v>0.5191699733792394</v>
+        <v>0.3255275495494014</v>
       </c>
       <c r="C932" t="n">
-        <v>0.2442676843335672</v>
+        <v>0.2507902994041949</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="n">
-        <v>2718</v>
+        <v>2951</v>
       </c>
       <c r="B933" t="n">
-        <v>0.3739721165609389</v>
+        <v>0.3353632104076897</v>
       </c>
       <c r="C933" t="n">
-        <v>0.3246401199904337</v>
+        <v>0.2897660478652996</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="n">
-        <v>2713</v>
+        <v>2880</v>
       </c>
       <c r="B934" t="n">
-        <v>0.4985237809848007</v>
+        <v>0.2714211292979192</v>
       </c>
       <c r="C934" t="n">
-        <v>0.3031735343487112</v>
+        <v>0.2214169514369332</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="n">
-        <v>2712</v>
+        <v>2876</v>
       </c>
       <c r="B935" t="n">
-        <v>0.3264412288584079</v>
+        <v>0.3621596385605007</v>
       </c>
       <c r="C935" t="n">
-        <v>0.1442943257761799</v>
+        <v>0.3001264624162437</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="n">
-        <v>2709</v>
+        <v>2869</v>
       </c>
       <c r="B936" t="n">
-        <v>0.4939588378657578</v>
+        <v>0.3028466178228051</v>
       </c>
       <c r="C936" t="n">
-        <v>0.2190802475832403</v>
+        <v>0.2514092271349473</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="n">
-        <v>2706</v>
+        <v>2866</v>
       </c>
       <c r="B937" t="n">
-        <v>0.5249699465785376</v>
+        <v>0.5621305388653212</v>
       </c>
       <c r="C937" t="n">
-        <v>0.2645897031908594</v>
+        <v>0.2842802165435908</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="n">
-        <v>2682</v>
+        <v>2847</v>
       </c>
       <c r="B938" t="n">
-        <v>0.5625433414490392</v>
+        <v>0.9716356061417373</v>
       </c>
       <c r="C938" t="n">
-        <v>0.3044680867128435</v>
+        <v>0.3338154086735513</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="n">
-        <v>2679</v>
+        <v>2836</v>
       </c>
       <c r="B939" t="n">
-        <v>0.3541714741767636</v>
+        <v>0.3904267181121351</v>
       </c>
       <c r="C939" t="n">
-        <v>0.06094501094141404</v>
+        <v>0.2133157872669535</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="n">
-        <v>2625</v>
+        <v>2832</v>
       </c>
       <c r="B940" t="n">
-        <v>0.3654202605510061</v>
+        <v>0.3790382711651467</v>
       </c>
       <c r="C940" t="n">
-        <v>0.2503071918863281</v>
+        <v>0.2650944331044763</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="n">
-        <v>2594</v>
+        <v>2831</v>
       </c>
       <c r="B941" t="n">
-        <v>0.4142945451402056</v>
+        <v>0.2483639083878845</v>
       </c>
       <c r="C941" t="n">
-        <v>0.2611511206787226</v>
+        <v>0.01380290962039178</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="n">
-        <v>2539</v>
+        <v>2828</v>
       </c>
       <c r="B942" t="n">
-        <v>0.4038754703228204</v>
+        <v>0.3646026641021252</v>
       </c>
       <c r="C942" t="n">
-        <v>0.2985397071204375</v>
+        <v>0.1929013573584469</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="n">
-        <v>2527</v>
+        <v>2823</v>
       </c>
       <c r="B943" t="n">
-        <v>0.3965988724685964</v>
+        <v>0.346862092163365</v>
       </c>
       <c r="C943" t="n">
-        <v>0.2114278737273</v>
+        <v>0.3445169079850843</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="n">
-        <v>2521</v>
+        <v>2817</v>
       </c>
       <c r="B944" t="n">
-        <v>0.2957015831691797</v>
+        <v>0.3399157335318119</v>
       </c>
       <c r="C944" t="n">
-        <v>0.2840673337387752</v>
+        <v>0.2276697801513621</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="n">
-        <v>2517</v>
+        <v>2790</v>
       </c>
       <c r="B945" t="n">
-        <v>0.3363087849791647</v>
+        <v>0.2997899353602586</v>
       </c>
       <c r="C945" t="n">
-        <v>0.3113254017755438</v>
+        <v>0.1221145396483305</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="n">
-        <v>2516</v>
+        <v>2727</v>
       </c>
       <c r="B946" t="n">
-        <v>0.343083214065268</v>
+        <v>0.3850476929669744</v>
       </c>
       <c r="C946" t="n">
-        <v>0.313258377450982</v>
+        <v>0.349660379445293</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="n">
-        <v>2514</v>
+        <v>2723</v>
       </c>
       <c r="B947" t="n">
-        <v>0.2527764711842732</v>
+        <v>0.5018057054083022</v>
       </c>
       <c r="C947" t="n">
-        <v>0.2513373768961785</v>
+        <v>0.1609011691355129</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="n">
-        <v>2512</v>
+        <v>2721</v>
       </c>
       <c r="B948" t="n">
-        <v>0.273151857566635</v>
+        <v>0.4022156496393816</v>
       </c>
       <c r="C948" t="n">
-        <v>0.1187964423359394</v>
+        <v>0.299490970225146</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="n">
-        <v>2511</v>
+        <v>2720</v>
       </c>
       <c r="B949" t="n">
-        <v>0.3487570361908441</v>
+        <v>0.5191699733792394</v>
       </c>
       <c r="C949" t="n">
-        <v>0.3134587448339016</v>
+        <v>0.2442676843335672</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="n">
-        <v>2500</v>
+        <v>2718</v>
       </c>
       <c r="B950" t="n">
-        <v>0.449304286689014</v>
+        <v>0.3739721165609389</v>
       </c>
       <c r="C950" t="n">
-        <v>0.4627160527811268</v>
+        <v>0.3246401199904337</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="n">
-        <v>2499</v>
+        <v>2713</v>
       </c>
       <c r="B951" t="n">
-        <v>0.218333548113914</v>
+        <v>0.4987177669260705</v>
       </c>
       <c r="C951" t="n">
-        <v>0.2244712663557784</v>
+        <v>0.3031934489004169</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="n">
-        <v>2494</v>
+        <v>2712</v>
       </c>
       <c r="B952" t="n">
-        <v>0.2359348707028153</v>
+        <v>0.3257131641442564</v>
       </c>
       <c r="C952" t="n">
-        <v>0.2191699663127435</v>
+        <v>0.1444814173510989</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="n">
-        <v>2493</v>
+        <v>2709</v>
       </c>
       <c r="B953" t="n">
-        <v>0.3462328774211229</v>
+        <v>0.4944038049537199</v>
       </c>
       <c r="C953" t="n">
-        <v>0.06493089511406455</v>
+        <v>0.2191182834675088</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="n">
-        <v>2490</v>
+        <v>2706</v>
       </c>
       <c r="B954" t="n">
-        <v>0.3772691969847144</v>
+        <v>0.5249699465785376</v>
       </c>
       <c r="C954" t="n">
-        <v>0.2409229264989685</v>
+        <v>0.2645897031908594</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="n">
-        <v>2480</v>
+        <v>2682</v>
       </c>
       <c r="B955" t="n">
-        <v>0.4204364442066428</v>
+        <v>0.5625433414490392</v>
       </c>
       <c r="C955" t="n">
-        <v>0.2593369467512701</v>
+        <v>0.3044680867128435</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="n">
-        <v>2454</v>
+        <v>2679</v>
       </c>
       <c r="B956" t="n">
-        <v>0.3256839573775044</v>
+        <v>0.3541714741767636</v>
       </c>
       <c r="C956" t="n">
-        <v>0.3039051105943902</v>
+        <v>0.06094501094141404</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="n">
-        <v>2451</v>
+        <v>2625</v>
       </c>
       <c r="B957" t="n">
-        <v>0.3214188556918863</v>
+        <v>0.3654202605510061</v>
       </c>
       <c r="C957" t="n">
-        <v>0.2464629428161404</v>
+        <v>0.2503071918863281</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="n">
-        <v>2450</v>
+        <v>2594</v>
       </c>
       <c r="B958" t="n">
-        <v>0.306747114992023</v>
+        <v>0.4142945451402056</v>
       </c>
       <c r="C958" t="n">
-        <v>0.1932978309611562</v>
+        <v>0.2611511206787226</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="n">
-        <v>2446</v>
+        <v>2539</v>
       </c>
       <c r="B959" t="n">
-        <v>0.3336972700913136</v>
+        <v>0.4038754703228204</v>
       </c>
       <c r="C959" t="n">
-        <v>0.252150919756107</v>
+        <v>0.2985397071204375</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="n">
-        <v>2444</v>
+        <v>2527</v>
       </c>
       <c r="B960" t="n">
-        <v>0.3265798040591081</v>
+        <v>0.3965988724685964</v>
       </c>
       <c r="C960" t="n">
-        <v>0.2773165992309444</v>
+        <v>0.2114278737273</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="n">
-        <v>2442</v>
+        <v>2521</v>
       </c>
       <c r="B961" t="n">
-        <v>0.3537728971986241</v>
+        <v>0.2957015831691797</v>
       </c>
       <c r="C961" t="n">
-        <v>0.2490159905231921</v>
+        <v>0.2840673337387752</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="n">
-        <v>2434</v>
+        <v>2517</v>
       </c>
       <c r="B962" t="n">
-        <v>0.4134519472321848</v>
+        <v>0.3363087849791647</v>
       </c>
       <c r="C962" t="n">
-        <v>0.3442100769628512</v>
+        <v>0.3113254017755438</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="n">
-        <v>2411</v>
+        <v>2516</v>
       </c>
       <c r="B963" t="n">
-        <v>0.531741398175233</v>
+        <v>0.343083214065268</v>
       </c>
       <c r="C963" t="n">
-        <v>0.308927937451231</v>
+        <v>0.313258377450982</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="n">
-        <v>2406</v>
+        <v>2514</v>
       </c>
       <c r="B964" t="n">
-        <v>0.4917004512519892</v>
+        <v>0.2527764711842732</v>
       </c>
       <c r="C964" t="n">
-        <v>0.4514557359535616</v>
+        <v>0.2513373768961785</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="n">
-        <v>2404</v>
+        <v>2512</v>
       </c>
       <c r="B965" t="n">
-        <v>0.4805392331696089</v>
+        <v>0.273151857566635</v>
       </c>
       <c r="C965" t="n">
-        <v>0.3194397303930547</v>
+        <v>0.1187964423359394</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="n">
-        <v>2399</v>
+        <v>2511</v>
       </c>
       <c r="B966" t="n">
-        <v>0.6723003046328146</v>
+        <v>0.3487570361908441</v>
       </c>
       <c r="C966" t="n">
-        <v>0.3644643434433779</v>
+        <v>0.3134587448339016</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="n">
-        <v>2398</v>
+        <v>2504</v>
       </c>
       <c r="B967" t="n">
-        <v>0.3060747714676981</v>
+        <v>0.2170252922494831</v>
       </c>
       <c r="C967" t="n">
-        <v>0.2862480491878255</v>
+        <v>0.09818340162906836</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="n">
-        <v>2393</v>
+        <v>2500</v>
       </c>
       <c r="B968" t="n">
-        <v>0.2912107516254547</v>
+        <v>0.449304286689014</v>
       </c>
       <c r="C968" t="n">
-        <v>0.2644626162734216</v>
+        <v>0.4627160527811268</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="n">
-        <v>2379</v>
+        <v>2499</v>
       </c>
       <c r="B969" t="n">
-        <v>0.165855503789214</v>
+        <v>0.218333548113914</v>
       </c>
       <c r="C969" t="n">
-        <v>0.03507418513028628</v>
+        <v>0.2244712663557784</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="n">
-        <v>2364</v>
+        <v>2494</v>
       </c>
       <c r="B970" t="n">
-        <v>0.3695700885438269</v>
+        <v>0.2359348707028153</v>
       </c>
       <c r="C970" t="n">
-        <v>0.2344174514756019</v>
+        <v>0.2191699663127435</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="n">
-        <v>2336</v>
+        <v>2493</v>
       </c>
       <c r="B971" t="n">
-        <v>0.4587188415122542</v>
+        <v>0.3462328774211229</v>
       </c>
       <c r="C971" t="n">
-        <v>0.4145871662350363</v>
+        <v>0.06493089511406455</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="n">
-        <v>2330</v>
+        <v>2490</v>
       </c>
       <c r="B972" t="n">
-        <v>0.3186530041125131</v>
+        <v>0.3772691969847144</v>
       </c>
       <c r="C972" t="n">
-        <v>0.2549470827100957</v>
+        <v>0.2409229264989685</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="n">
-        <v>2322</v>
+        <v>2480</v>
       </c>
       <c r="B973" t="n">
-        <v>0.3242736682503169</v>
+        <v>0.4204364442066428</v>
       </c>
       <c r="C973" t="n">
-        <v>0.3225355424415948</v>
+        <v>0.2593369467512701</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="n">
-        <v>2292</v>
+        <v>2454</v>
       </c>
       <c r="B974" t="n">
-        <v>0.2832401594849104</v>
+        <v>0.3256839573775044</v>
       </c>
       <c r="C974" t="n">
-        <v>0.2591146327190964</v>
+        <v>0.3039051105943902</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="n">
-        <v>2291</v>
+        <v>2451</v>
       </c>
       <c r="B975" t="n">
-        <v>0.328277658173659</v>
+        <v>0.3214188556918863</v>
       </c>
       <c r="C975" t="n">
-        <v>0.3600944757742686</v>
+        <v>0.2464629428161404</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="n">
-        <v>2290</v>
+        <v>2450</v>
       </c>
       <c r="B976" t="n">
-        <v>0.2414301041190026</v>
+        <v>0.306747114992023</v>
       </c>
       <c r="C976" t="n">
-        <v>0.09697539965839994</v>
+        <v>0.1932978309611562</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="n">
-        <v>2277</v>
+        <v>2446</v>
       </c>
       <c r="B977" t="n">
-        <v>0.3443508774257961</v>
+        <v>0.3336972700913136</v>
       </c>
       <c r="C977" t="n">
-        <v>0.2154325653961399</v>
+        <v>0.252150919756107</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="n">
-        <v>2271</v>
+        <v>2444</v>
       </c>
       <c r="B978" t="n">
-        <v>0.2635122062175486</v>
+        <v>0.3265798040591081</v>
       </c>
       <c r="C978" t="n">
-        <v>0.2440763055437585</v>
+        <v>0.2773165992309444</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="n">
-        <v>2266</v>
+        <v>2442</v>
       </c>
       <c r="B979" t="n">
-        <v>0.2353845541918275</v>
+        <v>0.3537728971986241</v>
       </c>
       <c r="C979" t="n">
-        <v>0.2367355713089085</v>
+        <v>0.2490159905231921</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="n">
-        <v>2265</v>
+        <v>2434</v>
       </c>
       <c r="B980" t="n">
-        <v>0.249542963220413</v>
+        <v>0.4134519472321848</v>
       </c>
       <c r="C980" t="n">
-        <v>0.267727999055376</v>
+        <v>0.3442100769628512</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="n">
-        <v>2250</v>
+        <v>2411</v>
       </c>
       <c r="B981" t="n">
-        <v>0.2298444807529223</v>
+        <v>0.531741398175233</v>
       </c>
       <c r="C981" t="n">
-        <v>0.2191416387943035</v>
+        <v>0.308927937451231</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="n">
-        <v>2241</v>
+        <v>2406</v>
       </c>
       <c r="B982" t="n">
-        <v>0.5361598451687419</v>
+        <v>0.4917004512519892</v>
       </c>
       <c r="C982" t="n">
-        <v>0.225597429022325</v>
+        <v>0.4514557359535616</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="n">
-        <v>2226</v>
+        <v>2404</v>
       </c>
       <c r="B983" t="n">
-        <v>0.2787117950090887</v>
+        <v>0.4805392331696089</v>
       </c>
       <c r="C983" t="n">
-        <v>0.2717786955460036</v>
+        <v>0.3194397303930547</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="n">
-        <v>2176</v>
+        <v>2399</v>
       </c>
       <c r="B984" t="n">
-        <v>0.9351186067231136</v>
+        <v>0.6723003046328146</v>
       </c>
       <c r="C984" t="n">
-        <v>0.1717133048071366</v>
+        <v>0.3644643434433779</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="n">
-        <v>2168</v>
+        <v>2398</v>
       </c>
       <c r="B985" t="n">
-        <v>0.3612199133303978</v>
+        <v>0.3060747714676981</v>
       </c>
       <c r="C985" t="n">
-        <v>0.3099783876706896</v>
+        <v>0.2862480491878255</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="n">
-        <v>2167</v>
+        <v>2393</v>
       </c>
       <c r="B986" t="n">
-        <v>0.4098353396923721</v>
+        <v>0.2912107516254547</v>
       </c>
       <c r="C986" t="n">
-        <v>0.3109081694071992</v>
+        <v>0.2644626162734216</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="n">
-        <v>2161</v>
+        <v>2379</v>
       </c>
       <c r="B987" t="n">
-        <v>0.3890214381182513</v>
+        <v>0.165855503789214</v>
       </c>
       <c r="C987" t="n">
-        <v>0.2376101952101783</v>
+        <v>0.03507418513028628</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="n">
-        <v>2123</v>
+        <v>2364</v>
       </c>
       <c r="B988" t="n">
-        <v>0.6701774539249614</v>
+        <v>0.3695700885438269</v>
       </c>
       <c r="C988" t="n">
-        <v>0.3808269640019463</v>
+        <v>0.2344174514756019</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="n">
-        <v>2122</v>
+        <v>2336</v>
       </c>
       <c r="B989" t="n">
-        <v>0.3344153990881624</v>
+        <v>0.4587188415122542</v>
       </c>
       <c r="C989" t="n">
-        <v>0.2239418233802891</v>
+        <v>0.4145871662350363</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="n">
-        <v>2107</v>
+        <v>2330</v>
       </c>
       <c r="B990" t="n">
-        <v>0.3631356099551653</v>
+        <v>0.3186530041125131</v>
       </c>
       <c r="C990" t="n">
-        <v>0.2032514028942073</v>
+        <v>0.2549470827100957</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="n">
-        <v>2104</v>
+        <v>2322</v>
       </c>
       <c r="B991" t="n">
-        <v>0.3575556055710235</v>
+        <v>0.3242736682503169</v>
       </c>
       <c r="C991" t="n">
-        <v>0.2931521553522304</v>
+        <v>0.3225355424415948</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="n">
-        <v>2103</v>
+        <v>2292</v>
       </c>
       <c r="B992" t="n">
-        <v>0.3642466182160162</v>
+        <v>0.2832401594849104</v>
       </c>
       <c r="C992" t="n">
-        <v>0.3632169034245849</v>
+        <v>0.2591146327190964</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="n">
-        <v>2098</v>
+        <v>2291</v>
       </c>
       <c r="B993" t="n">
-        <v>0.3002860656087262</v>
+        <v>0.328277658173659</v>
       </c>
       <c r="C993" t="n">
-        <v>0.1670120629315311</v>
+        <v>0.3600944757742686</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="n">
-        <v>2092</v>
+        <v>2290</v>
       </c>
       <c r="B994" t="n">
-        <v>0.2845003038851442</v>
+        <v>0.2414301041190026</v>
       </c>
       <c r="C994" t="n">
-        <v>0.1165339577803334</v>
+        <v>0.09697539965839994</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="n">
-        <v>2082</v>
+        <v>2277</v>
       </c>
       <c r="B995" t="n">
-        <v>0.242063539701362</v>
+        <v>0.3443508774257961</v>
       </c>
       <c r="C995" t="n">
-        <v>0.2527529810582473</v>
+        <v>0.2154325653961399</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="n">
-        <v>2081</v>
+        <v>2271</v>
       </c>
       <c r="B996" t="n">
-        <v>0.2012231939590986</v>
+        <v>0.2635122062175486</v>
       </c>
       <c r="C996" t="n">
-        <v>0.1623456292717326</v>
+        <v>0.2440763055437585</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="n">
-        <v>2079</v>
+        <v>2266</v>
       </c>
       <c r="B997" t="n">
-        <v>0.3678617856362116</v>
+        <v>0.2353845541918275</v>
       </c>
       <c r="C997" t="n">
-        <v>0.2576552492351843</v>
+        <v>0.2367355713089085</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="n">
-        <v>2070</v>
+        <v>2265</v>
       </c>
       <c r="B998" t="n">
-        <v>0.4118919921602884</v>
+        <v>0.249542963220413</v>
       </c>
       <c r="C998" t="n">
-        <v>0.2581567866278275</v>
+        <v>0.267727999055376</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="n">
-        <v>2050</v>
+        <v>2250</v>
       </c>
       <c r="B999" t="n">
-        <v>0.3763951194799018</v>
+        <v>0.2298444807529223</v>
       </c>
       <c r="C999" t="n">
-        <v>0.2686420036966094</v>
+        <v>0.2191416387943035</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="n">
-        <v>2049</v>
+        <v>2241</v>
       </c>
       <c r="B1000" t="n">
-        <v>0.3630586585371207</v>
+        <v>0.5361598451687419</v>
       </c>
       <c r="C1000" t="n">
-        <v>0.3327524968941063</v>
+        <v>0.225597429022325</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="n">
-        <v>2047</v>
+        <v>2226</v>
       </c>
       <c r="B1001" t="n">
-        <v>0.2949171026926352</v>
+        <v>0.2787117950090887</v>
       </c>
       <c r="C1001" t="n">
-        <v>0.2505166472457834</v>
+        <v>0.2717786955460036</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="n">
-        <v>2042</v>
+        <v>2176</v>
       </c>
       <c r="B1002" t="n">
-        <v>0.216565070704672</v>
+        <v>0.9351186067231136</v>
       </c>
       <c r="C1002" t="n">
-        <v>0.2074618137597638</v>
+        <v>0.1717133048071366</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="n">
-        <v>2039</v>
+        <v>2168</v>
       </c>
       <c r="B1003" t="n">
-        <v>0.3385103735515902</v>
+        <v>0.3612199133303978</v>
       </c>
       <c r="C1003" t="n">
-        <v>0.2318680899405047</v>
+        <v>0.3099783876706896</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="n">
-        <v>2038</v>
+        <v>2167</v>
       </c>
       <c r="B1004" t="n">
-        <v>0.3464835114238967</v>
+        <v>0.4098353396923721</v>
       </c>
       <c r="C1004" t="n">
-        <v>0.1574250651051143</v>
+        <v>0.3109081694071992</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="n">
-        <v>1927</v>
+        <v>2161</v>
       </c>
       <c r="B1005" t="n">
-        <v>0.4961275053620846</v>
+        <v>0.3890214381182513</v>
       </c>
       <c r="C1005" t="n">
-        <v>0.2798542605330617</v>
+        <v>0.2376101952101783</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="n">
-        <v>1915</v>
+        <v>2123</v>
       </c>
       <c r="B1006" t="n">
-        <v>0.3499861004857333</v>
+        <v>0.6701774539249614</v>
       </c>
       <c r="C1006" t="n">
-        <v>0.1410078593639557</v>
+        <v>0.3808269640019463</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="n">
-        <v>1913</v>
+        <v>2122</v>
       </c>
       <c r="B1007" t="n">
-        <v>0.2478711486524166</v>
+        <v>0.3344153990881624</v>
       </c>
       <c r="C1007" t="n">
-        <v>0.2095862600500816</v>
+        <v>0.2239418233802891</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="n">
-        <v>1912</v>
+        <v>2107</v>
       </c>
       <c r="B1008" t="n">
-        <v>0.4667514303438227</v>
+        <v>0.3631356099551653</v>
       </c>
       <c r="C1008" t="n">
-        <v>0.243984818003131</v>
+        <v>0.2032514028942073</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="n">
-        <v>1904</v>
+        <v>2104</v>
       </c>
       <c r="B1009" t="n">
-        <v>0.4527414893057691</v>
+        <v>0.3575556055710235</v>
       </c>
       <c r="C1009" t="n">
-        <v>0.2700162631761449</v>
+        <v>0.2931521553522304</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="n">
-        <v>1897</v>
+        <v>2103</v>
       </c>
       <c r="B1010" t="n">
-        <v>0.5952673536868067</v>
+        <v>0.3642466182160162</v>
       </c>
       <c r="C1010" t="n">
-        <v>0.3044906742618847</v>
+        <v>0.3632169034245849</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="n">
-        <v>1893</v>
+        <v>2098</v>
       </c>
       <c r="B1011" t="n">
-        <v>0.358761396645651</v>
+        <v>0.3002860656087262</v>
       </c>
       <c r="C1011" t="n">
-        <v>0.2295736855785919</v>
+        <v>0.1670120629315311</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="n">
-        <v>1891</v>
+        <v>2092</v>
       </c>
       <c r="B1012" t="n">
-        <v>0.2740440437817809</v>
+        <v>0.2845003038851442</v>
       </c>
       <c r="C1012" t="n">
-        <v>0.1376127035374123</v>
+        <v>0.1165339577803334</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="n">
-        <v>1866</v>
+        <v>2082</v>
       </c>
       <c r="B1013" t="n">
-        <v>0.5430997694407427</v>
+        <v>0.242063539701362</v>
       </c>
       <c r="C1013" t="n">
-        <v>0.631022720572067</v>
+        <v>0.2527529810582473</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="n">
-        <v>1832</v>
+        <v>2081</v>
       </c>
       <c r="B1014" t="n">
-        <v>0.2906166316561978</v>
+        <v>0.2012231939590986</v>
       </c>
       <c r="C1014" t="n">
-        <v>0.2826381354273395</v>
+        <v>0.1623456292717326</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="n">
-        <v>1743</v>
+        <v>2079</v>
       </c>
       <c r="B1015" t="n">
-        <v>0.3696648949379892</v>
+        <v>0.3678617856362116</v>
       </c>
       <c r="C1015" t="n">
-        <v>0.3296286229243044</v>
+        <v>0.2576552492351843</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="n">
-        <v>1733</v>
+        <v>2070</v>
       </c>
       <c r="B1016" t="n">
-        <v>0.3713716537993457</v>
+        <v>0.4118919921602884</v>
       </c>
       <c r="C1016" t="n">
-        <v>0.3530850879238085</v>
+        <v>0.2581567866278275</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="n">
-        <v>1730</v>
+        <v>2050</v>
       </c>
       <c r="B1017" t="n">
-        <v>0.2451033171544099</v>
+        <v>0.3763951194799018</v>
       </c>
       <c r="C1017" t="n">
-        <v>0.2424380627916502</v>
+        <v>0.2686420036966094</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="n">
-        <v>1728</v>
+        <v>2049</v>
       </c>
       <c r="B1018" t="n">
-        <v>0.2828203152534864</v>
+        <v>0.3630586585371207</v>
       </c>
       <c r="C1018" t="n">
-        <v>0.2808071153192882</v>
+        <v>0.3327524968941063</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="n">
-        <v>1710</v>
+        <v>2047</v>
       </c>
       <c r="B1019" t="n">
-        <v>0.3604099982577438</v>
+        <v>0.2949171026926352</v>
       </c>
       <c r="C1019" t="n">
-        <v>0.3197838800033547</v>
+        <v>0.2505166472457834</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="n">
-        <v>1702</v>
+        <v>2042</v>
       </c>
       <c r="B1020" t="n">
-        <v>0.3159855099363813</v>
+        <v>0.216565070704672</v>
       </c>
       <c r="C1020" t="n">
-        <v>0.300054493021973</v>
+        <v>0.2074618137597638</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="n">
-        <v>1678</v>
+        <v>2039</v>
       </c>
       <c r="B1021" t="n">
-        <v>0.2905058115460306</v>
+        <v>0.3385103735515902</v>
       </c>
       <c r="C1021" t="n">
-        <v>0.2671926424950811</v>
+        <v>0.2318680899405047</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="n">
-        <v>1660</v>
+        <v>2038</v>
       </c>
       <c r="B1022" t="n">
-        <v>0.4600106870564355</v>
+        <v>0.3464835114238967</v>
       </c>
       <c r="C1022" t="n">
-        <v>0.3468653886717077</v>
+        <v>0.1574250651051143</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="n">
-        <v>1642</v>
+        <v>1927</v>
       </c>
       <c r="B1023" t="n">
-        <v>0.3136396576779081</v>
+        <v>0.4961275053620846</v>
       </c>
       <c r="C1023" t="n">
-        <v>0.2679130611294995</v>
+        <v>0.2798542605330617</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="n">
-        <v>1599</v>
+        <v>1915</v>
       </c>
       <c r="B1024" t="n">
-        <v>0.4272069938541936</v>
+        <v>0.3499861004857333</v>
       </c>
       <c r="C1024" t="n">
-        <v>0.2596414163757593</v>
+        <v>0.1410078593639557</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="n">
-        <v>1595</v>
+        <v>1913</v>
       </c>
       <c r="B1025" t="n">
-        <v>0.5332210419796941</v>
+        <v>0.2478711486524166</v>
       </c>
       <c r="C1025" t="n">
-        <v>0.1347754064209462</v>
+        <v>0.2095862600500816</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="n">
-        <v>1588</v>
+        <v>1912</v>
       </c>
       <c r="B1026" t="n">
-        <v>0.6120448268569699</v>
+        <v>0.4667514303438227</v>
       </c>
       <c r="C1026" t="n">
-        <v>0.4483669054669033</v>
+        <v>0.243984818003131</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="n">
-        <v>1573</v>
+        <v>1904</v>
       </c>
       <c r="B1027" t="n">
-        <v>0.3680836646117465</v>
+        <v>0.4527414893057691</v>
       </c>
       <c r="C1027" t="n">
-        <v>0.2771593831911724</v>
+        <v>0.2700162631761449</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="n">
-        <v>1572</v>
+        <v>1893</v>
       </c>
       <c r="B1028" t="n">
-        <v>0.3056782148877957</v>
+        <v>0.358761396645651</v>
       </c>
       <c r="C1028" t="n">
-        <v>0.216419954801662</v>
+        <v>0.2295736855785919</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="n">
-        <v>1571</v>
+        <v>1891</v>
       </c>
       <c r="B1029" t="n">
-        <v>0.3266083861411698</v>
+        <v>0.2740440437817809</v>
       </c>
       <c r="C1029" t="n">
-        <v>0.2604978500089583</v>
+        <v>0.1376127035374123</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="n">
-        <v>1556</v>
+        <v>1866</v>
       </c>
       <c r="B1030" t="n">
-        <v>0.3491292839552692</v>
+        <v>0.2918302256248075</v>
       </c>
       <c r="C1030" t="n">
-        <v>0.3344118592769912</v>
+        <v>0.1736366390812027</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="n">
-        <v>1554</v>
+        <v>1832</v>
       </c>
       <c r="B1031" t="n">
-        <v>0.3963922893801808</v>
+        <v>0.2906166316561978</v>
       </c>
       <c r="C1031" t="n">
-        <v>0.2341916215875826</v>
+        <v>0.2826381354273395</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="n">
-        <v>1464</v>
+        <v>1743</v>
       </c>
       <c r="B1032" t="n">
-        <v>0.3010602079140953</v>
+        <v>0.3696648949379892</v>
       </c>
       <c r="C1032" t="n">
-        <v>0.2858892566013299</v>
+        <v>0.3296286229243044</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="n">
-        <v>1439</v>
+        <v>1733</v>
       </c>
       <c r="B1033" t="n">
-        <v>0.3433161159648999</v>
+        <v>0.3713716537993457</v>
       </c>
       <c r="C1033" t="n">
-        <v>0.3085796695198688</v>
+        <v>0.3530850879238085</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="n">
-        <v>1417</v>
+        <v>1730</v>
       </c>
       <c r="B1034" t="n">
-        <v>0.3061398020215746</v>
+        <v>0.2451033171544099</v>
       </c>
       <c r="C1034" t="n">
-        <v>0.2140457657958267</v>
+        <v>0.2424380627916502</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="n">
-        <v>1416</v>
+        <v>1728</v>
       </c>
       <c r="B1035" t="n">
-        <v>0.3224488211762996</v>
+        <v>0.2828203152534864</v>
       </c>
       <c r="C1035" t="n">
-        <v>0.2775652192866581</v>
+        <v>0.2808071153192882</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="n">
-        <v>1403</v>
+        <v>1710</v>
       </c>
       <c r="B1036" t="n">
-        <v>0.4767738695999163</v>
+        <v>0.3604099982577438</v>
       </c>
       <c r="C1036" t="n">
-        <v>0.3191843236861006</v>
+        <v>0.3197838800033547</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="n">
-        <v>1402</v>
+        <v>1702</v>
       </c>
       <c r="B1037" t="n">
-        <v>0.3365430801371554</v>
+        <v>0.3159459951964869</v>
       </c>
       <c r="C1037" t="n">
-        <v>0.2529235157359597</v>
+        <v>0.3000252268536175</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="n">
-        <v>1400</v>
+        <v>1678</v>
       </c>
       <c r="B1038" t="n">
-        <v>0.3466304408032501</v>
+        <v>0.2905058115460306</v>
       </c>
       <c r="C1038" t="n">
-        <v>0.2801177793918653</v>
+        <v>0.2671926424950811</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="n">
-        <v>1396</v>
+        <v>1660</v>
       </c>
       <c r="B1039" t="n">
-        <v>0.4684675832083423</v>
+        <v>0.4600106870564355</v>
       </c>
       <c r="C1039" t="n">
-        <v>0.2424721111080126</v>
+        <v>0.3468653886717077</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="n">
-        <v>1393</v>
+        <v>1642</v>
       </c>
       <c r="B1040" t="n">
-        <v>0.5154949318512225</v>
+        <v>0.3136396576779081</v>
       </c>
       <c r="C1040" t="n">
-        <v>0.2140629185495821</v>
+        <v>0.2679130611294995</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="n">
-        <v>1391</v>
+        <v>1599</v>
       </c>
       <c r="B1041" t="n">
-        <v>0.3038678905602508</v>
+        <v>0.4272069938541936</v>
       </c>
       <c r="C1041" t="n">
-        <v>0.3238217999474974</v>
+        <v>0.2596414163757593</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="n">
-        <v>1384</v>
+        <v>1595</v>
       </c>
       <c r="B1042" t="n">
-        <v>0.3668005759933306</v>
+        <v>0.5332210419796941</v>
       </c>
       <c r="C1042" t="n">
-        <v>0.2417215637378658</v>
+        <v>0.1347754064209462</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="n">
-        <v>1383</v>
+        <v>1588</v>
       </c>
       <c r="B1043" t="n">
-        <v>0.224862941975503</v>
+        <v>0.6120448268569699</v>
       </c>
       <c r="C1043" t="n">
-        <v>0.2057436499530833</v>
+        <v>0.4483669054669033</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="n">
-        <v>1379</v>
+        <v>1573</v>
       </c>
       <c r="B1044" t="n">
-        <v>0.3236985024052877</v>
+        <v>0.3680836646117465</v>
       </c>
       <c r="C1044" t="n">
-        <v>0.2878606654727463</v>
+        <v>0.2771593831911724</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="n">
-        <v>1378</v>
+        <v>1572</v>
       </c>
       <c r="B1045" t="n">
-        <v>0.5367323758413486</v>
+        <v>0.3056782148877957</v>
       </c>
       <c r="C1045" t="n">
-        <v>0.3487832074396544</v>
+        <v>0.216419954801662</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="n">
-        <v>1366</v>
+        <v>1571</v>
       </c>
       <c r="B1046" t="n">
-        <v>0.3622959532981296</v>
+        <v>0.3266083861411698</v>
       </c>
       <c r="C1046" t="n">
-        <v>0.2715451144286611</v>
+        <v>0.2604978500089583</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="n">
-        <v>1364</v>
+        <v>1564</v>
       </c>
       <c r="B1047" t="n">
-        <v>0.3736391041842588</v>
+        <v>0.3063067845372589</v>
       </c>
       <c r="C1047" t="n">
-        <v>0.2159180931019986</v>
+        <v>0.08107547311784448</v>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="n">
-        <v>1363</v>
+        <v>1556</v>
       </c>
       <c r="B1048" t="n">
-        <v>0.5125065854344164</v>
+        <v>0.3491292839552692</v>
       </c>
       <c r="C1048" t="n">
-        <v>0.2836848456536687</v>
+        <v>0.3344118592769912</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="n">
-        <v>1356</v>
+        <v>1554</v>
       </c>
       <c r="B1049" t="n">
-        <v>0.361302741826173</v>
+        <v>0.3963922893801808</v>
       </c>
       <c r="C1049" t="n">
-        <v>0.3379276609424133</v>
+        <v>0.2341916215875826</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="n">
-        <v>1353</v>
+        <v>1464</v>
       </c>
       <c r="B1050" t="n">
-        <v>0.3792550340211615</v>
+        <v>0.3010602079140953</v>
       </c>
       <c r="C1050" t="n">
-        <v>0.3028919671011683</v>
+        <v>0.2858892566013299</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="n">
-        <v>1336</v>
+        <v>1439</v>
       </c>
       <c r="B1051" t="n">
-        <v>0.4665378173135679</v>
+        <v>0.3433161159648999</v>
       </c>
       <c r="C1051" t="n">
-        <v>0.1963811247277241</v>
+        <v>0.3085796695198688</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="n">
-        <v>1305</v>
+        <v>1417</v>
       </c>
       <c r="B1052" t="n">
-        <v>0.244001669215253</v>
+        <v>0.3061398020215746</v>
       </c>
       <c r="C1052" t="n">
-        <v>0.2026103520783286</v>
+        <v>0.2140457657958267</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="n">
-        <v>1295</v>
+        <v>1416</v>
       </c>
       <c r="B1053" t="n">
-        <v>0.8479654190537641</v>
+        <v>0.3219435497736335</v>
       </c>
       <c r="C1053" t="n">
-        <v>0.1341532218102933</v>
+        <v>0.2775411325723787</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="n">
-        <v>1268</v>
+        <v>1403</v>
       </c>
       <c r="B1054" t="n">
-        <v>0.2856940354249143</v>
+        <v>0.4767738695999163</v>
       </c>
       <c r="C1054" t="n">
-        <v>0.2286444789536544</v>
+        <v>0.3191843236861006</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="n">
-        <v>1250</v>
+        <v>1402</v>
       </c>
       <c r="B1055" t="n">
-        <v>0.4255025872738121</v>
+        <v>0.3365430801371554</v>
       </c>
       <c r="C1055" t="n">
-        <v>0.3037894110783994</v>
+        <v>0.2529235157359597</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="n">
-        <v>1248</v>
+        <v>1400</v>
       </c>
       <c r="B1056" t="n">
-        <v>0.4683022631303216</v>
+        <v>0.3466304408032501</v>
       </c>
       <c r="C1056" t="n">
-        <v>0.1040002867659578</v>
+        <v>0.2801177793918653</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="n">
-        <v>1241</v>
+        <v>1396</v>
       </c>
       <c r="B1057" t="n">
-        <v>0.3722778112516296</v>
+        <v>0.4684675832083423</v>
       </c>
       <c r="C1057" t="n">
-        <v>0.2161269739978536</v>
+        <v>0.2424721111080126</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="n">
-        <v>1240</v>
+        <v>1393</v>
       </c>
       <c r="B1058" t="n">
-        <v>0.37364887817584</v>
+        <v>0.5154949318512225</v>
       </c>
       <c r="C1058" t="n">
-        <v>0.2709274329176925</v>
+        <v>0.2140629185495821</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="n">
-        <v>1239</v>
+        <v>1391</v>
       </c>
       <c r="B1059" t="n">
-        <v>0.5084881520333252</v>
+        <v>0.3038678905602508</v>
       </c>
       <c r="C1059" t="n">
-        <v>0.1654749895333653</v>
+        <v>0.3238217999474974</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="n">
-        <v>1233</v>
+        <v>1384</v>
       </c>
       <c r="B1060" t="n">
-        <v>0.3532384090060772</v>
+        <v>0.3668005759933306</v>
       </c>
       <c r="C1060" t="n">
-        <v>0.3417538804646136</v>
+        <v>0.2417215637378658</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="n">
-        <v>1217</v>
+        <v>1383</v>
       </c>
       <c r="B1061" t="n">
-        <v>0.2923865924597778</v>
+        <v>0.224862941975503</v>
       </c>
       <c r="C1061" t="n">
-        <v>0.2153029025494186</v>
+        <v>0.2057436499530833</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="n">
-        <v>1167</v>
+        <v>1379</v>
       </c>
       <c r="B1062" t="n">
-        <v>0.3074539675937367</v>
+        <v>0.3236985024052877</v>
       </c>
       <c r="C1062" t="n">
-        <v>0.2569797244866293</v>
+        <v>0.2878606654727463</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="n">
-        <v>1131</v>
+        <v>1378</v>
       </c>
       <c r="B1063" t="n">
-        <v>0.2717186444530582</v>
+        <v>0.5367323758413486</v>
       </c>
       <c r="C1063" t="n">
-        <v>0.1636680519382082</v>
+        <v>0.3487832074396544</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="n">
-        <v>1122</v>
+        <v>1366</v>
       </c>
       <c r="B1064" t="n">
-        <v>0.2661758322092959</v>
+        <v>0.3622959532981296</v>
       </c>
       <c r="C1064" t="n">
-        <v>0.1727194409237921</v>
+        <v>0.2715451144286611</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="n">
-        <v>1104</v>
+        <v>1364</v>
       </c>
       <c r="B1065" t="n">
-        <v>0.3391467084484838</v>
+        <v>0.3736391041842588</v>
       </c>
       <c r="C1065" t="n">
-        <v>0.2360393614459759</v>
+        <v>0.2159180931019986</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="n">
-        <v>1091</v>
+        <v>1363</v>
       </c>
       <c r="B1066" t="n">
-        <v>0.4384108213785287</v>
+        <v>0.5125065854344164</v>
       </c>
       <c r="C1066" t="n">
-        <v>0.2665945877468868</v>
+        <v>0.2836848456536687</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="n">
-        <v>1082</v>
+        <v>1356</v>
       </c>
       <c r="B1067" t="n">
-        <v>0.3601446404992924</v>
+        <v>0.361302741826173</v>
       </c>
       <c r="C1067" t="n">
-        <v>0.2616433449383033</v>
+        <v>0.3379276609424133</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="n">
-        <v>1073</v>
+        <v>1353</v>
       </c>
       <c r="B1068" t="n">
-        <v>0.6398305346014062</v>
+        <v>0.3792550340211615</v>
       </c>
       <c r="C1068" t="n">
-        <v>0.4583428845529319</v>
+        <v>0.3028919671011683</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="n">
-        <v>1068</v>
+        <v>1336</v>
       </c>
       <c r="B1069" t="n">
-        <v>0.2911274489320548</v>
+        <v>0.4665378173135679</v>
       </c>
       <c r="C1069" t="n">
-        <v>0.2301516306480158</v>
+        <v>0.1963811247277241</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="n">
-        <v>1047</v>
+        <v>1305</v>
       </c>
       <c r="B1070" t="n">
-        <v>0.3327505383402943</v>
+        <v>0.244001669215253</v>
       </c>
       <c r="C1070" t="n">
-        <v>0.1820425028362132</v>
+        <v>0.2026103520783286</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="n">
-        <v>1040</v>
+        <v>1295</v>
       </c>
       <c r="B1071" t="n">
-        <v>0.330150910124593</v>
+        <v>0.8479654190537641</v>
       </c>
       <c r="C1071" t="n">
-        <v>0.1629073369271821</v>
+        <v>0.1341532218102933</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="n">
-        <v>1012</v>
+        <v>1268</v>
       </c>
       <c r="B1072" t="n">
-        <v>0.3067531754481663</v>
+        <v>0.2856940354249143</v>
       </c>
       <c r="C1072" t="n">
-        <v>0.1348061704421278</v>
+        <v>0.2286444789536544</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="n">
-        <v>1008</v>
+        <v>1250</v>
       </c>
       <c r="B1073" t="n">
-        <v>0.4151207924604117</v>
+        <v>0.4255025872738121</v>
       </c>
       <c r="C1073" t="n">
-        <v>0.37291336608083</v>
+        <v>0.3037894110783994</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="n">
-        <v>1004</v>
+        <v>1248</v>
       </c>
       <c r="B1074" t="n">
-        <v>0.5051707377919983</v>
+        <v>0.4683022631303216</v>
       </c>
       <c r="C1074" t="n">
-        <v>0.199511832728445</v>
+        <v>0.1040002867659578</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="n">
-        <v>1001</v>
+        <v>1241</v>
       </c>
       <c r="B1075" t="n">
-        <v>0.3601669417242355</v>
+        <v>0.3722778112516296</v>
       </c>
       <c r="C1075" t="n">
-        <v>0.3559112651971137</v>
+        <v>0.2161269739978536</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="n">
-        <v>997</v>
+        <v>1240</v>
       </c>
       <c r="B1076" t="n">
-        <v>0.3630946729639685</v>
+        <v>0.37364887817584</v>
       </c>
       <c r="C1076" t="n">
-        <v>0.1720256051331531</v>
+        <v>0.2709274329176925</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="n">
-        <v>994</v>
+        <v>1239</v>
       </c>
       <c r="B1077" t="n">
-        <v>0.356920472627927</v>
+        <v>0.5084881520333252</v>
       </c>
       <c r="C1077" t="n">
-        <v>0.3378468750050675</v>
+        <v>0.1654749895333653</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="n">
-        <v>991</v>
+        <v>1233</v>
       </c>
       <c r="B1078" t="n">
-        <v>0.5353930463045027</v>
+        <v>0.3532384090060772</v>
       </c>
       <c r="C1078" t="n">
-        <v>0.2520676023836391</v>
+        <v>0.3417538804646136</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="n">
-        <v>983</v>
+        <v>1217</v>
       </c>
       <c r="B1079" t="n">
-        <v>0.3628047134430963</v>
+        <v>0.2923865924597778</v>
       </c>
       <c r="C1079" t="n">
-        <v>0.2852976988093481</v>
+        <v>0.2153029025494186</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="n">
-        <v>976</v>
+        <v>1167</v>
       </c>
       <c r="B1080" t="n">
-        <v>0.2408290568146572</v>
+        <v>0.3074539675937367</v>
       </c>
       <c r="C1080" t="n">
-        <v>0.1889405075179968</v>
+        <v>0.2569797244866293</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="n">
-        <v>963</v>
+        <v>1131</v>
       </c>
       <c r="B1081" t="n">
-        <v>0.3785074702614452</v>
+        <v>0.2717186444530582</v>
       </c>
       <c r="C1081" t="n">
-        <v>0.2638599319750121</v>
+        <v>0.1636680519382082</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="n">
-        <v>913</v>
+        <v>1122</v>
       </c>
       <c r="B1082" t="n">
-        <v>0.3551857848842614</v>
+        <v>0.2661758322092959</v>
       </c>
       <c r="C1082" t="n">
-        <v>0.308143119757854</v>
+        <v>0.1727194409237921</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="n">
-        <v>887</v>
+        <v>1104</v>
       </c>
       <c r="B1083" t="n">
-        <v>0.3465857844068893</v>
+        <v>0.3391467084484838</v>
       </c>
       <c r="C1083" t="n">
-        <v>0.3292585193719837</v>
+        <v>0.2360393614459759</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="n">
-        <v>884</v>
+        <v>1091</v>
       </c>
       <c r="B1084" t="n">
-        <v>0.3260924758049802</v>
+        <v>0.4384108213785287</v>
       </c>
       <c r="C1084" t="n">
-        <v>0.2680718881352154</v>
+        <v>0.2665945877468868</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="n">
-        <v>883</v>
+        <v>1082</v>
       </c>
       <c r="B1085" t="n">
-        <v>0.3373351996681215</v>
+        <v>0.3601446404992924</v>
       </c>
       <c r="C1085" t="n">
-        <v>0.2855467521538311</v>
+        <v>0.2616433449383033</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="n">
-        <v>879</v>
+        <v>1073</v>
       </c>
       <c r="B1086" t="n">
-        <v>0.3343481531119022</v>
+        <v>0.4594318744498183</v>
       </c>
       <c r="C1086" t="n">
-        <v>0.1986999372952519</v>
+        <v>0.3492346797368943</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="n">
-        <v>876</v>
+        <v>1068</v>
       </c>
       <c r="B1087" t="n">
-        <v>0.3805467434749932</v>
+        <v>0.2911274489320548</v>
       </c>
       <c r="C1087" t="n">
-        <v>0.1996424210516161</v>
+        <v>0.2301516306480158</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="n">
-        <v>856</v>
+        <v>1047</v>
       </c>
       <c r="B1088" t="n">
-        <v>0.3661734280532175</v>
+        <v>0.3327505383402943</v>
       </c>
       <c r="C1088" t="n">
-        <v>0.2780813554144335</v>
+        <v>0.1820425028362132</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="n">
-        <v>762</v>
+        <v>1040</v>
       </c>
       <c r="B1089" t="n">
-        <v>0.4353174094357232</v>
+        <v>0.330150910124593</v>
       </c>
       <c r="C1089" t="n">
-        <v>0.4257667882127271</v>
+        <v>0.1629073369271821</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="n">
-        <v>728</v>
+        <v>1012</v>
       </c>
       <c r="B1090" t="n">
-        <v>0.3485607284431029</v>
+        <v>0.3067531754481663</v>
       </c>
       <c r="C1090" t="n">
-        <v>0.2998804957661387</v>
+        <v>0.1348061704421278</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="n">
-        <v>715</v>
+        <v>1008</v>
       </c>
       <c r="B1091" t="n">
-        <v>0.2589388501514078</v>
+        <v>0.4151207924604117</v>
       </c>
       <c r="C1091" t="n">
-        <v>0.2492542556420061</v>
+        <v>0.37291336608083</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="n">
-        <v>710</v>
+        <v>1007</v>
       </c>
       <c r="B1092" t="n">
-        <v>0.5244581046230032</v>
+        <v>0.3430203786367698</v>
       </c>
       <c r="C1092" t="n">
-        <v>0.5056519504477275</v>
+        <v>0.1618570445777889</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="n">
-        <v>703</v>
+        <v>1004</v>
       </c>
       <c r="B1093" t="n">
-        <v>0.3591524328921668</v>
+        <v>0.5051707377919983</v>
       </c>
       <c r="C1093" t="n">
-        <v>0.3524377268447766</v>
+        <v>0.199511832728445</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="n">
-        <v>689</v>
+        <v>1001</v>
       </c>
       <c r="B1094" t="n">
-        <v>0.3615455592234132</v>
+        <v>0.3601669417242355</v>
       </c>
       <c r="C1094" t="n">
-        <v>0.1922224446063755</v>
+        <v>0.3559112651971137</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="n">
-        <v>688</v>
+        <v>997</v>
       </c>
       <c r="B1095" t="n">
-        <v>0.4535207134762662</v>
+        <v>0.3630946729639685</v>
       </c>
       <c r="C1095" t="n">
-        <v>0.325839896381712</v>
+        <v>0.1720256051331531</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="n">
-        <v>683</v>
+        <v>994</v>
       </c>
       <c r="B1096" t="n">
-        <v>0.2551187806420429</v>
+        <v>0.356920472627927</v>
       </c>
       <c r="C1096" t="n">
-        <v>0.1795645385551142</v>
+        <v>0.3378468750050675</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="n">
-        <v>676</v>
+        <v>991</v>
       </c>
       <c r="B1097" t="n">
-        <v>0.3567109654739428</v>
+        <v>0.5353930463045027</v>
       </c>
       <c r="C1097" t="n">
-        <v>0.2314730579761952</v>
+        <v>0.2520676023836391</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="n">
-        <v>675</v>
+        <v>983</v>
       </c>
       <c r="B1098" t="n">
-        <v>0.3148308475076089</v>
+        <v>0.3628047134430963</v>
       </c>
       <c r="C1098" t="n">
-        <v>0.1591497240235305</v>
+        <v>0.2852976988093481</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="n">
-        <v>667</v>
+        <v>976</v>
       </c>
       <c r="B1099" t="n">
-        <v>0.3353321191371518</v>
+        <v>0.2408290568146572</v>
       </c>
       <c r="C1099" t="n">
-        <v>0.2763087271190408</v>
+        <v>0.1889405075179968</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="n">
-        <v>666</v>
+        <v>963</v>
       </c>
       <c r="B1100" t="n">
-        <v>0.3887223713272476</v>
+        <v>0.3785074702614452</v>
       </c>
       <c r="C1100" t="n">
-        <v>0.2985982679059941</v>
+        <v>0.2638599319750121</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="n">
-        <v>664</v>
+        <v>913</v>
       </c>
       <c r="B1101" t="n">
-        <v>0.4566625410383857</v>
+        <v>0.3551857848842614</v>
       </c>
       <c r="C1101" t="n">
-        <v>0.1897301072990412</v>
+        <v>0.308143119757854</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="n">
-        <v>663</v>
+        <v>887</v>
       </c>
       <c r="B1102" t="n">
-        <v>0.3418847466956743</v>
+        <v>0.3465857844068893</v>
       </c>
       <c r="C1102" t="n">
-        <v>0.2903068653806908</v>
+        <v>0.3292585193719837</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="n">
-        <v>643</v>
+        <v>884</v>
       </c>
       <c r="B1103" t="n">
-        <v>0.4943734062629896</v>
+        <v>0.3260924758049802</v>
       </c>
       <c r="C1103" t="n">
-        <v>0.2743916587341739</v>
+        <v>0.2680718881352154</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="n">
-        <v>641</v>
+        <v>883</v>
       </c>
       <c r="B1104" t="n">
-        <v>0.3543957561670881</v>
+        <v>0.3373351996681215</v>
       </c>
       <c r="C1104" t="n">
-        <v>0.3157604025369849</v>
+        <v>0.2855467521538311</v>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="n">
-        <v>634</v>
+        <v>879</v>
       </c>
       <c r="B1105" t="n">
-        <v>0.4884074182396874</v>
+        <v>0.3343481531119022</v>
       </c>
       <c r="C1105" t="n">
-        <v>0.2664130362268205</v>
+        <v>0.1986999372952519</v>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="n">
-        <v>620</v>
+        <v>876</v>
       </c>
       <c r="B1106" t="n">
-        <v>0.5357586221152316</v>
+        <v>0.3805467434749932</v>
       </c>
       <c r="C1106" t="n">
-        <v>0.3333746865000109</v>
+        <v>0.1996424210516161</v>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="n">
-        <v>619</v>
+        <v>856</v>
       </c>
       <c r="B1107" t="n">
-        <v>0.5646428731061034</v>
+        <v>0.3661734280532175</v>
       </c>
       <c r="C1107" t="n">
-        <v>0.3226684765109895</v>
+        <v>0.2780813554144335</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="n">
-        <v>617</v>
+        <v>762</v>
       </c>
       <c r="B1108" t="n">
-        <v>0.6033783324681763</v>
+        <v>0.4362061291556342</v>
       </c>
       <c r="C1108" t="n">
-        <v>0.3711520901638845</v>
+        <v>0.4276964828076878</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="n">
-        <v>613</v>
+        <v>728</v>
       </c>
       <c r="B1109" t="n">
-        <v>0.3440570213965753</v>
+        <v>0.3485607284431029</v>
       </c>
       <c r="C1109" t="n">
-        <v>0.3337385277062161</v>
+        <v>0.2998804957661387</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="n">
-        <v>612</v>
+        <v>715</v>
       </c>
       <c r="B1110" t="n">
-        <v>0.5163250813375736</v>
+        <v>0.2589388501514078</v>
       </c>
       <c r="C1110" t="n">
-        <v>0.2876565628282416</v>
+        <v>0.2492542556420061</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="n">
-        <v>609</v>
+        <v>710</v>
       </c>
       <c r="B1111" t="n">
-        <v>0.5459718990857361</v>
+        <v>0.5244581046230032</v>
       </c>
       <c r="C1111" t="n">
-        <v>0.3309883992890583</v>
+        <v>0.5056519504477275</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="n">
-        <v>607</v>
+        <v>703</v>
       </c>
       <c r="B1112" t="n">
-        <v>0.4458916397083664</v>
+        <v>0.3591524328921668</v>
       </c>
       <c r="C1112" t="n">
-        <v>0.2986216382865483</v>
+        <v>0.3524377268447766</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="n">
-        <v>602</v>
+        <v>689</v>
       </c>
       <c r="B1113" t="n">
-        <v>0.3722972390158685</v>
+        <v>0.3615455592234132</v>
       </c>
       <c r="C1113" t="n">
-        <v>0.2233328976219193</v>
+        <v>0.1922224446063755</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="n">
-        <v>594</v>
+        <v>688</v>
       </c>
       <c r="B1114" t="n">
-        <v>0.3399215690806617</v>
+        <v>0.4535207134762662</v>
       </c>
       <c r="C1114" t="n">
-        <v>0.2310363020399777</v>
+        <v>0.325839896381712</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="n">
-        <v>593</v>
+        <v>683</v>
       </c>
       <c r="B1115" t="n">
-        <v>0.3320283267086759</v>
+        <v>0.2551187806420429</v>
       </c>
       <c r="C1115" t="n">
-        <v>0.2542393894907791</v>
+        <v>0.1795645385551142</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="n">
-        <v>589</v>
+        <v>676</v>
       </c>
       <c r="B1116" t="n">
-        <v>0.2480210315699611</v>
+        <v>0.3567109654739428</v>
       </c>
       <c r="C1116" t="n">
-        <v>0.0626501023053334</v>
+        <v>0.2314730579761952</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="n">
-        <v>568</v>
+        <v>675</v>
       </c>
       <c r="B1117" t="n">
-        <v>0.5348144217052087</v>
+        <v>0.3148308475076089</v>
       </c>
       <c r="C1117" t="n">
-        <v>0.4817852561827354</v>
+        <v>0.1591497240235305</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="n">
-        <v>564</v>
+        <v>667</v>
       </c>
       <c r="B1118" t="n">
-        <v>0.3839432190299117</v>
+        <v>0.3353321191371518</v>
       </c>
       <c r="C1118" t="n">
-        <v>0.2559023588795094</v>
+        <v>0.2763087271190408</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="n">
-        <v>562</v>
+        <v>666</v>
       </c>
       <c r="B1119" t="n">
-        <v>0.3779649563584072</v>
+        <v>0.3887223713272476</v>
       </c>
       <c r="C1119" t="n">
-        <v>0.3611567934388646</v>
+        <v>0.2985982679059941</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="n">
-        <v>546</v>
+        <v>664</v>
       </c>
       <c r="B1120" t="n">
-        <v>0.3202937101094996</v>
+        <v>0.4566625410383857</v>
       </c>
       <c r="C1120" t="n">
-        <v>0.2794628725556555</v>
+        <v>0.1897301072990412</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="n">
-        <v>544</v>
+        <v>663</v>
       </c>
       <c r="B1121" t="n">
-        <v>0.3590367057577712</v>
+        <v>0.3418847466956743</v>
       </c>
       <c r="C1121" t="n">
-        <v>0.2885262033772404</v>
+        <v>0.2903068653806908</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="n">
-        <v>533</v>
+        <v>643</v>
       </c>
       <c r="B1122" t="n">
-        <v>0.3517907505094081</v>
+        <v>0.4943734062629896</v>
       </c>
       <c r="C1122" t="n">
-        <v>0.2683683142835063</v>
+        <v>0.2743916587341739</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="n">
-        <v>525</v>
+        <v>641</v>
       </c>
       <c r="B1123" t="n">
-        <v>0.3365374921657849</v>
+        <v>0.3543957561670881</v>
       </c>
       <c r="C1123" t="n">
-        <v>0.2753415854725687</v>
+        <v>0.3157604025369849</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="n">
-        <v>492</v>
+        <v>634</v>
       </c>
       <c r="B1124" t="n">
-        <v>0.3081868086850818</v>
+        <v>0.4884074182396874</v>
       </c>
       <c r="C1124" t="n">
-        <v>0.2034236192545361</v>
+        <v>0.2664130362268205</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="n">
-        <v>470</v>
+        <v>620</v>
       </c>
       <c r="B1125" t="n">
-        <v>0.3657319839094679</v>
+        <v>0.5357586221152316</v>
       </c>
       <c r="C1125" t="n">
-        <v>0.3167216654272322</v>
+        <v>0.3333746865000109</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="n">
-        <v>469</v>
+        <v>619</v>
       </c>
       <c r="B1126" t="n">
-        <v>0.5129694368684958</v>
+        <v>0.5646428731061034</v>
       </c>
       <c r="C1126" t="n">
-        <v>0.4073873210694758</v>
+        <v>0.3226684765109895</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="n">
-        <v>422</v>
+        <v>617</v>
       </c>
       <c r="B1127" t="n">
-        <v>0.4220577970203784</v>
+        <v>0.6033783324681763</v>
       </c>
       <c r="C1127" t="n">
-        <v>0.2797780994255004</v>
+        <v>0.3711520901638845</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="n">
-        <v>408</v>
+        <v>613</v>
       </c>
       <c r="B1128" t="n">
-        <v>0.5055553259058945</v>
+        <v>0.3440570213965753</v>
       </c>
       <c r="C1128" t="n">
-        <v>0.3289547267588889</v>
+        <v>0.3337385277062161</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="n">
-        <v>404</v>
+        <v>612</v>
       </c>
       <c r="B1129" t="n">
-        <v>0.4917629056610113</v>
+        <v>0.5163250813375736</v>
       </c>
       <c r="C1129" t="n">
-        <v>0.3227668565900211</v>
+        <v>0.2876565628282416</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="n">
-        <v>400</v>
+        <v>609</v>
       </c>
       <c r="B1130" t="n">
-        <v>0.489544680875939</v>
+        <v>0.5459718990857361</v>
       </c>
       <c r="C1130" t="n">
-        <v>0.4593864455640758</v>
+        <v>0.3309883992890583</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="n">
-        <v>399</v>
+        <v>607</v>
       </c>
       <c r="B1131" t="n">
-        <v>0.3891082115478011</v>
+        <v>0.4458916397083664</v>
       </c>
       <c r="C1131" t="n">
-        <v>0.3432206406128681</v>
+        <v>0.2986216382865483</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="n">
-        <v>384</v>
+        <v>602</v>
       </c>
       <c r="B1132" t="n">
-        <v>0.3586155263237701</v>
+        <v>0.3722972390158685</v>
       </c>
       <c r="C1132" t="n">
-        <v>0.2889873212971075</v>
+        <v>0.2233328976219193</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="n">
-        <v>377</v>
+        <v>594</v>
       </c>
       <c r="B1133" t="n">
-        <v>0.3515542636079219</v>
+        <v>0.3399215690806617</v>
       </c>
       <c r="C1133" t="n">
-        <v>0.2585838025166219</v>
+        <v>0.2310363020399777</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="n">
-        <v>358</v>
+        <v>593</v>
       </c>
       <c r="B1134" t="n">
-        <v>0.5000033944491633</v>
+        <v>0.3320283267086759</v>
       </c>
       <c r="C1134" t="n">
-        <v>0.3729916448571253</v>
+        <v>0.2542393894907791</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="n">
-        <v>356</v>
+        <v>589</v>
       </c>
       <c r="B1135" t="n">
-        <v>0.3327558356755754</v>
+        <v>0.2480210315699611</v>
       </c>
       <c r="C1135" t="n">
-        <v>0.2199000990241202</v>
+        <v>0.0626501023053334</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="n">
-        <v>350</v>
+        <v>568</v>
       </c>
       <c r="B1136" t="n">
-        <v>0.3598804688315212</v>
+        <v>0.5348144217052087</v>
       </c>
       <c r="C1136" t="n">
-        <v>0.2387882887645696</v>
+        <v>0.4817852561827354</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="n">
-        <v>341</v>
+        <v>564</v>
       </c>
       <c r="B1137" t="n">
-        <v>0.2829854997111776</v>
+        <v>0.3839432190299117</v>
       </c>
       <c r="C1137" t="n">
-        <v>0.2091905340160411</v>
+        <v>0.2559023588795094</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="n">
-        <v>335</v>
+        <v>562</v>
       </c>
       <c r="B1138" t="n">
-        <v>0.5093757602482574</v>
+        <v>0.3790943074742468</v>
       </c>
       <c r="C1138" t="n">
-        <v>0.3043546729337944</v>
+        <v>0.3614077963456704</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="n">
-        <v>330</v>
+        <v>546</v>
       </c>
       <c r="B1139" t="n">
-        <v>0.4348408689715856</v>
+        <v>0.3202937101094996</v>
       </c>
       <c r="C1139" t="n">
-        <v>0.4374665044216579</v>
+        <v>0.2794628725556555</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="n">
-        <v>315</v>
+        <v>544</v>
       </c>
       <c r="B1140" t="n">
-        <v>0.4863745411124581</v>
+        <v>0.356095238815319</v>
       </c>
       <c r="C1140" t="n">
-        <v>0.2936616097412655</v>
+        <v>0.289554856575572</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="n">
-        <v>302</v>
+        <v>533</v>
       </c>
       <c r="B1141" t="n">
-        <v>0.3816660954294568</v>
+        <v>0.3517907505094081</v>
       </c>
       <c r="C1141" t="n">
-        <v>0.2793017507597848</v>
+        <v>0.2683683142835063</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="n">
-        <v>298</v>
+        <v>525</v>
       </c>
       <c r="B1142" t="n">
-        <v>0.3541408987732657</v>
+        <v>0.3365374921657849</v>
       </c>
       <c r="C1142" t="n">
-        <v>0.2786673434862694</v>
+        <v>0.2753415854725687</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="n">
-        <v>203</v>
+        <v>492</v>
       </c>
       <c r="B1143" t="n">
-        <v>0.3566917131396231</v>
+        <v>0.3081868086850818</v>
       </c>
       <c r="C1143" t="n">
-        <v>0.164819095239044</v>
+        <v>0.2034236192545361</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="n">
-        <v>201</v>
+        <v>470</v>
       </c>
       <c r="B1144" t="n">
-        <v>0.4259763733830724</v>
+        <v>0.3657319839094679</v>
       </c>
       <c r="C1144" t="n">
-        <v>0.08325449233915297</v>
+        <v>0.3167216654272322</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="n">
-        <v>170</v>
+        <v>469</v>
       </c>
       <c r="B1145" t="n">
-        <v>0.3480045353396229</v>
+        <v>0.5129694368684958</v>
       </c>
       <c r="C1145" t="n">
-        <v>0.2265326864931875</v>
+        <v>0.4073873210694758</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="n">
-        <v>165</v>
+        <v>422</v>
       </c>
       <c r="B1146" t="n">
-        <v>0.5844229148025044</v>
+        <v>0.4220577970203784</v>
       </c>
       <c r="C1146" t="n">
-        <v>0.2457090053564991</v>
+        <v>0.2797780994255004</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="n">
-        <v>160</v>
+        <v>408</v>
       </c>
       <c r="B1147" t="n">
-        <v>0.3392081143258015</v>
+        <v>0.5055553259058945</v>
       </c>
       <c r="C1147" t="n">
-        <v>0.279430526288543</v>
+        <v>0.3289547267588889</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="n">
-        <v>136</v>
+        <v>404</v>
       </c>
       <c r="B1148" t="n">
-        <v>0.3932107561686001</v>
+        <v>0.4917629056610113</v>
       </c>
       <c r="C1148" t="n">
-        <v>0.1147663344235801</v>
+        <v>0.3227668565900211</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="n">
-        <v>130</v>
+        <v>400</v>
       </c>
       <c r="B1149" t="n">
-        <v>0.334497244222458</v>
+        <v>0.489544680875939</v>
       </c>
       <c r="C1149" t="n">
-        <v>0.1693133175887665</v>
+        <v>0.4593864455640758</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="n">
-        <v>126</v>
+        <v>399</v>
       </c>
       <c r="B1150" t="n">
-        <v>0.3445791856648016</v>
+        <v>0.3891082115478011</v>
       </c>
       <c r="C1150" t="n">
-        <v>0.3078962958388993</v>
+        <v>0.3432206406128681</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="n">
-        <v>120</v>
+        <v>384</v>
       </c>
       <c r="B1151" t="n">
-        <v>0.3393268853040135</v>
+        <v>0.3586155263237701</v>
       </c>
       <c r="C1151" t="n">
-        <v>0.3096825354799859</v>
+        <v>0.2889873212971075</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="n">
-        <v>117</v>
+        <v>377</v>
       </c>
       <c r="B1152" t="n">
-        <v>0.5335248479868884</v>
+        <v>0.3515542636079219</v>
       </c>
       <c r="C1152" t="n">
-        <v>0.4186304566690558</v>
+        <v>0.2585838025166219</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="n">
-        <v>113</v>
+        <v>358</v>
       </c>
       <c r="B1153" t="n">
-        <v>0.2992042475452925</v>
+        <v>0.5000033944491633</v>
       </c>
       <c r="C1153" t="n">
-        <v>0.2749310471712628</v>
+        <v>0.3729916448571253</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="n">
-        <v>108</v>
+        <v>356</v>
       </c>
       <c r="B1154" t="n">
-        <v>0.3592549515250067</v>
+        <v>0.3327558356755754</v>
       </c>
       <c r="C1154" t="n">
-        <v>0.1963604589734766</v>
+        <v>0.2199000990241202</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="B1155" t="n">
-        <v>0.365545036299887</v>
+        <v>0.3598804688315212</v>
       </c>
       <c r="C1155" t="n">
-        <v>0.2647821919446209</v>
+        <v>0.2387882887645696</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="n">
-        <v>59</v>
+        <v>341</v>
       </c>
       <c r="B1156" t="n">
-        <v>0.295662973781009</v>
+        <v>0.2829854997111776</v>
       </c>
       <c r="C1156" t="n">
-        <v>0.2916591672572181</v>
+        <v>0.2091905340160411</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="n">
-        <v>54</v>
+        <v>335</v>
       </c>
       <c r="B1157" t="n">
-        <v>0.3614324876092318</v>
+        <v>0.5093757602482574</v>
       </c>
       <c r="C1157" t="n">
-        <v>0.3342401589364378</v>
+        <v>0.3043546729337944</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="n">
-        <v>51</v>
+        <v>330</v>
       </c>
       <c r="B1158" t="n">
-        <v>0.3968447072746557</v>
+        <v>0.4344370131957644</v>
       </c>
       <c r="C1158" t="n">
-        <v>0.1994597014144195</v>
+        <v>0.435236960593105</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="n">
-        <v>47</v>
+        <v>315</v>
       </c>
       <c r="B1159" t="n">
-        <v>0.2558056569818195</v>
+        <v>0.4863745411124581</v>
       </c>
       <c r="C1159" t="n">
-        <v>0.2548967820192801</v>
+        <v>0.2936616097412655</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="n">
-        <v>26</v>
+        <v>302</v>
       </c>
       <c r="B1160" t="n">
-        <v>0.3615219683875739</v>
+        <v>0.3816660954294568</v>
       </c>
       <c r="C1160" t="n">
-        <v>0.2937034697284091</v>
+        <v>0.2793017507597848</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="n">
-        <v>10</v>
+        <v>298</v>
       </c>
       <c r="B1161" t="n">
-        <v>0.337820674061093</v>
+        <v>0.3541408987732657</v>
       </c>
       <c r="C1161" t="n">
-        <v>0.3408693863136335</v>
+        <v>0.2786673434862694</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="n">
-        <v>9</v>
+        <v>203</v>
       </c>
       <c r="B1162" t="n">
-        <v>0.2571638469293809</v>
+        <v>0.3566917131396231</v>
       </c>
       <c r="C1162" t="n">
-        <v>0.06586683880326279</v>
+        <v>0.164819095239044</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="n">
+        <v>201</v>
+      </c>
+      <c r="B1163" t="n">
+        <v>0.4259763733830724</v>
+      </c>
+      <c r="C1163" t="n">
+        <v>0.08325449233915297</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="n">
+        <v>170</v>
+      </c>
+      <c r="B1164" t="n">
+        <v>0.3480045353396229</v>
+      </c>
+      <c r="C1164" t="n">
+        <v>0.2265326864931875</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="n">
+        <v>165</v>
+      </c>
+      <c r="B1165" t="n">
+        <v>0.5844229148025044</v>
+      </c>
+      <c r="C1165" t="n">
+        <v>0.2457090053564991</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="n">
+        <v>160</v>
+      </c>
+      <c r="B1166" t="n">
+        <v>0.3392081143258015</v>
+      </c>
+      <c r="C1166" t="n">
+        <v>0.279430526288543</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="n">
+        <v>147</v>
+      </c>
+      <c r="B1167" t="n">
+        <v>0.5626876443412214</v>
+      </c>
+      <c r="C1167" t="n">
+        <v>0.2495177824507541</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="n">
+        <v>136</v>
+      </c>
+      <c r="B1168" t="n">
+        <v>0.3932107561686001</v>
+      </c>
+      <c r="C1168" t="n">
+        <v>0.1147663344235801</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="n">
+        <v>130</v>
+      </c>
+      <c r="B1169" t="n">
+        <v>0.334497244222458</v>
+      </c>
+      <c r="C1169" t="n">
+        <v>0.1693133175887665</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="n">
+        <v>126</v>
+      </c>
+      <c r="B1170" t="n">
+        <v>0.3445791856648016</v>
+      </c>
+      <c r="C1170" t="n">
+        <v>0.3078962958388993</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="n">
+        <v>120</v>
+      </c>
+      <c r="B1171" t="n">
+        <v>0.3393268853040135</v>
+      </c>
+      <c r="C1171" t="n">
+        <v>0.3096825354799859</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="n">
+        <v>117</v>
+      </c>
+      <c r="B1172" t="n">
+        <v>0.5335248479868884</v>
+      </c>
+      <c r="C1172" t="n">
+        <v>0.4186304566690558</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="n">
+        <v>113</v>
+      </c>
+      <c r="B1173" t="n">
+        <v>0.2992042475452925</v>
+      </c>
+      <c r="C1173" t="n">
+        <v>0.2749310471712628</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="n">
+        <v>108</v>
+      </c>
+      <c r="B1174" t="n">
+        <v>0.3592549515250067</v>
+      </c>
+      <c r="C1174" t="n">
+        <v>0.1963604589734766</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="n">
+        <v>60</v>
+      </c>
+      <c r="B1175" t="n">
+        <v>0.365545036299887</v>
+      </c>
+      <c r="C1175" t="n">
+        <v>0.2647821919446209</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="n">
+        <v>59</v>
+      </c>
+      <c r="B1176" t="n">
+        <v>0.295662973781009</v>
+      </c>
+      <c r="C1176" t="n">
+        <v>0.2916591672572181</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="n">
+        <v>54</v>
+      </c>
+      <c r="B1177" t="n">
+        <v>0.3614324876092318</v>
+      </c>
+      <c r="C1177" t="n">
+        <v>0.3342401589364378</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="n">
+        <v>51</v>
+      </c>
+      <c r="B1178" t="n">
+        <v>0.3968447072746557</v>
+      </c>
+      <c r="C1178" t="n">
+        <v>0.1994597014144195</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="n">
+        <v>47</v>
+      </c>
+      <c r="B1179" t="n">
+        <v>0.2558056569818195</v>
+      </c>
+      <c r="C1179" t="n">
+        <v>0.2548967820192801</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="n">
+        <v>26</v>
+      </c>
+      <c r="B1180" t="n">
+        <v>0.3615219683875739</v>
+      </c>
+      <c r="C1180" t="n">
+        <v>0.2937034697284091</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="n">
+        <v>10</v>
+      </c>
+      <c r="B1181" t="n">
+        <v>0.337820674061093</v>
+      </c>
+      <c r="C1181" t="n">
+        <v>0.3408693863136335</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="n">
+        <v>9</v>
+      </c>
+      <c r="B1182" t="n">
+        <v>0.2571638469293809</v>
+      </c>
+      <c r="C1182" t="n">
+        <v>0.06586683880326279</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="n">
         <v>3</v>
       </c>
-      <c r="B1163" t="n">
+      <c r="B1183" t="n">
         <v>0.4554266993734111</v>
       </c>
-      <c r="C1163" t="n">
+      <c r="C1183" t="n">
         <v>0.4384625016000254</v>
       </c>
     </row>
